--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="791">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -221,6 +221,34 @@
     <t xml:space="preserve">philosophe indien connu pour son approche des "capabilités" qui mesure le développement.</t>
   </si>
   <si>
+    <t xml:space="preserve">Richard SWINBURNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Swinburne" title=" Wikipedia"&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bBud5SeV0jI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard SWINBURNE par Closer to Truth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/rswinburne-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Britannique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epistemologie ; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytique ; Théisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe britannique et figure de la philosophie analytique de la religion au XXe et XXIe siècles. </t>
+  </si>
+  <si>
     <t xml:space="preserve">1936</t>
   </si>
   <si>
@@ -456,6 +484,103 @@
     <t xml:space="preserve">philosophe canadienne-américaine connue pour avoir développé la neurophilosophie.</t>
   </si>
   <si>
+    <t xml:space="preserve">Frank JACKSON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Frank_Jackson" title=" Wikipedia"&gt;Frank JACKSON&lt;/a&gt; est un philosophe analytique australien, surtout connu pour son « argument de la connaissance » (ou « chambre de Mary »), l’un des défis les plus célèbres au physicalisme en philosophie de l’esprit. Il n a formulé cet argument dans les années 1980, en particulier dans ses articles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="https://www.youtube.com/results?search_query=Frank+Jackson+(philosophe)" &gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">« Epiphenomenal Qualia » &lt;/a&gt; (1982) et « What Mary Didn’t Know » (1986). Il y imagine Mary, une neuroscientifique brillante qui connaît toutes les vérités physiques sur la vision des couleurs, mais qui a toujours vécu dans une pièce en noir et blanc et n’a jamais fait l’expérience subjective du rouge. Quand elle sort et voit pour la première fois un objet rouge, elle apprend quelque chose de nouveau : « ce que cela fait » de voir du rouge. Il en conclut qu’il existe des faits (ou au moins des connaissances) qui ne sont pas réductibles aux faits physiques, et donc que le physicalisme – la thèse selon laquelle tout ce qui existe est physique – est faux. &lt;/p&gt; &lt;p&gt; Au-delà de cet argument,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="https://nyphilosophyreview.wordpress.com/2017/09/02/conversation-professor-frank-jackson/"  title="frank jackson par nanyang philo"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> il a travaillé &lt;/a&gt; sur de nombreux sujets de la philosophie analytique : philosophie de l’esprit, métaphysique, épistémologie, et éthique. Il s’est intéressé aux qualia (les aspects subjectifs et phénoménaux de l’expérience), au dualisme, à l’épiphénoménisme (l’idée que les états mentaux sont des effets sans causalité propre), ainsi qu’à la défense de l’analyse conceptuelle comme méthode philosophique. Son style est typique de la tradition analytique anglophone : clarté argumentative, usage d’exemples précis et de scénarios imaginaires pour tester des thèses générales. &lt;/p&gt; p&gt; Un point important est qu’il a ensuite évolué dans sa propre position. Après avoir longtemps défendu l’idée que l’argument de Mary montrait la fausseté du physicalisme, il a fini par changer d’avis et a adopté une forme de physicalisme, tout en maintenant que l’intuition derrière l’exemple de Mary reste puissante et doit être expliquée. Cela montre que, pour lui, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="https://www.youtube.com/watch?v=JhmncFBmHGg"  title="frank jackson on the knowledge par philosophy overdose"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">la philosophie progresse &lt;/a&gt;  en confrontant des intuitions fortes à des cadres théoriques rigoureux, et en acceptant de réviser ses propres thèses quand les arguments l’exigent. &lt;/p&gt; &lt;p&gt; Il est une figure centrale de la philosophie de l’esprit contemporaine, surtout grâce à son scénario de Mary, qui a structuré des décennies de débats sur la conscience, le physicalisme et la nature des faits phénoménaux. Son travail illustre bien la manière dont la philosophie analytique utilise des expériences de pensée simples mais puissantes pour mettre à l’épreuve des conceptions métaphysiques ambitieuses sur ce qu’est le monde et ce qu’est l’esprit. &lt;/p&gt; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3ffiCPgNeho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chambre de Mary par Noé Jacomet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/fjackson-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australienne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epistemologie ; metaphysique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytique ; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe analytique australien connu pour son « argument de la connaissance »  ou « chambre de Mary », l’un des défis les plus célèbres au physicalisme en philosophie de l’esprit.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1944</t>
   </si>
   <si>
@@ -526,6 +651,57 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe allemand à l'intersection de la philosophie du langage, de l'anthropologie &amp; sciences sociales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lew ROCKWELL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lew_Rockwell"   title=" Wikipedia"&gt;Lew ROCKWELL&lt;/a&gt; est est un penseur, auteur, et consultant politique américain, figure centrale du libertarianisme radical et de l’anarcho-capitalisme contemporain. Il est surtout connu comme fondateur et président du Ludwig von Mises Institute, un centre de recherche dédié à la promotion de l’École autrichienne d’économie et des idées libertariennes. &lt;/p&gt; &lt;p&gt; Il a été chef de cabinet du congressman républicain Ron Paul de 1978 à 1982, avant de quitter le Congrès pour fonder le Mises Institute en 1982. Très proche de Murray Rothbard jusqu’à la mort de ce dernier en 1995, il a cofondé avec lui le courant « paléo-libertarien », qui combine un anarcho-capitalisme fondé sur les droits naturels avec des valeurs de conservatisme culturel et une fidélité à la tradition de l’École autrichienne (Mises, Rothbard, Hazlitt). Son site LewRockwell.com, lancé en 1999, est devenu l’une des principales plateformes de diffusion d’articles et de commentaires libertariens, avec le slogan « anti-État, anti-guerre, pro-marché ». &lt;/p&gt; &lt;p&gt; Sur le plan philosophique et politique, il se définit comme </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/Anarcho-capitalisme"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">anarcho-capitaliste : &lt;/a&gt;  il rejette toute légitimité de l’État et considère que la société pourrait mieux protéger les libertés individuelles sans gouvernement, grâce à des institutions privées, des marchés libres et le principe de non-agression. Pour lui, l’État est par nature un monopole de la violence qui initie systématiquement la coercition, finance la guerre, étend le « police state » et intervient de manière nuisible dans l’économie ; il plaide donc pour une décentralisation radicale, y compris jusqu’à la sécession de certaines régions, afin de réduire le pouvoir du gouvernement central. &lt;/p&gt; &lt;p&gt; Il a aussi développé une critique virulente des libertariens qu’il juge trop modérés, en particulier les penseurs du Cato Institute, qu’il qualifie de « Beltway libertarians », accusés de compromissions avec le pouvoir washingtonien. Dans des ouvrages comme Against the State: An Anarcho-Capitalist Manifesto, il cherche à convertir des lecteurs sceptiques à l’anarchisme de marché en montrant que l’idée d’un « gouvernement limité » est, selon lui, irréaliste et que seule l’absence totale d’État peut garantir une liberté cohérente avec le principe de non-agression. &lt;/p&gt; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">79gUqenl4cQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">why egalitarianism lead to the destruction of the family par philosophyinsights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/lrockwell-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">politique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libertarianisme ; Anarcho-Capitalisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penseur, auteur, et consultant politique américain, figure centrale du libertarianisme radical et de l’anarcho-capitalisme contemporain.</t>
   </si>
   <si>
     <t xml:space="preserve">1945</t>
@@ -572,9 +748,6 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/singer-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Australienne</t>
-  </si>
-  <si>
     <t xml:space="preserve">Utilitarisme ; Antispécisme</t>
   </si>
   <si>
@@ -639,9 +812,6 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/dpapineau-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Britannique</t>
-  </si>
-  <si>
     <t xml:space="preserve">metaphysique ; epistemologie</t>
   </si>
   <si>
@@ -821,9 +991,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/hhhoppe-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">politique</t>
   </si>
   <si>
     <t xml:space="preserve">Anarcho-Capitalisme</t>
@@ -2438,7 +2605,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2527,14 +2694,20 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -2544,6 +2717,31 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2634,7 +2832,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2687,10 +2885,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2700,18 +2894,42 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2719,11 +2937,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2979,7 +3193,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2989,10 +3203,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="98.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="13.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="4.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="13.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="25.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
@@ -3213,7 +3427,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="214.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>1933</v>
       </c>
@@ -3250,81 +3464,81 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="233.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>1936</v>
-      </c>
-      <c r="C9" s="1" t="s">
+    <row r="9" customFormat="false" ht="247.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="10"/>
+      <c r="J9" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="192.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>1937</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+    <row r="10" customFormat="false" ht="288.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="15" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="185.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="228.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
@@ -3347,10 +3561,10 @@
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>89</v>
@@ -3359,9 +3573,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="185.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="s">
@@ -3370,7 +3584,7 @@
       <c r="D12" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="12" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -3384,10 +3598,10 @@
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="1" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>98</v>
@@ -3396,9 +3610,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
@@ -3421,44 +3635,44 @@
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>116</v>
@@ -3470,55 +3684,55 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
         <v>1942</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="11" t="s">
         <v>120</v>
       </c>
+      <c r="E15" s="10" t="s">
+        <v>121</v>
+      </c>
       <c r="F15" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F16" s="7" t="s">
@@ -3532,99 +3746,99 @@
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="138.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="371.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
-        <v>141</v>
+      <c r="C19" s="7" t="n">
+        <v>1943</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>150</v>
@@ -3638,146 +3852,146 @@
       <c r="G19" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="12" t="s">
         <v>154</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="1" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B20" s="7"/>
-      <c r="C20" s="7" t="n">
-        <v>1944</v>
+      <c r="C20" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="210.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
-        <v>172</v>
+      <c r="C22" s="7" t="n">
+        <v>1944</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="1" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="7" t="s">
-        <v>181</v>
+      <c r="C23" s="7" t="n">
+        <v>1944</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="18" t="s">
         <v>183</v>
       </c>
       <c r="F23" s="7" t="s">
@@ -3786,7 +4000,7 @@
       <c r="G23" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="12" t="s">
         <v>186</v>
       </c>
       <c r="I23" s="10"/>
@@ -3794,468 +4008,468 @@
         <v>51</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="M23" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M23" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>62</v>
+        <v>196</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B25" s="7"/>
-      <c r="C25" s="7" t="n">
-        <v>1947</v>
+      <c r="C25" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="1" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>208</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="1" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>23</v>
+        <v>212</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="10"/>
+      <c r="J28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I29" s="10"/>
+      <c r="J29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
         <v>1948</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>1948</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
-        <v>1949</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E30" s="10" t="s">
         <v>235</v>
       </c>
+      <c r="E30" s="9" t="s">
+        <v>236</v>
+      </c>
       <c r="F30" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="1" t="s">
-        <v>239</v>
+        <v>51</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="M30" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="7"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="I31" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="J31" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="K31" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="1" t="s">
+      <c r="L31" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D32" s="8" t="s">
+    <row r="32" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I32" s="10"/>
+      <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>187</v>
+        <v>254</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B33" s="7"/>
-      <c r="C33" s="7" t="n">
-        <v>1949</v>
+      <c r="C33" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="1" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>267</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="1" t="s">
-        <v>51</v>
+        <v>271</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E35" s="12" t="s">
         <v>273</v>
       </c>
+      <c r="E35" s="10" t="s">
+        <v>274</v>
+      </c>
       <c r="F35" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>277</v>
+        <v>42</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
-        <v>271</v>
+      <c r="C36" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="9" t="s">
         <v>280</v>
       </c>
       <c r="F36" s="7" t="s">
@@ -4264,35 +4478,35 @@
       <c r="G36" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="12" t="s">
         <v>283</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B37" s="7"/>
-      <c r="C37" s="7" t="n">
-        <v>1950</v>
+      <c r="C37" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="11" t="s">
         <v>287</v>
       </c>
       <c r="F37" s="7" t="s">
@@ -4301,12 +4515,12 @@
       <c r="G37" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="10" t="s">
         <v>290</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="1" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>291</v>
@@ -4314,85 +4528,85 @@
       <c r="L37" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M37" s="18" t="s">
+      <c r="M37" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E38" s="10" t="s">
         <v>295</v>
       </c>
+      <c r="E38" s="12" t="s">
+        <v>296</v>
+      </c>
       <c r="F38" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>116</v>
+        <v>300</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B39" s="7"/>
-      <c r="C39" s="7" t="n">
-        <v>1950</v>
+      <c r="C39" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>303</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="1" t="s">
-        <v>51</v>
+        <v>307</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>305</v>
+        <v>88</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>306</v>
+        <v>142</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1950</v>
       </c>
@@ -4400,79 +4614,79 @@
       <c r="C40" s="7" t="n">
         <v>1950</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E40" s="19" t="s">
+      <c r="D40" s="8" t="s">
         <v>309</v>
       </c>
+      <c r="E40" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="F40" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="1" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>315</v>
+      </c>
+      <c r="M40" s="17" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="E41" s="12" t="s">
         <v>317</v>
       </c>
+      <c r="E41" s="10" t="s">
+        <v>318</v>
+      </c>
       <c r="F41" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="1" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="7" t="s">
-        <v>315</v>
+      <c r="C42" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>323</v>
@@ -4486,7 +4700,7 @@
       <c r="G42" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="12" t="s">
         <v>327</v>
       </c>
       <c r="I42" s="10"/>
@@ -4494,303 +4708,303 @@
         <v>51</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>70</v>
+        <v>328</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B43" s="7"/>
-      <c r="C43" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="E43" s="11" t="s">
+      <c r="C43" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D43" s="21" t="s">
         <v>331</v>
       </c>
+      <c r="E43" s="23" t="s">
+        <v>332</v>
+      </c>
       <c r="F43" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="H43" s="10" t="s">
         <v>334</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>51</v>
+        <v>245</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>340</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="7" t="n">
-        <v>1952</v>
+      <c r="C45" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>345</v>
+        <v>346</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>347</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>350</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M45" s="15" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>351</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E46" s="10" t="s">
         <v>353</v>
       </c>
+      <c r="E46" s="11" t="s">
+        <v>354</v>
+      </c>
       <c r="F46" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>62</v>
+        <v>358</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>361</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="C48" s="7" t="s">
-        <v>351</v>
+      <c r="C48" s="7" t="n">
+        <v>1952</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>368</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>376</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>222</v>
+        <v>32</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>377</v>
+        <v>62</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="1" t="s">
-        <v>385</v>
+        <v>51</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>386</v>
@@ -4799,18 +5013,18 @@
         <v>387</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="10" t="s">
         <v>389</v>
       </c>
       <c r="F51" s="7" t="s">
@@ -4827,155 +5041,155 @@
         <v>51</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E52" s="21" t="s">
         <v>395</v>
       </c>
+      <c r="E52" s="11" t="s">
+        <v>396</v>
+      </c>
       <c r="F52" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="K52" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="E53" s="20" t="s">
         <v>403</v>
       </c>
+      <c r="E53" s="10" t="s">
+        <v>404</v>
+      </c>
       <c r="F53" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
-        <v>200</v>
+        <v>408</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>407</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B54" s="7"/>
-      <c r="C54" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="E54" s="19" t="s">
+      <c r="C54" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>411</v>
       </c>
+      <c r="E54" s="11" t="s">
+        <v>412</v>
+      </c>
       <c r="F54" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="H54" s="12" t="s">
         <v>414</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>415</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
-        <v>221</v>
+        <v>51</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="L54" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="M54" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="55" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="E55" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="F55" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="G55" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="H55" s="10" t="s">
         <v>421</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>423</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>200</v>
+        <v>422</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>230</v>
+        <v>423</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>53</v>
@@ -4984,18 +5198,18 @@
         <v>424</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="24" t="s">
         <v>426</v>
       </c>
       <c r="F56" s="7" t="s">
@@ -5009,1078 +5223,1078 @@
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="M56" s="2" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="D57" s="8" t="s">
+      <c r="E57" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="F57" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="G57" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="12" t="s">
         <v>437</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>51</v>
+        <v>245</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>32</v>
+        <v>438</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>328</v>
+        <v>439</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B58" s="7"/>
-      <c r="C58" s="7" t="n">
-        <v>1955</v>
+      <c r="C58" s="7" t="s">
+        <v>441</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>443</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>42</v>
+        <v>454</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>148</v>
+        <v>455</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>459</v>
+        <v>351</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="s">
-        <v>453</v>
+      <c r="C61" s="7" t="n">
+        <v>1955</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>464</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>466</v>
+        <v>133</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>467</v>
+        <v>166</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B62" s="7"/>
-      <c r="C62" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D62" s="16" t="s">
+      <c r="C62" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="D62" s="8" t="s">
         <v>470</v>
       </c>
+      <c r="E62" s="12" t="s">
+        <v>471</v>
+      </c>
       <c r="F62" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
-        <v>221</v>
+        <v>51</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>260</v>
+        <v>42</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>474</v>
+        <v>166</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B63" s="7"/>
-      <c r="C63" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D63" s="16" t="s">
+      <c r="C63" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="D63" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="12" t="s">
+      <c r="E63" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="F63" s="7" t="s">
         <v>479</v>
       </c>
+      <c r="G63" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="I63" s="10"/>
       <c r="J63" s="1" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>260</v>
+        <v>187</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>485</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>222</v>
+        <v>489</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>490</v>
+      <c r="C65" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>493</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>170</v>
+        <v>497</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="F66" s="7" t="s">
+      <c r="C66" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L66" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G66" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="M66" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="7" t="n">
-        <v>1958</v>
+      <c r="C67" s="7" t="s">
+        <v>504</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>502</v>
+        <v>505</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>506</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>505</v>
+        <v>508</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>509</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="M67" s="15" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B68" s="7"/>
       <c r="C68" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="1" t="s">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>516</v>
+        <v>518</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>520</v>
+        <v>422</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>187</v>
+        <v>351</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B70" s="7"/>
       <c r="C70" s="7" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>523</v>
+        <v>524</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>525</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="1" t="s">
-        <v>527</v>
+        <v>97</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>528</v>
+        <v>42</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M70" s="15" t="s">
+      <c r="M70" s="20" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="D71" s="1" t="s">
+    <row r="71" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="D71" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="E71" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="F71" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="G71" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="I71" s="1"/>
+      <c r="H71" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="I71" s="10"/>
       <c r="J71" s="1" t="s">
-        <v>536</v>
+        <v>271</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L71" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="72" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="E72" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="F72" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="G72" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="H72" s="10" t="s">
         <v>542</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>544</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>260</v>
+        <v>42</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>23</v>
+        <v>212</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="D73" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="G73" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="10"/>
       <c r="H73" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="I73" s="12" t="s">
+      <c r="I73" s="10"/>
+      <c r="J73" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="K73" s="2" t="s">
-        <v>79</v>
+        <v>551</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="M73" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="E74" s="11" t="s">
+    </row>
+    <row r="74" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="E74" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="F74" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="G74" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="I74" s="10"/>
+      <c r="H74" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
-        <v>247</v>
+        <v>559</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>187</v>
+      <c r="L74" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="1" t="s">
-        <v>51</v>
+        <v>568</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>564</v>
+        <v>23</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>1962</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="I76" s="10"/>
-      <c r="J76" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
-        <v>1963</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="E77" s="12" t="s">
         <v>576</v>
       </c>
+      <c r="E77" s="11" t="s">
+        <v>577</v>
+      </c>
       <c r="F77" s="7" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>580</v>
+        <v>42</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>487</v>
+        <v>212</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="E78" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="F78" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="G78" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="H78" s="10" t="s">
         <v>586</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>587</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="L78" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="M78" s="2" t="s">
+    </row>
+    <row r="79" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7" t="s">
+      <c r="E79" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="G79" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="H79" s="12" t="s">
         <v>593</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>595</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>42</v>
+        <v>594</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>187</v>
+        <v>595</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="E80" s="10" t="s">
         <v>598</v>
       </c>
+      <c r="E80" s="12" t="s">
+        <v>599</v>
+      </c>
       <c r="F80" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="1" t="s">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>602</v>
+        <v>510</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="1" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B82" s="7"/>
-      <c r="C82" s="7" t="n">
-        <v>1966</v>
+      <c r="C82" s="7" t="s">
+        <v>613</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>615</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="H82" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>617</v>
+        <v>21</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>618</v>
+        <v>212</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="E83" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="F83" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="G83" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="H83" s="10" t="s">
         <v>624</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>625</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="M83" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="84" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="F84" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="G84" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="H84" s="10" t="s">
         <v>632</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>634</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>53</v>
+        <v>633</v>
       </c>
       <c r="M84" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="D85" s="8" t="s">
+      <c r="E85" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="F85" s="7" t="s">
         <v>637</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="12" t="s">
         <v>639</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>640</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
-        <v>200</v>
+        <v>640</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>641</v>
@@ -6089,231 +6303,231 @@
         <v>642</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="E86" s="12" t="s">
         <v>644</v>
       </c>
+      <c r="E86" s="10" t="s">
+        <v>645</v>
+      </c>
       <c r="F86" s="7" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
-        <v>51</v>
+        <v>649</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>291</v>
+        <v>42</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7" t="n">
-        <v>1968</v>
+      <c r="C87" s="7" t="s">
+        <v>652</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>651</v>
+        <v>653</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>654</v>
+        <v>656</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>657</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>618</v>
+        <v>53</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>466</v>
+        <v>246</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>53</v>
+        <v>664</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>667</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>669</v>
+        <v>51</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>124</v>
+        <v>314</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>53</v>
+        <v>671</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="7" t="s">
-        <v>671</v>
+      <c r="C90" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="E90" s="9" t="s">
         <v>673</v>
       </c>
+      <c r="E90" s="12" t="s">
+        <v>674</v>
+      </c>
       <c r="F90" s="7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="H90" s="10" t="s">
         <v>676</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>677</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>580</v>
+        <v>79</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>487</v>
+        <v>641</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B91" s="7"/>
       <c r="C91" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="D91" s="22" t="s">
         <v>679</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="D91" s="8" t="s">
         <v>680</v>
       </c>
+      <c r="E91" s="10" t="s">
+        <v>681</v>
+      </c>
       <c r="F91" s="7" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>430</v>
+        <v>51</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>42</v>
+        <v>489</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="M91" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M91" s="2" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
@@ -6339,96 +6553,96 @@
         <v>692</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>466</v>
+        <v>133</v>
       </c>
       <c r="L92" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M92" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="93" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="D93" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="E93" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="F93" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="G93" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="H93" s="10" t="s">
         <v>699</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>700</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>124</v>
+        <v>603</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D94" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="E94" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="F94" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="H94" s="10" t="s">
         <v>706</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>707</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>200</v>
+        <v>453</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>277</v>
+        <v>42</v>
       </c>
       <c r="L94" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="M94" s="20" t="s">
         <v>708</v>
       </c>
-      <c r="M94" s="15" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="95" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>710</v>
@@ -6447,275 +6661,386 @@
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>106</v>
+        <v>715</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>415</v>
+        <v>489</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1980</v>
+        <v>1974</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>580</v>
+        <v>133</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>602</v>
+        <v>53</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>727</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>466</v>
+        <v>300</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>731</v>
+      </c>
+      <c r="M97" s="20" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1982</v>
+        <v>1975</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>692</v>
+        <v>115</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>466</v>
+        <v>438</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>53</v>
+        <v>738</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>739</v>
+        <v>741</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>742</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>32</v>
+        <v>603</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>53</v>
+        <v>625</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>41</v>
+        <v>715</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>42</v>
+        <v>489</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>757</v>
+        <v>53</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1990</v>
+        <v>1983</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="D102" s="22" t="s">
         <v>760</v>
       </c>
+      <c r="D102" s="8" t="s">
+        <v>761</v>
+      </c>
       <c r="E102" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>765</v>
+        <v>155</v>
       </c>
       <c r="K102" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="7" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="I103" s="10"/>
+      <c r="J103" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="7" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="I104" s="10"/>
+      <c r="J104" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K104" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L102" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>767</v>
+      <c r="L104" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="D105" s="26" t="s">
+        <v>783</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="I105" s="10"/>
+      <c r="J105" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -6727,61 +7052,65 @@
     <hyperlink ref="E4" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Hermann_L%C3%BCbbe&quot; title=&quot; Wikipedia&quot;&gt;Hermann LUBBE&lt;/a&gt; est un philosophe allemand dont l'œuvre se concentre sur une théorie de la civilisation moderne et de la démocratie libérale. Figure marquante du paysage intellectuel d'après-guerre, il s'est fait connaître en analysant les bouleversements de la société dynamique et en s'opposant fermement aux mouvements de protestation de 1968, ce qui lui a valu d'être perçu comme l'un des principaux représentants du &lt;a href=&quot;https://www.persee.fr/doc/reval_0035-0974_1988_num_20_1_3302&quot; title=&quot;Le néoconservatisme par persée&quot;&gt; néoconservatisme allemand. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Sa pensée se définit comme une « philosophie après les Lumières », cherchant à sécuriser les acquis du libéralisme tout en rejetant les grandes théories historiques totalisantes. Plutôt que de proposer des projets idéologiques, il privilégie une approche pragmatique qui examine la réalité sous l'angle de l'action pratique et de la résolution de problèmes. Cette méthode valorise le sens commun, la pratique quotidienne et une attention particulière à l'individu dans sa dimension contingente. &lt;/p&gt; &lt;p&gt; Il a développé une réflexion approfondie sur la dialectique entre le progrès technique et la stabilité sociale. Face à l'accélération constante du changement social, il insiste sur l'importance irremplaçable des traditions, des conventions et des institutions stables pour offrir une orientation aux citoyens. Pour lui, ces éléments ne sont pas des freins au progrès, mais des conditions nécessaires pour permettre aux individus de faire face à la complexité et à l'imprévisibilité du monde moderne. &lt;/p&gt; &lt;p&gt; La question de la religion occupe une place centrale dans sa réflexion sur la modernité, qu'il considère comme une ressource essentielle pour donner du sens à l'existence face à la contingence. Il soutient que, malgré le recul des dogmes institutionnels, la religion demeure une composante indispensable de la conscience humaine. À travers &lt;a href=&quot;https://www.persee.fr/doc/rscir_0035-2217_1988_num_62_1_3090_t1_0082_0000_3&quot; title=&quot;Fortdchrittsreaktionen par persée&quot;&gt;ses écrits, &lt;/a&gt; comme dans Sphären der Menschlichkeit, il explore la fragilité de la condition humaine face aux défis technologiques, plaidant pour une approche qui maintient la dignité et l'identité des sujets dans un monde en mutation permanente. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E6" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Taylor_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;Charles TAYLOR&lt;/a&gt; est un philosophe canadien connu pour ses travaux sur l’identité, la modernité, la morale et la reconnaissance. Il s’intéresse moins à des vérités abstraites qu’à la manière dont les êtres humains donnent du sens à leur vie dans des contextes historiques et culturels précis. &lt;/p&gt; &lt;p&gt; Sa philosophie critique d’abord l’idée d’un  &lt;a href=&quot;https://laviedesidees.fr/Charles-Taylor-philosophe-de-la&quot; title=&quot;Charles Taylor par la vie des idées&quot;&gt; individu totalement autonome &lt;/a&gt; et isolé. Il soutient que le moi se construit toujours dans un « horizon moral », c’est-à-dire à travers des valeurs, des langages et des relations qui le dépassent; on ne comprend donc pas une personne sans comprendre le monde partagé dans lequel elle vit. &lt;/p&gt; &lt;p&gt; Un de ses apports majeurs est la notion de reconnaissance. Il explique que chacun a besoin d’être reconnu dans sa singularité, par exemple dans son identité culturelle, linguistique ou religieuse, et il défend ainsi une politique qui respecte les différences sans tomber dans le repli communautaire. Il cherche donc  &lt;a href=&quot;https://www.youtube.com/watch?v=Drd0UT-BcGU&quot; title=&quot;Charles Taylor par Sociologie de l’intégration&quot;&gt; un équilibre entre l’universel &lt;/a&gt; et le particulier, entre les droits communs et la valeur des appartenances. &lt;/p&gt; &lt;p&gt; Il critique le réductionnisme des sciences humaines et l’idée que la raison humaine serait seulement calculatrice ou « désengagée ». Il privilégie une approche interprétative de l’être humain, inspirée de   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Herm%C3%A9neutique&quot; title=&quot;Herméneutique par Wikipedia&quot;&gt; l’herméneutique, &lt;/a&gt;  selon laquelle comprendre une action, une croyance ou une identité demande d’en saisir le sens vécu de l’intérieur. &lt;/p&gt; &#10; &lt;audio controls title= &quot;La modernité peut elle survivre aux religions par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-29.06.2012-ITEMA_20381664-2012C6608S0181-NET_9F56B454-BEBB-469E-974A-6F8782D1D7B5_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="E7" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Searle&quot;  title=&quot; Wikipedia&quot;&gt;John SEARLE&lt;/a&gt; est un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href=&quot;https://www.youtube.com/watch?v=pIbkpLfrD6A&quot; title=&quot;&#10;La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse&quot;&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du &quot;naturalisme biologique&quot; en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href=&quot;https://www.youtube.com/watch?v=EriAhi0mj7w&quot; title=&quot; Conscience et matière grise par TEDx Talks&quot;&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href=&quot;https://www.youtube.com/watch?v=Bq2bfSzkTfU&quot;  title=&quot;John Searle - Une personne peut-elle être une âme ? par Closer To Truth&quot;&gt;biologiques réels&lt;/a&gt; , causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href=&quot;https://www.youtube.com/watch?v=P5DtwDr9YEc&quot; title=&quot; La Chambre chinoise par Ian et frank&quot;&gt;Chambre Chinoise&lt;/a&gt; . Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href=&quot;https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf&quot;  title=&quot; La construction e la réalité sociale par nonmarchand&quot;&gt;&quot;La Construction de la Réalité Sociale&quot;&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les &quot;Faits bruts&quot; qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des &quot;Faits institutionnels&quot; qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H9" r:id="rId4" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
-    <hyperlink ref="E10" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E11" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
-    <hyperlink ref="E16" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
-    <hyperlink ref="E20" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H20" r:id="rId9" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
-    <hyperlink ref="E22" r:id="rId10" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H25" r:id="rId11" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
-    <hyperlink ref="E26" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
-    <hyperlink ref="E27" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H28" r:id="rId14" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
-    <hyperlink ref="I28" r:id="rId15" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
-    <hyperlink ref="H29" r:id="rId16" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
-    <hyperlink ref="E33" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H33" r:id="rId18" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
-    <hyperlink ref="E35" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
-    <hyperlink ref="E36" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H37" r:id="rId21" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
-    <hyperlink ref="E39" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H39" r:id="rId23" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
-    <hyperlink ref="E40" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
-    <hyperlink ref="H40" r:id="rId25" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
-    <hyperlink ref="E41" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E42" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H45" r:id="rId28" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
-    <hyperlink ref="E52" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E54" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
-    <hyperlink ref="H54" r:id="rId31" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
-    <hyperlink ref="E56" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E59" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E61" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="E62" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
-    <hyperlink ref="E63" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
-    <hyperlink ref="H63" r:id="rId37" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
-    <hyperlink ref="I63" r:id="rId38" display="https://www.laphilo.fr/photo/tarassov.webp"/>
-    <hyperlink ref="E64" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
-    <hyperlink ref="E67" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H67" r:id="rId41" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
-    <hyperlink ref="H70" r:id="rId42" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
-    <hyperlink ref="H71" r:id="rId43" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
-    <hyperlink ref="H73" r:id="rId44" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
-    <hyperlink ref="I73" r:id="rId45" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
-    <hyperlink ref="E76" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H76" r:id="rId47" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
-    <hyperlink ref="E77" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
-    <hyperlink ref="E79" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="H82" r:id="rId50" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E86" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H87" r:id="rId52" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E90" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E91" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E93" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E96" r:id="rId56" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E97" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E9" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Swinburne&quot; title=&quot; Wikipedia&quot;&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H9" r:id="rId5" display="https://www.laphilo.fr/pho/rswinburne-mini.webp"/>
+    <hyperlink ref="H10" r:id="rId6" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
+    <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
+    <hyperlink ref="E17" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
+    <hyperlink ref="H19" r:id="rId10" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
+    <hyperlink ref="E22" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H22" r:id="rId12" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
+    <hyperlink ref="H23" r:id="rId13" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
+    <hyperlink ref="E25" r:id="rId14" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H28" r:id="rId15" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
+    <hyperlink ref="E29" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
+    <hyperlink ref="E30" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H31" r:id="rId18" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
+    <hyperlink ref="I31" r:id="rId19" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
+    <hyperlink ref="H32" r:id="rId20" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
+    <hyperlink ref="E36" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H36" r:id="rId22" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
+    <hyperlink ref="E38" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
+    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H40" r:id="rId25" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H42" r:id="rId27" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
+    <hyperlink ref="E43" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
+    <hyperlink ref="H43" r:id="rId29" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
+    <hyperlink ref="E44" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H48" r:id="rId32" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
+    <hyperlink ref="E55" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E57" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
+    <hyperlink ref="H57" r:id="rId35" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
+    <hyperlink ref="E59" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E62" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E64" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="E65" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
+    <hyperlink ref="E66" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
+    <hyperlink ref="H66" r:id="rId41" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
+    <hyperlink ref="I66" r:id="rId42" display="https://www.laphilo.fr/photo/tarassov.webp"/>
+    <hyperlink ref="E67" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
+    <hyperlink ref="E70" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H70" r:id="rId45" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
+    <hyperlink ref="H73" r:id="rId46" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
+    <hyperlink ref="H74" r:id="rId47" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
+    <hyperlink ref="H76" r:id="rId48" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
+    <hyperlink ref="I76" r:id="rId49" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
+    <hyperlink ref="E79" r:id="rId50" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H79" r:id="rId51" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
+    <hyperlink ref="E80" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
+    <hyperlink ref="E82" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="H85" r:id="rId54" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
+    <hyperlink ref="E89" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H90" r:id="rId56" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E93" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E94" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E96" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E99" r:id="rId60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E100" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E103" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="797">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -359,6 +359,101 @@
     <t xml:space="preserve">philosophe américain connu pour ses contributions en logique modale.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ernest SOSA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">https://fr.wikipedia.org/wiki/Ernest_Sosa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">"  title=" Wikipedia"&gt;Ernest SOSA&lt;/a&gt; est l’un des épistémologues contemporains les plus influents, surtout connu pour avoir fondé l’épistémologie des vertus moderne et proposé une théorie de la connaissance comme « performance cognitive réussie ». &lt;/p&gt; &lt;p&gt; L’innovation majeure de Sosa est de concevoir la connaissance à partir de la notion de vertu intellectuelle : une qualité stable de l’agent qui le dispose à former des croyances vraies de façon fiable. Pour lui, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">  &lt;a href="https://www.la-philosophie.fr/philosophie-analytique/enest-sosa.html" title="ernest sosa : philosophie analytique par la-philosophie,fr"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">une vertu intellectuelle &lt;/a&gt; est « une qualité qui aide à maximiser l’excédent de vérité sur l’erreur » dans nos jugements. Ainsi, au lieu de se demander seulement si une croyance est justifiée par des raisons conscientes ou par des processus fiables, on demande si elle résulte d’une compétence épistémique de l’agent. &lt;/p&gt; &lt;p&gt; Il propose un modèle général d’évaluation des performances, appliqué aux croyances : Accuracy (exactitude), Adroitness (adresse/compétence), Aptness (justesse). Une croyance est accurate si elle est vraie, adroit si elle est formée avec compétence (en manifestant une vertu intellectuelle), et apte si elle est vraie parce que formée avec cette compétence. Dans ce cadre, la connaissance est essentiellement une « croyance apte » : une réussite cognitive où la vérité du jugement s’explique par la compétence de celui qui juge, et non par la chance. &lt;/p&gt; &lt;p&gt; Il distingue deux niveaux de connaissance : la « connaissance animale » (premier ordre) et la « connaissance réflexive » (second ordre). La première est une croyance apte produite par une compétence fiable, sans que l’agent ait besoin de théoriser sur sa propre fiabilité ; c’est le type de connaissance que partagent humains et animaux. La seconde exige en plus que l’agent soit en mesure de reconnaître, de façon elle-même compétente, que sa croyance de premier ordre est apte : il s’agit d’une approbation réflexive de sa propre performance cognitive. Cette distinction lui permet de rendre compte à la fois de la connaissance ordinaire et des exigences plus fortes de la philosophie sceptique. &lt;/p&gt; &lt;p&gt; L’épistémologie de Sosa vise à résoudre des problèmes classiques comme les cas de Gettier, le problème de la valeur de la connaissance, et certaines formes de scepticisme, en montrant que la connaissance est une réussite non accidentelle due à la compétence. Elle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">https://www.youtube.com/watch?v=C0H9htS0--c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">" title="ernest sosa « intuitions » par Rodrigo Borges"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">réconcilie partiellement &lt;/a&gt; internalisme et externalisme : la compétence peut être comprise de façon externaliste (fiabilité), tandis que la dimension réflexive réintroduit une exigence interne de prise de conscience de sa propre fiabilité. Enfin, il insiste sur la valeur de la « pleine connaissance » (full knowledge) comme contribuant à l’épanouissement humain au sens aristotélicien : bien connaître, c’est exercer au mieux nos vertus intellectuelles dans la vie. &lt;/p&gt; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">5FoVZ_A4vLg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ernest Sosa’s classical analysis par Elmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/esosa-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epistemologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Philosophe et épistémologue américain  connu pour avoir fondé l’épistémologie des vertus moderne.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1941</t>
   </si>
   <si>
@@ -430,9 +525,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/pchurchland-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epistemologie</t>
   </si>
   <si>
     <t xml:space="preserve">Eliminativisme ; Connexionnisme</t>
@@ -662,6 +754,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Lew_Rockwell"   title=" Wikipedia"&gt;Lew ROCKWELL&lt;/a&gt; est est un penseur, auteur, et consultant politique américain, figure centrale du libertarianisme radical et de l’anarcho-capitalisme contemporain. Il est surtout connu comme fondateur et président du Ludwig von Mises Institute, un centre de recherche dédié à la promotion de l’École autrichienne d’économie et des idées libertariennes. &lt;/p&gt; &lt;p&gt; Il a été chef de cabinet du congressman républicain Ron Paul de 1978 à 1982, avant de quitter le Congrès pour fonder le Mises Institute en 1982. Très proche de Murray Rothbard jusqu’à la mort de ce dernier en 1995, il a cofondé avec lui le courant « paléo-libertarien », qui combine un anarcho-capitalisme fondé sur les droits naturels avec des valeurs de conservatisme culturel et une fidélité à la tradition de l’École autrichienne (Mises, Rothbard, Hazlitt). Son site LewRockwell.com, lancé en 1999, est devenu l’une des principales plateformes de diffusion d’articles et de commentaires libertariens, avec le slogan « anti-État, anti-guerre, pro-marché ». &lt;/p&gt; &lt;p&gt; Sur le plan philosophique et politique, il se définit comme </t>
     </r>
@@ -671,6 +764,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/Anarcho-capitalisme"&gt;</t>
     </r>
@@ -680,6 +774,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">anarcho-capitaliste : &lt;/a&gt;  il rejette toute légitimité de l’État et considère que la société pourrait mieux protéger les libertés individuelles sans gouvernement, grâce à des institutions privées, des marchés libres et le principe de non-agression. Pour lui, l’État est par nature un monopole de la violence qui initie systématiquement la coercition, finance la guerre, étend le « police state » et intervient de manière nuisible dans l’économie ; il plaide donc pour une décentralisation radicale, y compris jusqu’à la sécession de certaines régions, afin de réduire le pouvoir du gouvernement central. &lt;/p&gt; &lt;p&gt; Il a aussi développé une critique virulente des libertariens qu’il juge trop modérés, en particulier les penseurs du Cato Institute, qu’il qualifie de « Beltway libertarians », accusés de compromissions avec le pouvoir washingtonien. Dans des ouvrages comme Against the State: An Anarcho-Capitalist Manifesto, il cherche à convertir des lecteurs sceptiques à l’anarchisme de marché en montrant que l’idée d’un « gouvernement limité » est, selon lui, irréaliste et que seule l’absence totale d’État peut garantir une liberté cohérente avec le principe de non-agression. &lt;/p&gt; 
 </t>
@@ -2605,7 +2700,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2704,6 +2799,37 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2717,31 +2843,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2897,15 +2998,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2914,6 +3011,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2921,7 +3022,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2929,15 +3030,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3193,7 +3294,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3610,7 +3711,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="219.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>1940</v>
       </c>
@@ -3647,198 +3748,198 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="312.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="7" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="G15" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="1" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="248.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>1942</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="138.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="G17" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="H17" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="138.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="371.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B19" s="7"/>
-      <c r="C19" s="7" t="n">
-        <v>1943</v>
+      <c r="C19" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>150</v>
@@ -3852,135 +3953,135 @@
       <c r="G19" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="10" t="s">
         <v>154</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="K19" s="2" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="371.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="E20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M19" s="17" t="s">
+      <c r="F20" s="7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>1944</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7" t="s">
+      <c r="G20" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="H20" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="1" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>163</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="G21" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="H21" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>22</v>
+        <v>171</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="210.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="7" t="n">
-        <v>1944</v>
+      <c r="C22" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>179</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="23" customFormat="false" ht="210.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>1944</v>
       </c>
@@ -3989,194 +4090,194 @@
         <v>1944</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="F23" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="12" t="s">
         <v>185</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>186</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="L23" s="2" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="E24" s="9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="G24" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="H24" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>194</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="G25" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="H25" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="1" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="G26" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="H26" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="1" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="H27" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B28" s="7"/>
-      <c r="C28" s="7" t="n">
-        <v>1947</v>
+      <c r="C28" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>221</v>
       </c>
       <c r="F28" s="7" t="s">
@@ -4185,72 +4286,72 @@
       <c r="G28" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="10" t="s">
         <v>224</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="L28" s="2" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="G29" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="H29" s="12" t="s">
         <v>230</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="12" t="s">
         <v>236</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -4264,195 +4365,195 @@
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B31" s="7"/>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L31" s="2" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="E32" s="22" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="F32" s="7"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C33" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="K33" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="L33" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="M33" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="34" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="G34" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="H34" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M34" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="35" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D35" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="G35" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="1" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>278</v>
@@ -4463,13 +4564,13 @@
         <v>1949</v>
       </c>
       <c r="B36" s="7"/>
-      <c r="C36" s="7" t="n">
-        <v>1949</v>
+      <c r="C36" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="10" t="s">
         <v>280</v>
       </c>
       <c r="F36" s="7" t="s">
@@ -4478,7 +4579,7 @@
       <c r="G36" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="10" t="s">
         <v>283</v>
       </c>
       <c r="I36" s="10"/>
@@ -4486,212 +4587,212 @@
         <v>21</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="L36" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="37" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B37" s="7"/>
-      <c r="C37" s="7" t="s">
-        <v>257</v>
+      <c r="C37" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="F37" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="G37" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="12" t="s">
         <v>289</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="38" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="G38" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="H38" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>53</v>
+        <v>298</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D39" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="F39" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="G39" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>306</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="40" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B40" s="7"/>
-      <c r="C40" s="7" t="n">
-        <v>1950</v>
+      <c r="C40" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="G40" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="H40" s="10" t="s">
         <v>312</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="1" t="s">
-        <v>69</v>
+        <v>313</v>
       </c>
       <c r="K40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="M40" s="17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="41" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B41" s="7"/>
-      <c r="C41" s="7" t="s">
-        <v>294</v>
+      <c r="C41" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D41" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="G41" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="H41" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>321</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>125</v>
+        <v>320</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M41" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="M41" s="20" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="7" t="n">
-        <v>1950</v>
+      <c r="C42" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="10" t="s">
         <v>324</v>
       </c>
       <c r="F42" s="7" t="s">
@@ -4700,24 +4801,24 @@
       <c r="G42" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="10" t="s">
         <v>327</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="K42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M42" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="43" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>1950</v>
       </c>
@@ -4725,264 +4826,264 @@
       <c r="C43" s="7" t="n">
         <v>1950</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="G43" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="H43" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>335</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>245</v>
+        <v>51</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>180</v>
+        <v>334</v>
       </c>
       <c r="L43" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="M43" s="2" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7" t="s">
+      <c r="E44" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="F44" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="G44" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="H44" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>343</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D45" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="F45" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="G45" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>349</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>350</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="M45" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D46" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E46" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="F46" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="G46" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="H46" s="10" t="s">
         <v>356</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="L46" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="M46" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="47" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D47" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="F47" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="G47" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="L47" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="48" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="C48" s="7" t="n">
-        <v>1952</v>
+      <c r="C48" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="D48" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="F48" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="G48" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="H48" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>371</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="L48" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="M48" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="M48" s="20" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7" t="s">
+      <c r="E49" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="F49" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="G49" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="H49" s="12" t="s">
         <v>377</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>379</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>381</v>
@@ -5004,37 +5105,37 @@
         <v>51</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="51" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D51" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="F51" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="G51" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="1" t="s">
@@ -5044,135 +5145,135 @@
         <v>42</v>
       </c>
       <c r="L51" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M51" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="52" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D52" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="F52" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="G52" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="H52" s="10" t="s">
         <v>398</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>399</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>246</v>
+        <v>42</v>
       </c>
       <c r="L52" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="M52" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="53" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E53" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="F53" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="G53" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="H53" s="10" t="s">
         <v>405</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>407</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
-        <v>408</v>
+        <v>51</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D54" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="G54" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="H54" s="10" t="s">
         <v>413</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>415</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
-        <v>51</v>
+        <v>414</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="E55" s="25" t="s">
+      <c r="E55" s="11" t="s">
         <v>418</v>
       </c>
       <c r="F55" s="7" t="s">
@@ -5186,141 +5287,141 @@
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="M55" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="56" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D56" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="F56" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="G56" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="H56" s="10" t="s">
         <v>427</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>429</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
-        <v>69</v>
+        <v>428</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="57" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B57" s="7"/>
-      <c r="C57" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D57" s="21" t="s">
+      <c r="C57" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="F57" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="G57" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="H57" s="10" t="s">
         <v>435</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>437</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>245</v>
+        <v>69</v>
       </c>
       <c r="K57" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="L57" s="2" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>439</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="E58" s="23" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="G58" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="H58" s="12" t="s">
         <v>443</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>254</v>
+        <v>444</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>53</v>
+        <v>445</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="10" t="s">
         <v>449</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -5334,67 +5435,67 @@
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="60" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D60" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G60" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="H60" s="10" t="s">
         <v>458</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>461</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
-        <v>51</v>
+        <v>459</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>32</v>
+        <v>460</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>351</v>
+        <v>461</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="n">
-        <v>1955</v>
+      <c r="C61" s="7" t="s">
+        <v>447</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="10" t="s">
         <v>464</v>
       </c>
       <c r="F61" s="7" t="s">
@@ -5411,161 +5512,161 @@
         <v>51</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>166</v>
+        <v>357</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B62" s="7"/>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="7" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="E62" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="F62" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="G62" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="H62" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>474</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="E63" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="F63" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="G63" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>480</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>481</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>482</v>
+        <v>172</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
         <v>1957</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E64" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="F64" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="G64" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="H64" s="10" t="s">
         <v>487</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>488</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="K64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D65" s="21" t="s">
+      <c r="C65" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="G65" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="H65" s="10" t="s">
         <v>494</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>496</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
-        <v>245</v>
+        <v>51</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>187</v>
+        <v>495</v>
       </c>
       <c r="L65" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="M65" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5577,118 +5678,118 @@
         <v>1958</v>
       </c>
       <c r="D66" s="21" t="s">
+        <v>498</v>
+      </c>
+      <c r="E66" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="E66" s="23" t="s">
+      <c r="F66" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="F66" s="7"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="12" t="s">
+      <c r="G66" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="H66" s="10" t="s">
         <v>502</v>
       </c>
+      <c r="I66" s="10"/>
       <c r="J66" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="D67" s="8" t="s">
+      <c r="C67" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D67" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="7"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="I67" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="J67" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="M67" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="68" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B68" s="7"/>
       <c r="C68" s="7" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D68" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="F68" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="G68" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="H68" s="10" t="s">
         <v>515</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>516</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>300</v>
+        <v>252</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>196</v>
+        <v>516</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="10" t="s">
         <v>519</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -5702,30 +5803,30 @@
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>351</v>
+        <v>202</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B70" s="7"/>
-      <c r="C70" s="7" t="n">
-        <v>1958</v>
+      <c r="C70" s="7" t="s">
+        <v>510</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="E70" s="11" t="s">
         <v>525</v>
       </c>
       <c r="F70" s="7" t="s">
@@ -5734,67 +5835,67 @@
       <c r="G70" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="10" t="s">
         <v>528</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="1" t="s">
-        <v>97</v>
+        <v>428</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L70" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="M70" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M70" s="20" t="s">
+    </row>
+    <row r="71" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7" t="s">
+      <c r="E71" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="F71" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="G71" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="H71" s="12" t="s">
         <v>534</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>536</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="1" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>535</v>
+      </c>
+      <c r="M71" s="14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
         <v>1959</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>538</v>
@@ -5813,170 +5914,172 @@
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M72" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M72" s="2" t="s">
+    </row>
+    <row r="73" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7" t="n">
-        <v>1960</v>
-      </c>
-      <c r="D73" s="8" t="s">
+      <c r="E73" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="F73" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="G73" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>548</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>549</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="K73" s="2" t="s">
+    </row>
+    <row r="74" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L73" s="2" t="s">
+      <c r="E74" s="24" t="s">
         <v>552</v>
       </c>
-      <c r="M73" s="20" t="s">
+      <c r="F74" s="7" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
+      <c r="G74" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="I74" s="10"/>
+      <c r="J74" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="M74" s="14" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
         <v>1960</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C75" s="1" t="n">
         <v>1960</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="K74" s="2" t="s">
+      <c r="D75" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L74" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="L75" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="M75" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="I75" s="10"/>
-      <c r="J75" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="76" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="B76" s="7"/>
-      <c r="C76" s="7" t="n">
+      <c r="C76" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="I76" s="10"/>
+      <c r="J76" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>1961</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="F76" s="7"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>573</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
-        <v>1962</v>
-      </c>
       <c r="B77" s="7"/>
-      <c r="C77" s="7" t="s">
-        <v>575</v>
+      <c r="C77" s="7" t="n">
+        <v>1961</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>576</v>
@@ -5984,36 +6087,34 @@
       <c r="E77" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="7"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="I77" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="J77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="I77" s="10"/>
-      <c r="J77" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="78" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>582</v>
@@ -6032,178 +6133,178 @@
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="1" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L78" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="79" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B79" s="7"/>
-      <c r="C79" s="7" t="n">
-        <v>1962</v>
+      <c r="C79" s="7" t="s">
+        <v>581</v>
       </c>
       <c r="D79" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="E79" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="F79" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="G79" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="H79" s="10" t="s">
         <v>592</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>593</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="L79" s="2" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D80" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="E80" s="9" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="G80" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="H80" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>602</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>510</v>
+        <v>601</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="F81" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="G81" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="H81" s="10" t="s">
         <v>608</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>610</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>133</v>
+        <v>609</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>611</v>
+        <v>516</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="E82" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="F82" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="G82" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="H82" s="10" t="s">
         <v>616</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>618</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>212</v>
+        <v>617</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="12" t="s">
         <v>621</v>
       </c>
       <c r="F83" s="7" t="s">
@@ -6217,173 +6318,173 @@
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>603</v>
+        <v>42</v>
       </c>
       <c r="L83" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M83" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="M83" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="84" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="F84" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="G84" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="H84" s="10" t="s">
         <v>630</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>632</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="B85" s="7"/>
-      <c r="C85" s="7" t="n">
-        <v>1966</v>
+      <c r="C85" s="7" t="s">
+        <v>633</v>
       </c>
       <c r="D85" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="F85" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>638</v>
-      </c>
-      <c r="H85" s="12" t="s">
-        <v>639</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="M85" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L85" s="2" t="s">
+    </row>
+    <row r="86" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="E86" s="10" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7" t="s">
+      <c r="F86" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="G86" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="H86" s="12" t="s">
         <v>645</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>648</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="G87" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="H87" s="10" t="s">
         <v>654</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>656</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>657</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
-        <v>51</v>
+        <v>655</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>53</v>
+        <v>656</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>659</v>
@@ -6402,53 +6503,53 @@
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c r="L88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="M88" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="89" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D89" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="E89" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="F89" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="F89" s="7" t="s">
+      <c r="G89" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="H89" s="10" t="s">
         <v>669</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>670</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="L89" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="M89" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6456,369 +6557,369 @@
         <v>1968</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="7" t="n">
-        <v>1968</v>
+      <c r="C90" s="7" t="s">
+        <v>658</v>
       </c>
       <c r="D90" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="F90" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="G90" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="H90" s="10" t="s">
         <v>676</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>677</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>271</v>
+        <v>51</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="7" t="n">
+        <v>1968</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="E91" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="F91" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="G91" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="H91" s="12" t="s">
         <v>683</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>684</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>489</v>
+        <v>79</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>53</v>
+        <v>647</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="D92" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="E92" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="F92" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="G92" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="H92" s="10" t="s">
         <v>690</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>691</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
-        <v>692</v>
+        <v>51</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>133</v>
+        <v>495</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="F93" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="G93" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="H93" s="10" t="s">
         <v>697</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>699</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>603</v>
+        <v>114</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="D94" s="26" t="s">
+      <c r="E94" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="F94" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="10" t="s">
         <v>704</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="H94" s="10" t="s">
         <v>705</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>706</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>453</v>
+        <v>21</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>42</v>
+        <v>609</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="M94" s="20" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>516</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="E95" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="F95" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="G95" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="H95" s="10" t="s">
         <v>712</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>713</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>714</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>715</v>
+        <v>459</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>489</v>
+        <v>42</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>713</v>
+      </c>
+      <c r="M95" s="14" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="F96" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="G96" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="H96" s="10" t="s">
         <v>720</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>722</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>723</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>51</v>
+        <v>721</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>133</v>
+        <v>495</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>53</v>
+        <v>722</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D97" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="E97" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="F97" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="G97" s="10" t="s">
+      <c r="H97" s="10" t="s">
         <v>729</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>730</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>300</v>
+        <v>114</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="M97" s="20" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D98" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="F98" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="G98" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="G98" s="10" t="s">
+      <c r="H98" s="10" t="s">
         <v>736</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>737</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>438</v>
+        <v>306</v>
       </c>
       <c r="L98" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="M98" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="M98" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="E99" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="F99" s="7" t="s">
         <v>741</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="G99" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="H99" s="10" t="s">
         <v>743</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>744</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>745</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>603</v>
+        <v>444</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>625</v>
+        <v>744</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6827,7 +6928,7 @@
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>747</v>
@@ -6846,201 +6947,238 @@
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>489</v>
+        <v>609</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>53</v>
+        <v>631</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D101" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="E101" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="F101" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="G101" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="G101" s="10" t="s">
+      <c r="H101" s="10" t="s">
         <v>757</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>758</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>715</v>
+        <v>51</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="D102" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="E102" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="F102" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="G102" s="10" t="s">
         <v>763</v>
       </c>
-      <c r="G102" s="10" t="s">
+      <c r="H102" s="10" t="s">
         <v>764</v>
-      </c>
-      <c r="H102" s="10" t="s">
-        <v>765</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>155</v>
+        <v>721</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>32</v>
+        <v>495</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="D103" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="E103" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="F103" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="G103" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="G103" s="10" t="s">
+      <c r="H103" s="10" t="s">
         <v>771</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>772</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>489</v>
+        <v>32</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="E104" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="F104" s="7" t="s">
         <v>776</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="G104" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="G104" s="10" t="s">
+      <c r="H104" s="10" t="s">
         <v>778</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>779</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>42</v>
+        <v>495</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>780</v>
+        <v>53</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="E105" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="D105" s="26" t="s">
+      <c r="F105" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="G105" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="H105" s="10" t="s">
         <v>785</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>786</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>787</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="1" t="s">
-        <v>788</v>
+        <v>41</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L105" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="D106" s="26" t="s">
         <v>789</v>
       </c>
-      <c r="M105" s="2" t="s">
+      <c r="E106" s="10" t="s">
         <v>790</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="I106" s="10"/>
+      <c r="J106" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -7057,60 +7195,61 @@
     <hyperlink ref="H10" r:id="rId6" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
     <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
-    <hyperlink ref="E17" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
-    <hyperlink ref="H19" r:id="rId10" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
-    <hyperlink ref="E22" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H22" r:id="rId12" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
-    <hyperlink ref="H23" r:id="rId13" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
-    <hyperlink ref="E25" r:id="rId14" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H28" r:id="rId15" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
-    <hyperlink ref="E29" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
-    <hyperlink ref="E30" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H31" r:id="rId18" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
-    <hyperlink ref="I31" r:id="rId19" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
-    <hyperlink ref="H32" r:id="rId20" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
-    <hyperlink ref="E36" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H36" r:id="rId22" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
-    <hyperlink ref="E38" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
-    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H40" r:id="rId25" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
-    <hyperlink ref="E42" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H42" r:id="rId27" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
-    <hyperlink ref="E43" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
-    <hyperlink ref="H43" r:id="rId29" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H48" r:id="rId32" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
-    <hyperlink ref="E55" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E57" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
-    <hyperlink ref="H57" r:id="rId35" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
-    <hyperlink ref="E59" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E62" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E64" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="E65" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
-    <hyperlink ref="E66" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
-    <hyperlink ref="H66" r:id="rId41" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
-    <hyperlink ref="I66" r:id="rId42" display="https://www.laphilo.fr/photo/tarassov.webp"/>
-    <hyperlink ref="E67" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
-    <hyperlink ref="E70" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H70" r:id="rId45" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
-    <hyperlink ref="H73" r:id="rId46" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
-    <hyperlink ref="H74" r:id="rId47" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
-    <hyperlink ref="H76" r:id="rId48" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
-    <hyperlink ref="I76" r:id="rId49" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
-    <hyperlink ref="E79" r:id="rId50" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H79" r:id="rId51" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
-    <hyperlink ref="E80" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
-    <hyperlink ref="E82" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="H85" r:id="rId54" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E89" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H90" r:id="rId56" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E93" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E94" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E96" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E99" r:id="rId60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E100" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E103" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="H14" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
+    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
+    <hyperlink ref="H20" r:id="rId11" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
+    <hyperlink ref="E23" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H23" r:id="rId13" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
+    <hyperlink ref="H24" r:id="rId14" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
+    <hyperlink ref="E26" r:id="rId15" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H29" r:id="rId16" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
+    <hyperlink ref="E30" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
+    <hyperlink ref="E31" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H32" r:id="rId19" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
+    <hyperlink ref="I32" r:id="rId20" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
+    <hyperlink ref="H33" r:id="rId21" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
+    <hyperlink ref="E37" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H37" r:id="rId23" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
+    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
+    <hyperlink ref="E40" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H41" r:id="rId26" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
+    <hyperlink ref="E43" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H43" r:id="rId28" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
+    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
+    <hyperlink ref="H44" r:id="rId30" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
+    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E46" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H49" r:id="rId33" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
+    <hyperlink ref="E56" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E58" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
+    <hyperlink ref="H58" r:id="rId36" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
+    <hyperlink ref="E60" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E63" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E65" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="E66" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
+    <hyperlink ref="E67" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
+    <hyperlink ref="H67" r:id="rId42" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
+    <hyperlink ref="I67" r:id="rId43" display="https://www.laphilo.fr/photo/tarassov.webp"/>
+    <hyperlink ref="E68" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
+    <hyperlink ref="E71" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H71" r:id="rId46" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
+    <hyperlink ref="H74" r:id="rId47" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
+    <hyperlink ref="H75" r:id="rId48" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
+    <hyperlink ref="H77" r:id="rId49" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
+    <hyperlink ref="I77" r:id="rId50" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
+    <hyperlink ref="E80" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H80" r:id="rId52" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
+    <hyperlink ref="E81" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
+    <hyperlink ref="E83" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="H86" r:id="rId55" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
+    <hyperlink ref="E90" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H91" r:id="rId57" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E94" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E95" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E97" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E100" r:id="rId61" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E101" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E104" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="804">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -367,6 +367,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;p&gt;&lt;a href="</t>
     </r>
@@ -376,6 +377,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">https://fr.wikipedia.org/wiki/Ernest_Sosa</t>
     </r>
@@ -384,6 +386,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">"  title=" Wikipedia"&gt;Ernest SOSA&lt;/a&gt; est l’un des épistémologues contemporains les plus influents, surtout connu pour avoir fondé l’épistémologie des vertus moderne et proposé une théorie de la connaissance comme « performance cognitive réussie ». &lt;/p&gt; &lt;p&gt; L’innovation majeure de Sosa est de concevoir la connaissance à partir de la notion de vertu intellectuelle : une qualité stable de l’agent qui le dispose à former des croyances vraies de façon fiable. Pour lui, </t>
     </r>
@@ -392,6 +395,7 @@
         <sz val="9"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">  &lt;a href="https://www.la-philosophie.fr/philosophie-analytique/enest-sosa.html" title="ernest sosa : philosophie analytique par la-philosophie,fr"&gt;</t>
     </r>
@@ -400,6 +404,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">une vertu intellectuelle &lt;/a&gt; est « une qualité qui aide à maximiser l’excédent de vérité sur l’erreur » dans nos jugements. Ainsi, au lieu de se demander seulement si une croyance est justifiée par des raisons conscientes ou par des processus fiables, on demande si elle résulte d’une compétence épistémique de l’agent. &lt;/p&gt; &lt;p&gt; Il propose un modèle général d’évaluation des performances, appliqué aux croyances : Accuracy (exactitude), Adroitness (adresse/compétence), Aptness (justesse). Une croyance est accurate si elle est vraie, adroit si elle est formée avec compétence (en manifestant une vertu intellectuelle), et apte si elle est vraie parce que formée avec cette compétence. Dans ce cadre, la connaissance est essentiellement une « croyance apte » : une réussite cognitive où la vérité du jugement s’explique par la compétence de celui qui juge, et non par la chance. &lt;/p&gt; &lt;p&gt; Il distingue deux niveaux de connaissance : la « connaissance animale » (premier ordre) et la « connaissance réflexive » (second ordre). La première est une croyance apte produite par une compétence fiable, sans que l’agent ait besoin de théoriser sur sa propre fiabilité ; c’est le type de connaissance que partagent humains et animaux. La seconde exige en plus que l’agent soit en mesure de reconnaître, de façon elle-même compétente, que sa croyance de premier ordre est apte : il s’agit d’une approbation réflexive de sa propre performance cognitive. Cette distinction lui permet de rendre compte à la fois de la connaissance ordinaire et des exigences plus fortes de la philosophie sceptique. &lt;/p&gt; &lt;p&gt; L’épistémologie de Sosa vise à résoudre des problèmes classiques comme les cas de Gettier, le problème de la valeur de la connaissance, et certaines formes de scepticisme, en montrant que la connaissance est une réussite non accidentelle due à la compétence. Elle </t>
     </r>
@@ -408,6 +413,7 @@
         <sz val="9"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;a href="</t>
     </r>
@@ -417,6 +423,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">https://www.youtube.com/watch?v=C0H9htS0--c</t>
     </r>
@@ -425,6 +432,7 @@
         <sz val="9"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">" title="ernest sosa « intuitions » par Rodrigo Borges"&gt;</t>
     </r>
@@ -433,6 +441,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">réconcilie partiellement &lt;/a&gt; internalisme et externalisme : la compétence peut être comprise de façon externaliste (fiabilité), tandis que la dimension réflexive réintroduit une exigence interne de prise de conscience de sa propre fiabilité. Enfin, il insiste sur la valeur de la « pleine connaissance » (full knowledge) comme contribuant à l’épanouissement humain au sens aristotélicien : bien connaître, c’est exercer au mieux nos vertus intellectuelles dans la vie. &lt;/p&gt; 
 </t>
@@ -531,6 +540,68 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe canadien-américain connu pour défendre une approche naturaliste de la pensée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alison JAGGAR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://en.wikipedia.org/wiki/Alison_Jaggar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"  title=" Wikipedia"&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;a href="https://journals.openedition.org/lectures/15257?lang=es"  title="alison jaggar ; gender and global justice par openedition "&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ht4tG96X7Gg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alison Jaggar par Center  for Global ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/ajaggar-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Féminisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> philosophe féministe anglo-américaine qui a contribué à installer les questions de genre dans la philosophie morale, politique et sociale contemporaine.</t>
   </si>
   <si>
     <t xml:space="preserve">1943</t>
@@ -2700,7 +2771,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2803,20 +2874,21 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2828,21 +2900,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2998,7 +3063,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3014,10 +3083,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3030,15 +3095,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3294,7 +3359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3759,7 +3824,7 @@
       <c r="D14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="11" t="s">
         <v>110</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -3768,7 +3833,7 @@
       <c r="G14" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="12" t="s">
         <v>113</v>
       </c>
       <c r="I14" s="10"/>
@@ -3781,7 +3846,7 @@
       <c r="L14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="16" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3859,7 +3924,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="183.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>1942</v>
       </c>
@@ -3896,55 +3961,55 @@
         <v>141</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="138.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="307.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="F18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M18" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" customFormat="false" ht="138.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="20" t="s">
         <v>151</v>
       </c>
       <c r="F19" s="7" t="s">
@@ -3958,121 +4023,121 @@
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>114</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="371.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B20" s="7"/>
-      <c r="C20" s="7" t="n">
-        <v>1943</v>
+      <c r="C20" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="12" t="s">
         <v>160</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="1" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="L20" s="2" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="371.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="M20" s="20" t="s">
+      <c r="E21" s="9" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>1944</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="G21" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="H21" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="1" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="K21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>179</v>
@@ -4081,13 +4146,13 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="210.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="7" t="n">
-        <v>1944</v>
+      <c r="C23" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>181</v>
@@ -4101,24 +4166,24 @@
       <c r="G23" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="10" t="s">
         <v>185</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="210.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>1944</v>
       </c>
@@ -4143,136 +4208,136 @@
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>193</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="M24" s="20" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="G25" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="H25" s="12" t="s">
         <v>199</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M25" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="F26" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="H26" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="1" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="27" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="H27" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="1" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L27" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>220</v>
@@ -4294,278 +4359,278 @@
         <v>51</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B29" s="7"/>
-      <c r="C29" s="7" t="n">
-        <v>1947</v>
+      <c r="C29" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
+      <c r="E29" s="10" t="s">
+        <v>228</v>
+      </c>
       <c r="F29" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="H29" s="12" t="s">
         <v>230</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="L29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="M29" s="14" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
+      <c r="E30" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="G30" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="H30" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="M30" s="14" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E31" s="9" t="s">
         <v>242</v>
       </c>
+      <c r="E31" s="12" t="s">
+        <v>243</v>
+      </c>
       <c r="F31" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B32" s="7"/>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="M32" s="2" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="E33" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C34" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1" t="s">
+      <c r="D34" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G34" s="10" t="s">
+      <c r="K34" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="L34" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="1" t="s">
+      <c r="M34" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="35" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D35" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="G35" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>279</v>
@@ -4584,16 +4649,16 @@
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="1" t="s">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4601,50 +4666,50 @@
         <v>1949</v>
       </c>
       <c r="B37" s="7"/>
-      <c r="C37" s="7" t="n">
-        <v>1949</v>
+      <c r="C37" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="E37" s="9" t="s">
         <v>286</v>
       </c>
+      <c r="E37" s="10" t="s">
+        <v>287</v>
+      </c>
       <c r="F37" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="H37" s="12" t="s">
         <v>289</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>290</v>
+        <v>225</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="7" t="s">
-        <v>263</v>
+      <c r="C38" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="9" t="s">
         <v>293</v>
       </c>
       <c r="F38" s="7" t="s">
@@ -4653,67 +4718,67 @@
       <c r="G38" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="12" t="s">
         <v>296</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K38" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="F39" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="G39" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="H39" s="10" t="s">
         <v>303</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K39" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="40" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>308</v>
@@ -4732,30 +4797,30 @@
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="L40" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B41" s="7"/>
-      <c r="C41" s="7" t="n">
-        <v>1950</v>
+      <c r="C41" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="12" t="s">
         <v>316</v>
       </c>
       <c r="F41" s="7" t="s">
@@ -4764,98 +4829,98 @@
       <c r="G41" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="10" t="s">
         <v>319</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="1" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>320</v>
+        <v>88</v>
       </c>
       <c r="L41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M41" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="M41" s="20" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="7" t="s">
-        <v>300</v>
+      <c r="C42" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="E42" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="F42" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="G42" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="H42" s="12" t="s">
         <v>326</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>132</v>
+        <v>327</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M42" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M42" s="16" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B43" s="7"/>
-      <c r="C43" s="7" t="n">
-        <v>1950</v>
+      <c r="C43" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="9" t="s">
         <v>330</v>
       </c>
+      <c r="E43" s="10" t="s">
+        <v>331</v>
+      </c>
       <c r="F43" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="H43" s="12" t="s">
         <v>333</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>334</v>
+        <v>132</v>
       </c>
       <c r="L43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="44" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1950</v>
       </c>
@@ -4863,27 +4928,27 @@
       <c r="C44" s="7" t="n">
         <v>1950</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="F44" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="G44" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="H44" s="12" t="s">
         <v>340</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>251</v>
+        <v>51</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>342</v>
@@ -4892,55 +4957,55 @@
         <v>343</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="E45" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="F45" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="G45" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="12" t="s">
         <v>348</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
-        <v>61</v>
+        <v>258</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="L45" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="M45" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="12" t="s">
         <v>353</v>
       </c>
       <c r="F46" s="7" t="s">
@@ -4954,10 +5019,10 @@
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>357</v>
@@ -4966,18 +5031,18 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="9" t="s">
         <v>360</v>
       </c>
       <c r="F47" s="7" t="s">
@@ -4994,7 +5059,7 @@
         <v>51</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>364</v>
@@ -5003,13 +5068,13 @@
         <v>365</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>366</v>
@@ -5028,10 +5093,10 @@
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>371</v>
@@ -5040,18 +5105,18 @@
         <v>372</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B49" s="7"/>
-      <c r="C49" s="7" t="n">
-        <v>1952</v>
+      <c r="C49" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="11" t="s">
         <v>374</v>
       </c>
       <c r="F49" s="7" t="s">
@@ -5060,104 +5125,104 @@
       <c r="G49" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H49" s="10" t="s">
         <v>377</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="M49" s="14" t="s">
+      <c r="M49" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B50" s="7"/>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="E50" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="F50" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="G50" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="H50" s="12" t="s">
         <v>384</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>385</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M50" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="M50" s="14" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>394</v>
@@ -5188,18 +5253,18 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="10" t="s">
         <v>402</v>
       </c>
       <c r="F53" s="7" t="s">
@@ -5216,7 +5281,7 @@
         <v>51</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>406</v>
@@ -5225,351 +5290,351 @@
         <v>407</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="E54" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="F54" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="G54" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="H54" s="10" t="s">
         <v>412</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="K54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="55" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D55" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="F55" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="G55" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>51</v>
+        <v>421</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="E56" s="25" t="s">
         <v>424</v>
       </c>
+      <c r="E56" s="11" t="s">
+        <v>425</v>
+      </c>
       <c r="F56" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
-        <v>428</v>
+        <v>51</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="57" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D57" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="E57" s="25" t="s">
         <v>431</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="F57" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="G57" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>434</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>435</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>69</v>
+        <v>435</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>436</v>
       </c>
       <c r="L57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="M57" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="58" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B58" s="7"/>
-      <c r="C58" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D58" s="21" t="s">
+      <c r="C58" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="E58" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="F58" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="G58" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="H58" s="10" t="s">
         <v>442</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>443</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>251</v>
+        <v>69</v>
       </c>
       <c r="K58" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="L58" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="M58" s="2" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D59" s="21" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7" t="s">
+      <c r="E59" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="F59" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="G59" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="H59" s="12" t="s">
         <v>450</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>452</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>69</v>
+        <v>258</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>53</v>
+        <v>452</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="E60" s="12" t="s">
         <v>455</v>
       </c>
+      <c r="E60" s="10" t="s">
+        <v>456</v>
+      </c>
       <c r="F60" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
-        <v>459</v>
+        <v>69</v>
       </c>
       <c r="K60" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M60" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L60" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="61" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D61" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="G61" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="H61" s="10" t="s">
         <v>465</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>467</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="1" t="s">
-        <v>51</v>
+        <v>466</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>32</v>
+        <v>467</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>357</v>
+        <v>468</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B62" s="7"/>
-      <c r="C62" s="7" t="n">
-        <v>1955</v>
+      <c r="C62" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E62" s="11" t="s">
         <v>470</v>
       </c>
+      <c r="E62" s="10" t="s">
+        <v>471</v>
+      </c>
       <c r="F62" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>172</v>
+        <v>364</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B63" s="7"/>
-      <c r="C63" s="7" t="s">
-        <v>475</v>
+      <c r="C63" s="7" t="n">
+        <v>1955</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
         <v>477</v>
       </c>
       <c r="F63" s="7" t="s">
@@ -5586,18 +5651,18 @@
         <v>51</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
@@ -5606,7 +5671,7 @@
       <c r="D64" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="12" t="s">
         <v>484</v>
       </c>
       <c r="F64" s="7" t="s">
@@ -5620,30 +5685,30 @@
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="L64" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="M64" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="65" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
         <v>1957</v>
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="7" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="10" t="s">
         <v>491</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -5657,47 +5722,47 @@
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="K65" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="M65" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D66" s="21" t="s">
+      <c r="C66" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="E66" s="23" t="s">
+      <c r="F66" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="G66" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="H66" s="10" t="s">
         <v>501</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>502</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="1" t="s">
-        <v>251</v>
+        <v>51</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>193</v>
+        <v>502</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>503</v>
@@ -5720,76 +5785,76 @@
       <c r="E67" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="12" t="s">
+      <c r="F67" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="G67" s="10" t="s">
         <v>508</v>
       </c>
+      <c r="H67" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="I67" s="10"/>
       <c r="J67" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="I68" s="10"/>
-      <c r="J68" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="M68" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="69" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="12" t="s">
         <v>519</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -5803,178 +5868,178 @@
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>202</v>
+        <v>523</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B70" s="7"/>
       <c r="C70" s="7" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E70" s="11" t="s">
         <v>525</v>
       </c>
+      <c r="E70" s="10" t="s">
+        <v>526</v>
+      </c>
       <c r="F70" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="1" t="s">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>357</v>
+        <v>209</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B71" s="7"/>
-      <c r="C71" s="7" t="n">
-        <v>1958</v>
+      <c r="C71" s="7" t="s">
+        <v>517</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="E71" s="9" t="s">
         <v>531</v>
       </c>
+      <c r="E71" s="11" t="s">
+        <v>532</v>
+      </c>
       <c r="F71" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="H71" s="12" t="s">
         <v>534</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>535</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="1" t="s">
-        <v>97</v>
+        <v>435</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="M71" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="E72" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="F72" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="G72" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="H72" s="12" t="s">
         <v>541</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>542</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
-        <v>277</v>
+        <v>97</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="M72" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="M72" s="14" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
         <v>1959</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="1" t="s">
-        <v>549</v>
+        <v>284</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="7" t="n">
-        <v>1960</v>
+      <c r="C74" s="7" t="s">
+        <v>544</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="10" t="s">
         <v>552</v>
       </c>
       <c r="F74" s="7" t="s">
@@ -5983,7 +6048,7 @@
       <c r="G74" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="10" t="s">
         <v>555</v>
       </c>
       <c r="I74" s="10"/>
@@ -5991,95 +6056,95 @@
         <v>556</v>
       </c>
       <c r="K74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="L74" s="2" t="s">
+    </row>
+    <row r="75" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D75" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="M74" s="14" t="s">
+      <c r="E75" s="24" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
+      <c r="F75" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="I75" s="10"/>
+      <c r="J75" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
         <v>1960</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C76" s="1" t="n">
         <v>1960</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="K75" s="2" t="s">
+      <c r="D76" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="H76" s="10" t="s">
+      <c r="L76" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="I76" s="10"/>
-      <c r="J76" s="1" t="s">
+      <c r="M76" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="77" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="B77" s="7"/>
-      <c r="C77" s="7" t="n">
-        <v>1961</v>
+      <c r="C77" s="7" t="s">
+        <v>575</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>576</v>
@@ -6087,113 +6152,113 @@
       <c r="E77" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="12" t="s">
+      <c r="F77" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="I77" s="12" t="s">
+      <c r="G77" s="10" t="s">
         <v>579</v>
       </c>
+      <c r="H77" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="I77" s="10"/>
       <c r="J77" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="F78" s="7"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L77" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>583</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="I78" s="10"/>
-      <c r="J78" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="1" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>593</v>
+        <v>225</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="7" t="n">
-        <v>1962</v>
+      <c r="C80" s="7" t="s">
+        <v>588</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E80" s="11" t="s">
         <v>596</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -6202,215 +6267,215 @@
       <c r="G80" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="10" t="s">
         <v>599</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L80" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="L80" s="2" t="s">
+      <c r="M80" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="M80" s="2" t="s">
+    </row>
+    <row r="81" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D81" s="8" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7" t="s">
+      <c r="E81" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="F81" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="G81" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="H81" s="12" t="s">
         <v>606</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>608</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K81" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="M81" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="82" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="E82" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="F82" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="G82" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="H82" s="10" t="s">
         <v>615</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>616</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>114</v>
+        <v>616</v>
       </c>
       <c r="L82" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="M82" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="83" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="E83" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="F83" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="G83" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="H83" s="10" t="s">
         <v>623</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>624</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>218</v>
+        <v>624</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="E84" s="10" t="s">
         <v>627</v>
       </c>
+      <c r="E84" s="12" t="s">
+        <v>628</v>
+      </c>
       <c r="F84" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>609</v>
+        <v>42</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>631</v>
+        <v>225</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="E85" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="F85" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>637</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>638</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>306</v>
+        <v>616</v>
       </c>
       <c r="L85" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="M85" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="M85" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="86" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="B86" s="7"/>
-      <c r="C86" s="7" t="n">
-        <v>1966</v>
+      <c r="C86" s="7" t="s">
+        <v>640</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>641</v>
@@ -6424,146 +6489,146 @@
       <c r="G86" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="H86" s="10" t="s">
         <v>645</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L86" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L86" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="M86" s="2" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D87" s="8" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7" t="s">
+      <c r="E87" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="F87" s="7" t="s">
         <v>650</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="G87" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="H87" s="12" t="s">
         <v>652</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>654</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M87" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="K87" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="88" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E88" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="F88" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="G88" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="H88" s="10" t="s">
         <v>661</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>662</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>663</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>51</v>
+        <v>662</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>53</v>
+        <v>663</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>670</v>
+        <v>53</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="10" t="s">
         <v>673</v>
       </c>
       <c r="F90" s="7" t="s">
@@ -6577,10 +6642,10 @@
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>677</v>
@@ -6594,8 +6659,8 @@
         <v>1968</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="n">
-        <v>1968</v>
+      <c r="C91" s="7" t="s">
+        <v>665</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>679</v>
@@ -6609,35 +6674,35 @@
       <c r="G91" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="H91" s="12" t="s">
+      <c r="H91" s="10" t="s">
         <v>683</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>277</v>
+        <v>51</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B92" s="7"/>
-      <c r="C92" s="7" t="s">
-        <v>685</v>
+      <c r="C92" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="12" t="s">
         <v>687</v>
       </c>
       <c r="F92" s="7" t="s">
@@ -6646,26 +6711,26 @@
       <c r="G92" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="H92" s="10" t="s">
+      <c r="H92" s="12" t="s">
         <v>690</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>495</v>
+        <v>79</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>53</v>
+        <v>654</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
@@ -6688,67 +6753,67 @@
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>698</v>
+        <v>51</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>114</v>
+        <v>502</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="E94" s="10" t="s">
         <v>701</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="F94" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="H94" s="10" t="s">
         <v>704</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>705</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>609</v>
+        <v>114</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>516</v>
+        <v>53</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="D95" s="26" t="s">
+      <c r="D95" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="9" t="s">
         <v>709</v>
       </c>
       <c r="F95" s="7" t="s">
@@ -6762,95 +6827,95 @@
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>42</v>
+        <v>616</v>
       </c>
       <c r="L95" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="M95" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="M95" s="14" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="96" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D96" s="26" t="s">
         <v>715</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="E96" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="F96" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="G96" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="G96" s="10" t="s">
+      <c r="H96" s="10" t="s">
         <v>719</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>720</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="M96" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="97" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E97" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="F97" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="G97" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="H97" s="10" t="s">
         <v>727</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>728</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>729</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>51</v>
+        <v>728</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>114</v>
+        <v>502</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>53</v>
+        <v>729</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
@@ -6859,7 +6924,7 @@
       <c r="D98" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="12" t="s">
         <v>733</v>
       </c>
       <c r="F98" s="7" t="s">
@@ -6873,25 +6938,25 @@
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>306</v>
+        <v>114</v>
       </c>
       <c r="L98" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M98" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="M98" s="14" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="99" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>739</v>
@@ -6910,50 +6975,50 @@
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>444</v>
+        <v>313</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="M99" s="2" t="s">
+      <c r="M99" s="14" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="D100" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="E100" s="10" t="s">
         <v>747</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="F100" s="7" t="s">
         <v>748</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="G100" s="10" t="s">
         <v>749</v>
       </c>
-      <c r="G100" s="10" t="s">
+      <c r="H100" s="10" t="s">
         <v>750</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>751</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>631</v>
+        <v>751</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>752</v>
@@ -6965,49 +7030,49 @@
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>495</v>
+        <v>616</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>53</v>
+        <v>638</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E102" s="12" t="s">
         <v>761</v>
       </c>
       <c r="F102" s="7" t="s">
@@ -7021,10 +7086,10 @@
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>721</v>
+        <v>51</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>53</v>
@@ -7033,9 +7098,9 @@
         <v>765</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
@@ -7058,10 +7123,10 @@
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
-        <v>161</v>
+        <v>728</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>32</v>
+        <v>502</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>53</v>
@@ -7070,9 +7135,9 @@
         <v>772</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
@@ -7081,7 +7146,7 @@
       <c r="D104" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="10" t="s">
         <v>775</v>
       </c>
       <c r="F104" s="7" t="s">
@@ -7095,10 +7160,10 @@
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>495</v>
+        <v>32</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>53</v>
@@ -7107,9 +7172,9 @@
         <v>779</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
@@ -7118,7 +7183,7 @@
       <c r="D105" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="12" t="s">
         <v>782</v>
       </c>
       <c r="F105" s="7" t="s">
@@ -7132,53 +7197,90 @@
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="1" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>42</v>
+        <v>502</v>
       </c>
       <c r="L105" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M105" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="M105" s="2" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="106" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D106" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="D106" s="26" t="s">
+      <c r="E106" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="F106" s="7" t="s">
         <v>790</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="G106" s="10" t="s">
         <v>791</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="H106" s="10" t="s">
         <v>792</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>793</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="1" t="s">
-        <v>794</v>
+        <v>41</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L106" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="D107" s="26" t="s">
         <v>796</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="I107" s="10"/>
+      <c r="J107" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -7196,60 +7298,62 @@
     <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
     <hyperlink ref="H14" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
-    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
-    <hyperlink ref="H20" r:id="rId11" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
-    <hyperlink ref="E23" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H23" r:id="rId13" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
-    <hyperlink ref="H24" r:id="rId14" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
-    <hyperlink ref="E26" r:id="rId15" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H29" r:id="rId16" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
-    <hyperlink ref="E30" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
-    <hyperlink ref="E31" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H32" r:id="rId19" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
-    <hyperlink ref="I32" r:id="rId20" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
-    <hyperlink ref="H33" r:id="rId21" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
-    <hyperlink ref="E37" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H37" r:id="rId23" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
-    <hyperlink ref="E39" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
-    <hyperlink ref="E40" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H41" r:id="rId26" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
-    <hyperlink ref="E43" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H43" r:id="rId28" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
-    <hyperlink ref="H44" r:id="rId30" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E46" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H49" r:id="rId33" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
-    <hyperlink ref="E56" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E58" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
-    <hyperlink ref="H58" r:id="rId36" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
-    <hyperlink ref="E60" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E63" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E65" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="E66" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
-    <hyperlink ref="E67" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
-    <hyperlink ref="H67" r:id="rId42" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
-    <hyperlink ref="I67" r:id="rId43" display="https://www.laphilo.fr/photo/tarassov.webp"/>
-    <hyperlink ref="E68" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
-    <hyperlink ref="E71" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H71" r:id="rId46" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
-    <hyperlink ref="H74" r:id="rId47" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
-    <hyperlink ref="H75" r:id="rId48" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
-    <hyperlink ref="H77" r:id="rId49" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
-    <hyperlink ref="I77" r:id="rId50" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
-    <hyperlink ref="E80" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H80" r:id="rId52" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
-    <hyperlink ref="E81" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
-    <hyperlink ref="E83" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="H86" r:id="rId55" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E90" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H91" r:id="rId57" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E94" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E95" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E97" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId61" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E101" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E104" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E18" r:id="rId10" display="https://en.wikipedia.org/wiki/Alison_Jaggar"/>
+    <hyperlink ref="H18" r:id="rId11" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
+    <hyperlink ref="E19" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
+    <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
+    <hyperlink ref="E24" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H24" r:id="rId15" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
+    <hyperlink ref="H25" r:id="rId16" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
+    <hyperlink ref="E27" r:id="rId17" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H30" r:id="rId18" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
+    <hyperlink ref="E31" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
+    <hyperlink ref="E32" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H33" r:id="rId21" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
+    <hyperlink ref="I33" r:id="rId22" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
+    <hyperlink ref="H34" r:id="rId23" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
+    <hyperlink ref="E38" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H38" r:id="rId25" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
+    <hyperlink ref="E40" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
+    <hyperlink ref="E41" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H42" r:id="rId28" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
+    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H44" r:id="rId30" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
+    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
+    <hyperlink ref="H45" r:id="rId32" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
+    <hyperlink ref="E46" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E47" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H50" r:id="rId35" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
+    <hyperlink ref="E57" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E59" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
+    <hyperlink ref="H59" r:id="rId38" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
+    <hyperlink ref="E61" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E64" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E66" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="E67" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
+    <hyperlink ref="E68" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
+    <hyperlink ref="H68" r:id="rId44" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
+    <hyperlink ref="I68" r:id="rId45" display="https://www.laphilo.fr/photo/tarassov.webp"/>
+    <hyperlink ref="E69" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
+    <hyperlink ref="E72" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H72" r:id="rId48" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
+    <hyperlink ref="H75" r:id="rId49" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
+    <hyperlink ref="H76" r:id="rId50" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
+    <hyperlink ref="H78" r:id="rId51" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
+    <hyperlink ref="I78" r:id="rId52" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
+    <hyperlink ref="E81" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H81" r:id="rId54" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
+    <hyperlink ref="E82" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
+    <hyperlink ref="E84" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="H87" r:id="rId57" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
+    <hyperlink ref="E91" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H92" r:id="rId59" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E95" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E96" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E98" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E101" r:id="rId63" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E102" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E105" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="794">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -545,48 +545,8 @@
     <t xml:space="preserve">Alison JAGGAR</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;p&gt;&lt;a href="</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://en.wikipedia.org/wiki/Alison_Jaggar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">"  title=" Wikipedia"&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">&lt;a href="https://journals.openedition.org/lectures/15257?lang=es"  title="alison jaggar ; gender and global justice par openedition "&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; 
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Alison_Jaggar"  title=" Wikipedia"&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href="https://journals.openedition.org/lectures/15257?lang=es"  title="alison jaggar ; gender and global justice par openedition "&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; 
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Ht4tG96X7Gg</t>
@@ -2310,34 +2270,6 @@
     <t xml:space="preserve">philosophe sud-africain qui a formalisé l'antinatalisme dans la pensée contemporaine.</t>
   </si>
   <si>
-    <t xml:space="preserve">1967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franck FISCHBACH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franço-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QetmJoRDpY0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franck Fischbach, L’aliénation : un concept encore utile aujourd’hui ? par Departement Philosophie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/fischbach-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Française</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marxisme ; Théorie Critique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe franco-suisse spécialiste de la philosophie sociale.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1968</t>
   </si>
   <si>
@@ -2753,9 +2685,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/taiwo-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nigériane</t>
   </si>
   <si>
     <t xml:space="preserve">Tiers-mondisme ; Pan-africanisme</t>
@@ -2771,7 +2700,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2881,30 +2810,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -2998,7 +2903,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3071,18 +2976,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3095,7 +2988,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3103,7 +2996,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3359,7 +3252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3981,7 +3874,7 @@
       <c r="G18" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="12" t="s">
         <v>146</v>
       </c>
       <c r="I18" s="10"/>
@@ -3994,7 +3887,7 @@
       <c r="L18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="14" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4009,7 +3902,7 @@
       <c r="D19" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="17" t="s">
         <v>151</v>
       </c>
       <c r="F19" s="7" t="s">
@@ -4524,10 +4417,10 @@
       <c r="C33" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="19" t="s">
         <v>255</v>
       </c>
       <c r="F33" s="7"/>
@@ -4965,10 +4858,10 @@
       <c r="C45" s="7" t="n">
         <v>1950</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="20" t="s">
         <v>345</v>
       </c>
       <c r="F45" s="7" t="s">
@@ -5153,7 +5046,7 @@
       <c r="D50" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="21" t="s">
         <v>381</v>
       </c>
       <c r="F50" s="7" t="s">
@@ -5412,7 +5305,7 @@
       <c r="D57" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E57" s="25" t="s">
+      <c r="E57" s="22" t="s">
         <v>431</v>
       </c>
       <c r="F57" s="7" t="s">
@@ -5449,7 +5342,7 @@
       <c r="D58" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="21" t="s">
         <v>439</v>
       </c>
       <c r="F58" s="7" t="s">
@@ -5483,10 +5376,10 @@
       <c r="C59" s="7" t="n">
         <v>1954</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E59" s="20" t="s">
         <v>447</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -5779,10 +5672,10 @@
       <c r="C67" s="7" t="n">
         <v>1958</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="E67" s="23" t="s">
+      <c r="E67" s="20" t="s">
         <v>506</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -5816,10 +5709,10 @@
       <c r="C68" s="7" t="n">
         <v>1958</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="E68" s="23" t="s">
+      <c r="E68" s="20" t="s">
         <v>513</v>
       </c>
       <c r="F68" s="7"/>
@@ -6076,7 +5969,7 @@
       <c r="D75" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="21" t="s">
         <v>559</v>
       </c>
       <c r="F75" s="7" t="s">
@@ -6543,10 +6436,8 @@
         <v>655</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="141.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
-        <v>1967</v>
-      </c>
+    <row r="88" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
         <v>656</v>
@@ -6568,90 +6459,90 @@
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="89" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B89" s="7"/>
       <c r="C89" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="G89" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="H89" s="10" t="s">
         <v>667</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>669</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>670</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>88</v>
+        <v>259</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>53</v>
+        <v>668</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D90" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="F90" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="G90" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="H90" s="10" t="s">
         <v>674</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="H90" s="10" t="s">
-        <v>676</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6659,226 +6550,226 @@
         <v>1968</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="s">
-        <v>665</v>
+      <c r="C91" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D91" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="F91" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="G91" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="H91" s="12" t="s">
         <v>681</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>683</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="L91" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="7" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D92" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="M91" s="2" t="s">
+      <c r="E92" s="10" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7" t="n">
-        <v>1968</v>
-      </c>
-      <c r="D92" s="8" t="s">
+      <c r="F92" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="G92" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="H92" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>689</v>
-      </c>
-      <c r="H92" s="12" t="s">
-        <v>690</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
-        <v>284</v>
+        <v>51</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>654</v>
+        <v>53</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="F93" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="G93" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="H93" s="10" t="s">
         <v>695</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>697</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>51</v>
+        <v>696</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>502</v>
+        <v>114</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="E94" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="F94" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="H94" s="10" t="s">
         <v>703</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>704</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>114</v>
+        <v>616</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>53</v>
+        <v>523</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="D95" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="E95" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="F95" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="G95" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="H95" s="10" t="s">
         <v>710</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>711</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>712</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>616</v>
+        <v>42</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>711</v>
+      </c>
+      <c r="M95" s="14" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="D96" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="D96" s="26" t="s">
+      <c r="E96" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="F96" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="G96" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="G96" s="10" t="s">
+      <c r="H96" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>719</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>466</v>
+        <v>719</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>42</v>
+        <v>502</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="M96" s="14" t="s">
+      <c r="M96" s="2" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
@@ -6887,7 +6778,7 @@
       <c r="D97" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="12" t="s">
         <v>724</v>
       </c>
       <c r="F97" s="7" t="s">
@@ -6901,127 +6792,127 @@
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M97" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="K97" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="F98" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="G98" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="H98" s="10" t="s">
         <v>734</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>735</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>736</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>114</v>
+        <v>313</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>735</v>
+      </c>
+      <c r="M98" s="14" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="E99" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="F99" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="G99" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="H99" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>743</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>313</v>
+        <v>451</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="M99" s="14" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>742</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="D100" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="E100" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="F100" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="G100" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="G100" s="10" t="s">
+      <c r="H100" s="10" t="s">
         <v>749</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>750</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>451</v>
+        <v>616</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>751</v>
+        <v>638</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7030,63 +6921,63 @@
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="G101" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="E101" s="12" t="s">
+      <c r="H101" s="10" t="s">
         <v>755</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>757</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>758</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>616</v>
+        <v>502</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>638</v>
+        <v>53</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D102" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="F102" s="7" t="s">
         <v>760</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="G102" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="H102" s="10" t="s">
         <v>762</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>763</v>
-      </c>
-      <c r="H102" s="10" t="s">
-        <v>764</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>51</v>
+        <v>719</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>502</v>
@@ -7095,194 +6986,158 @@
         <v>53</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="E103" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="F103" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="G103" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="H103" s="10" t="s">
         <v>769</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>770</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>771</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
-        <v>728</v>
+        <v>168</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>502</v>
+        <v>32</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="E104" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="F104" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="G104" s="10" t="s">
         <v>775</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="H104" s="10" t="s">
         <v>776</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>777</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>778</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>32</v>
+        <v>502</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E105" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="F105" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="G105" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="H105" s="10" t="s">
         <v>783</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>784</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>785</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="1" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>502</v>
+        <v>42</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>53</v>
+        <v>784</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="n">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="D106" s="23" t="s">
         <v>787</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="E106" s="10" t="s">
         <v>788</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="F106" s="7" t="s">
         <v>789</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="G106" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="H106" s="10" t="s">
         <v>791</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>792</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L106" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="M106" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="M106" s="2" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7" t="s">
-        <v>795</v>
-      </c>
-      <c r="D107" s="26" t="s">
-        <v>796</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>797</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>799</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>800</v>
-      </c>
-      <c r="I107" s="10"/>
-      <c r="J107" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="M107" s="2" t="s">
-        <v>803</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -7298,7 +7153,7 @@
     <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
     <hyperlink ref="H14" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
-    <hyperlink ref="E18" r:id="rId10" display="https://en.wikipedia.org/wiki/Alison_Jaggar"/>
+    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alison_Jaggar&quot;  title=&quot; Wikipedia&quot;&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href=&quot;https://journals.openedition.org/lectures/15257?lang=es&quot;  title=&quot;alison jaggar ; gender and global justice par openedition &quot;&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; &#10;"/>
     <hyperlink ref="H18" r:id="rId11" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
     <hyperlink ref="E19" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
     <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
@@ -7346,14 +7201,14 @@
     <hyperlink ref="E82" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
     <hyperlink ref="E84" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
     <hyperlink ref="H87" r:id="rId57" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E91" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H92" r:id="rId59" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E95" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E96" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E98" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E101" r:id="rId63" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E102" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E105" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E90" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H91" r:id="rId59" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E94" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E95" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E97" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E100" r:id="rId63" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E101" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E104" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -6437,7 +6437,9 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7"/>
+      <c r="A88" s="7" t="n">
+        <v>1968</v>
+      </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
         <v>656</v>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="795">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -2276,7 +2276,34 @@
     <t xml:space="preserve">Jennifer SAUL</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Jennifer_Saul"  style="color:#6A142A"  title=" Wikipedia"&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe britanique spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href="https://www.youtube.com/watch?v=2_FqrHs9S-s" style="color:#88A1E9" title="Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy"&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre "Lying, Misleading, and What Is Said" aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  "Feminism: Issues &amp; Arguments", elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le "Women in Philosophy Task Force" au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href="https://www.youtube.com/watch?v=QDcuCIqCWdQ&amp;t=13s" style="color:#88A1E9" title=" Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy"&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; </t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Jennifer_Saul" title=" Wikipedia"&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe américaine  spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href="https://www.youtube.com/watch?v=2_FqrHs9S-s" title="Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy"&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre "Lying, Misleading, and What Is Said" aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  "Feminism: Issues &amp; Arguments", elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le "Women in Philosophy Task Force" au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://www.youtube.com/watch?v=QDcuCIqCWdQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" s title=" Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy"&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">QZUDokfLdAU</t>
@@ -2288,7 +2315,13 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/saul-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">philosophe britannique connue pour ses travaux sur les biais implicites, le langage et le genre.</t>
+    <t xml:space="preserve">langage ; ethique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytique ; Féminisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe américaine connue pour ses travaux sur les biais implicites, le langage et le genre.</t>
   </si>
   <si>
     <t xml:space="preserve">Timothy MORTON</t>
@@ -2510,9 +2543,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/jenkins-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytique ; Féminisme</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe canadienne connue pour ses travaux sur la métaphysique, l’épistémologie et la philosophie de l’amour. </t>
@@ -2700,7 +2730,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2825,6 +2855,13 @@
       <sz val="9"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -6399,7 +6436,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="224.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
         <v>1966</v>
       </c>
@@ -6436,7 +6473,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="196.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
         <v>1968</v>
       </c>
@@ -6464,13 +6501,13 @@
         <v>51</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>88</v>
+        <v>662</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>53</v>
+        <v>663</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6482,19 +6519,19 @@
         <v>656</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
@@ -6504,10 +6541,10 @@
         <v>259</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6519,19 +6556,19 @@
         <v>656</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
@@ -6541,10 +6578,10 @@
         <v>327</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6556,19 +6593,19 @@
         <v>1968</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
@@ -6581,7 +6618,7 @@
         <v>654</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6590,22 +6627,22 @@
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
@@ -6618,7 +6655,7 @@
         <v>53</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6627,26 +6664,26 @@
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>114</v>
@@ -6655,7 +6692,7 @@
         <v>53</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6664,22 +6701,22 @@
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
@@ -6692,7 +6729,7 @@
         <v>523</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6701,22 +6738,22 @@
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
@@ -6726,10 +6763,10 @@
         <v>42</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="M95" s="14" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6738,35 +6775,35 @@
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>502</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6775,22 +6812,22 @@
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
@@ -6803,7 +6840,7 @@
         <v>53</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6812,22 +6849,22 @@
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
@@ -6837,10 +6874,10 @@
         <v>313</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>735</v>
+        <v>663</v>
       </c>
       <c r="M98" s="14" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6849,22 +6886,22 @@
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
@@ -6874,10 +6911,10 @@
         <v>451</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6886,22 +6923,22 @@
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
@@ -6914,7 +6951,7 @@
         <v>638</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6923,22 +6960,22 @@
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
@@ -6951,7 +6988,7 @@
         <v>53</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6960,26 +6997,26 @@
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>502</v>
@@ -6988,7 +7025,7 @@
         <v>53</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6997,22 +7034,22 @@
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
@@ -7025,7 +7062,7 @@
         <v>53</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7034,22 +7071,22 @@
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
@@ -7062,7 +7099,7 @@
         <v>53</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7071,22 +7108,22 @@
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="1" t="s">
@@ -7096,10 +7133,10 @@
         <v>42</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7108,22 +7145,22 @@
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="1" t="s">
@@ -7133,10 +7170,10 @@
         <v>42</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7203,14 +7240,15 @@
     <hyperlink ref="E82" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
     <hyperlink ref="E84" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
     <hyperlink ref="H87" r:id="rId57" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E90" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H91" r:id="rId59" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E94" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E95" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E97" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId63" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E101" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E104" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E88" r:id="rId58" display="https://www.youtube.com/watch?v=QDcuCIqCWdQ"/>
+    <hyperlink ref="E90" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H91" r:id="rId60" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E94" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E95" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E97" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E100" r:id="rId64" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E101" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E104" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="24" min="1" max="1"/>
@@ -704,6 +704,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N3" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="157.5" customHeight="1" s="26">
       <c r="A4" s="31" t="n">
@@ -1107,6 +1112,11 @@
           <t>psychologue et philosophe américaine, fondatrice de l’éthique de la sollicitude  avec "Une voix différente".</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="228.35" customHeight="1" s="26">
       <c r="A11" s="31" t="n">
@@ -1165,6 +1175,11 @@
           <t>philosophe serbe connu pour sa critique des conceptions réductionnistes de l'esprit.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="185.8" customHeight="1" s="26">
       <c r="A12" s="31" t="n">
@@ -1280,6 +1295,11 @@
           <t>philosophe américain connu pour ses contributions en logique modale.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="312.65" customHeight="1" s="26">
       <c r="A14" s="31" t="n">
@@ -2020,6 +2040,11 @@
           <t>philosophe américain qui traite des problèmes d'identité, du concept de soi et de l'autre.</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="137.25" customHeight="1" s="26">
       <c r="A27" s="31" t="n">
@@ -2079,6 +2104,11 @@
           <t>philosophe australien défenseur de l'Utilitarisme et prônant l'Antispécisme.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="228.75" customHeight="1" s="26">
       <c r="A28" s="31" t="n">
@@ -2136,6 +2166,11 @@
           <t>philosophe américaine s'inscrivant dans la lignée de la Théorie Critique.</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="227.25" customHeight="1" s="26">
       <c r="A29" s="31" t="n">
@@ -2193,6 +2228,11 @@
           <t>philosophe américaine préoccupée par des questions de justice sociale et de bien-être humain.</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="147" customHeight="1" s="26">
       <c r="A30" s="31" t="n">
@@ -2757,6 +2797,11 @@
           <t>philosophe américain travaillant sur l'esthétique dans le renouveau du pragmatisme.</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="189" customHeight="1" s="26">
       <c r="A40" s="31" t="n">
@@ -2815,6 +2860,11 @@
           <t>philosophe américaine élue humaniste de l'année en 2011.</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="147.75" customHeight="1" s="26">
       <c r="A41" s="31" t="n">
@@ -3043,6 +3093,11 @@
           <t>Philosophe américaine d’origine turque figure de la théorie critique contemporaine.</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="147.75" customHeight="1" s="26">
       <c r="A45" s="31" t="n">
@@ -3098,6 +3153,11 @@
           <t>philosophe essayiste et théoricien russo-américain spécialiste de la culture russo-américaine.</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="137.25" customHeight="1" s="26">
       <c r="A46" s="31" t="n">
@@ -3271,6 +3331,11 @@
           <t>philosophe américaine représentante de la French Theory aux États-Unis.</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="216.75" customHeight="1" s="26">
       <c r="A49" s="31" t="n">
@@ -3555,6 +3620,11 @@
       <c r="M53" s="25" t="inlineStr">
         <is>
           <t>philosophe américain connu pour sa critique du libéralisme moderne.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>
@@ -4080,6 +4150,11 @@
           <t>philosophe américaine faisant le lien avec la philosophie morale des Lumières.</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="157.5" customHeight="1" s="26">
       <c r="A63" s="31" t="n">
@@ -4197,6 +4272,11 @@
           <t>philosophe américaine reconnue pour ses travaux sur le genre et la théorie Queer.</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="231.75" customHeight="1" s="26">
       <c r="A65" s="31" t="n">
@@ -5095,6 +5175,11 @@
       <c r="M80" s="25" t="inlineStr">
         <is>
           <t>philosophe afro-américain considéré comme le père de la phénoménologie postcoloniale.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3086,7 +3086,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N1048576"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3263,6 +3263,11 @@
       <c r="M5" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3476,8 +3481,10 @@
       <c r="M10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N10" s="0" t="s">
-        <v>83</v>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
         <is>
@@ -3821,6 +3828,11 @@
       <c r="M18" s="14" t="s">
         <v>150</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3905,6 +3917,11 @@
       <c r="M20" s="2" t="s">
         <v>164</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3989,6 +4006,11 @@
       <c r="M22" s="2" t="s">
         <v>182</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4247,8 +4269,10 @@
       <c r="M28" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="N28" s="0" t="s">
-        <v>83</v>
+      <c r="N28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O28" s="0" t="inlineStr">
         <is>
@@ -4292,8 +4316,10 @@
       <c r="M29" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="N29" s="0" t="s">
-        <v>83</v>
+      <c r="N29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
@@ -4420,6 +4446,11 @@
       </c>
       <c r="M32" s="2" t="s">
         <v>255</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4586,6 +4617,11 @@
       <c r="M36" s="2" t="s">
         <v>287</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4757,8 +4793,10 @@
       <c r="M40" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="N40" s="0" t="s">
-        <v>83</v>
+      <c r="N40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
@@ -4928,8 +4966,10 @@
       <c r="M44" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="N44" s="0" t="s">
-        <v>83</v>
+      <c r="N44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
@@ -5018,6 +5058,11 @@
       <c r="M46" s="2" t="s">
         <v>360</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">inde</t>
@@ -5060,6 +5105,11 @@
       <c r="M47" s="2" t="s">
         <v>367</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -5102,8 +5152,10 @@
       <c r="M48" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="N48" s="0" t="s">
-        <v>83</v>
+      <c r="N48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
@@ -5231,6 +5283,11 @@
       <c r="M51" s="2" t="s">
         <v>395</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -5706,8 +5763,10 @@
       <c r="M62" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="N62" s="0" t="s">
-        <v>83</v>
+      <c r="N62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
@@ -5793,8 +5852,10 @@
       <c r="M64" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="N64" s="0" t="s">
-        <v>83</v>
+      <c r="N64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
+        </is>
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
@@ -6175,6 +6236,11 @@
       <c r="M73" s="2" t="s">
         <v>552</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6263,6 +6329,11 @@
       </c>
       <c r="M75" s="14" t="s">
         <v>568</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6387,6 +6458,11 @@
       <c r="M78" s="2" t="s">
         <v>589</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6810,6 +6886,11 @@
       <c r="M88" s="2" t="s">
         <v>666</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7020,6 +7101,11 @@
       <c r="M93" s="2" t="s">
         <v>701</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7230,6 +7316,11 @@
       <c r="M98" s="14" t="s">
         <v>739</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7358,8 +7449,15 @@
       <c r="L101" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M101" s="2" t="s">
-        <v>759</v>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe américain·e non binaire travaillant sur les questions de genre et les questions LGBT.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme;non-binaire</t>
+        </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -7445,6 +7543,11 @@
       <c r="M103" s="2" t="s">
         <v>773</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7487,6 +7590,11 @@
       <c r="M104" s="2" t="s">
         <v>780</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -7580,6 +7688,59 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7">
+        <v>1944</v>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1944</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angela DAVIS</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Angela_Davis"  title=" Wikipedia"&gt;Angela DAVIS&lt;/a&gt; (née en 1944) est une philosophe, professeure et militante américaine. Née à Birmingham, en Alabama, dans un quartier surnommé « Dynamite Hill » en raison des attentats racistes qui le frappaient, elle étudia la philosophie aux États-Unis puis en Allemagne, avec Theodor Adorno, et fut l'élève d'Herbert Marcuse.&lt;/p&gt; &lt;p&gt;Membre du Parti communiste et proche des Black Panthers, elle fut accusée en 1970 de complicité dans une prise d'otages sanglante, à cause d'armes achetées à son nom. Inscrite sur la liste des personnes les plus recherchées par le FBI, elle fut arrêtée puis emprisonnée seize mois. Une immense campagne internationale, « Free Angela », se mobilisa pour elle, et elle fut acquittée en 1972.&lt;/p&gt; &lt;p&gt;Son parcours philosophique est marqué par l'École de Francfort, dont elle retient l'idée qu'une théorie critique doit viser la transformation de la société. Elle s'est aussi intéressée à la musique populaire noire, en particulier au blues de chanteuses comme Billie Holiday, qu'elle interprète comme une forme de conscience sociale et féministe. Elle est aujourd'hui une référence mondiale pour les mouvements antiracistes et féministes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Femmes, race et classe&lt;/em&gt; (1981), elle analyse comment l'esclavage, le racisme et le capitalisme ont façonné la condition des femmes noires. Elle est devenue l'une des grandes voix du mouvement pour l'abolition des prisons, qu'elle considère comme la continuation de l'esclavage et de la ségrégation. Professeure à l'université de Californie, elle incarne l'union entre la réflexion philosophique et l'engagement politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Américaine</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme ; Féminisme</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et militante afro-américaine, figure de la lutte contre le racisme, le sexisme et le système carcéral.</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme ; sud</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P107">
+        <v>2</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -7743,6 +7743,146 @@
         <v>2</v>
       </c>
     </row>
+    <row r="108" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="7">
+        <v>1933</v>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1933</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seyyed Hossein NASR</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Seyyed_Hossein_Nasr"  title=" Wikipedia"&gt;Seyyed Hossein NASR&lt;/a&gt; est un philosophe iranien né à Téhéran en 1933. Envoyé aux États-Unis à douze ans, il étudie la physique au MIT, puis l'histoire des sciences à Harvard, où il obtient son doctorat en 1958. Il rentre alors en Iran, enseigne à l'université de Téhéran et fonde en 1974 l'Académie impériale iranienne de philosophie. La révolution de 1979 le contraint à l'exil : il enseigne depuis 1984 à l'université George Washington.&lt;/p&gt; &lt;p&gt;Dès ses études, il est déçu par une science moderne qui ne dit rien du sens des choses, et découvre les auteurs de l'école dite « traditionaliste », René Guénon et Frithjof Schuon. Avec eux, il affirme qu'il existe une sagesse éternelle, la &lt;em&gt;philosophia perennis&lt;/em&gt;, présente au cœur de toutes les grandes religions, et que le monde moderne l'a oubliée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Connaissance et le Sacré&lt;/em&gt;, issu de conférences prononcées en 1981, il défend l'idée d'une « science sacrée » : connaître vraiment, c'est relier chaque chose à son origine divine. Il a consacré de nombreux ouvrages aux sciences et à la philosophie du monde musulman, d'Avicenne à Molla Sadra, ainsi qu'au soufisme, qu'il pratique lui-même. Il a aussi dirigé une traduction commentée du Coran en anglais, &lt;em&gt;The Study Quran&lt;/em&gt; (2015), qui rassemble les interprétations des différentes écoles.&lt;/p&gt; &lt;p&gt;Dès 1968, dans &lt;em&gt;L'Homme et la Nature&lt;/em&gt;, il soutient que la crise écologique est d'abord une crise spirituelle : en cessant de voir la nature comme sacrée, l'homme moderne s'est cru autorisé à la dominer sans limite. Il est l'un des premiers penseurs à avoir posé ce diagnostic.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perse</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pérennialisme ; Soufisme</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe iranien, penseur de la science sacrée et de la tradition, professeur aux États-Unis.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7">
+        <v>1933</v>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1933</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdallah LAROUI</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdallah_Laroui"  title=" Wikipedia"&gt;Abdallah LAROUI&lt;/a&gt; est un historien, philosophe et romancier marocain né à Azemmour en 1933. Après des études à Rabat et à Paris, il enseigne l'histoire à l'université Mohammed V de Rabat pendant plus de trente ans. Il écrit en français et en arabe, et a traduit en arabe des textes de Rousseau et de Montesquieu. Il est aussi l'auteur d'une &lt;em&gt;Histoire du Maghreb&lt;/em&gt; (1970) et de plusieurs romans.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;L'Idéologie arabe contemporaine&lt;/em&gt; (1967), paraît l'année de la défaite arabe face à Israël et devient une référence. Il y décrit trois figures qui, depuis un siècle, répondent chacune à sa façon au défi de l'Occident : le clerc, qui cherche le salut dans le retour à la religion ; le politicien libéral, qui l'attend de la démocratie ; le technophile, qui ne croit qu'à la science et à l'industrie. Aucune, selon lui, ne pense vraiment la situation.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Crise des intellectuels arabes&lt;/em&gt; (1974), il oppose deux attitudes : le traditionalisme, qui cherche dans le passé des réponses toutes faites, et l'historicisme, qu'il défend. Être historiciste, c'est admettre que l'histoire a un sens, que la modernité née en Europe est un acquis de toute l'humanité, et qu'un peuple en retard doit en assimiler les principes : raison, liberté, État, sans croire pouvoir s'en dispenser. Le marxisme l'intéresse surtout comme le résumé de cette pensée moderne.&lt;/p&gt; &lt;p&gt;Il plaide ainsi pour une rupture nette avec l'héritage, là où son compatriote al-Jabri proposait de le relire. Il a poursuivi ce travail dans une série d'ouvrages en arabe, chacun consacré à un concept : l'idéologie, la liberté, l'État, l'histoire, la raison.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marocaine</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien et philosophe marocain, auteur de L'Idéologie arabe contemporaine.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="7">
+        <v>1945</v>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1945</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdolkarim SOROUSH</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdolkarim_Soroush"  title=" Wikipedia"&gt;Abdolkarim SOROUSH&lt;/a&gt;, nom de plume de Hossein Haj Faraj Dabbagh, est un philosophe iranien né à Téhéran en 1945. Pharmacien de formation, il étudie à Londres la chimie, puis l'histoire et la philosophie des sciences, où il découvre Karl Popper. Rentré en Iran à la révolution de 1979, il siège au conseil chargé de réorganiser les universités, qu'il quitte en 1983. Il devient dans les années 1990 la principale voix des intellectuels réformateurs.&lt;/p&gt; &lt;p&gt;Sa thèse la plus connue est exposée dans &lt;em&gt;La Contraction et l'expansion théoriques de la charia&lt;/em&gt; (1990). Il y distingue la religion elle-même, d'origine divine, et la connaissance que les hommes en ont. Cette connaissance est humaine, faillible et historique : elle dépend de tout ce que nous savons par ailleurs, en science, en histoire ou en philosophie, et change donc avec les époques. Personne ne peut dès lors prétendre détenir l'interprétation définitive, pas même le clergé.&lt;/p&gt; &lt;p&gt;Il en tire une critique du pouvoir religieux : faire de la religion une idéologie d'État, c'est la figer et la corrompre. Un gouvernement peut être à la fois religieux et démocratique, mais seulement s'il respecte la liberté de croire et les droits de l'homme. Il rejette ainsi le principe iranien du gouvernement du juriste-théologien.&lt;/p&gt; &lt;p&gt;Il a ensuite soutenu que la révélation porte la marque de la personnalité et de l'époque du Prophète. Grand lecteur du poète mystique Rumi, il a été agressé et empêché d'enseigner, puis a quitté l'Iran vers 2000 pour les universités américaines et européennes. Il a reçu le prix Érasme en 2004. Il partagea ce prix avec la sociologue marocaine Fatima Mernissi.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perse</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe iranien, penseur de la réforme religieuse et de la distinction entre religion et connaissance religieuse.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+    </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="809">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES CONTEMPORAINS (AUTRES) — Données source</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t xml:space="preserve">Traditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importance</t>
   </si>
   <si>
     <t xml:space="preserve">1926</t>
@@ -101,6 +107,9 @@
     <t xml:space="preserve">philosophe allemand théoricien de la civilisation moderne et de la démocratie libérale.</t>
   </si>
   <si>
+    <t xml:space="preserve">occident</t>
+  </si>
+  <si>
     <t xml:space="preserve">1930</t>
   </si>
   <si>
@@ -130,6 +139,9 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe belge et figure majeure du féminisme français des années 1970.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">femme</t>
   </si>
   <si>
     <t xml:space="preserve">1931</t>
@@ -164,38 +176,6 @@
     <t xml:space="preserve">philosophe canadien connu pour ses travaux sur l’identité, la modernité, la morale &amp; la reconnaissance.</t>
   </si>
   <si>
-    <t xml:space="preserve">1932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John SEARLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Searle"  title=" Wikipedia"&gt;John SEARLE&lt;/a&gt; est un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href="https://www.youtube.com/watch?v=pIbkpLfrD6A" title="
-La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse"&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du "naturalisme biologique" en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href="https://www.youtube.com/watch?v=EriAhi0mj7w" title=" Conscience et matière grise par TEDx Talks"&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href="https://www.youtube.com/watch?v=Bq2bfSzkTfU"  title="John Searle - Une personne peut-elle être une âme ? par Closer To Truth"&gt;biologiques réels&lt;/a&gt; , causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href="https://www.youtube.com/watch?v=P5DtwDr9YEc" title=" La Chambre chinoise par Ian et frank"&gt;Chambre Chinoise&lt;/a&gt; . Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href="https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf"  title=" La construction e la réalité sociale par nonmarchand"&gt;"La Construction de la Réalité Sociale"&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les "Faits bruts" qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des "Faits institutionnels" qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eqDgt12m26c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"John Searle: Notre condition partagée - la conscience" par TED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/searle-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Américaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epistemologie ; langage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe américain spécialiste de la philosophie du langage et de l'esprit.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1933</t>
   </si>
   <si>
@@ -224,6 +204,9 @@
     <t xml:space="preserve">philosophe indien connu pour son approche des "capabilités" qui mesure le développement.</t>
   </si>
   <si>
+    <t xml:space="preserve">inde</t>
+  </si>
+  <si>
     <t xml:space="preserve">Richard SWINBURNE</t>
   </si>
   <si>
@@ -270,6 +253,9 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/cgilligan-mini.webp</t>
   </si>
   <si>
+    <t xml:space="preserve">Américaine</t>
+  </si>
+  <si>
     <t xml:space="preserve">ethique</t>
   </si>
   <si>
@@ -279,7 +265,7 @@
     <t xml:space="preserve">psychologue et philosophe américaine, fondatrice de l’éthique de la sollicitude  avec "Une voix différente".</t>
   </si>
   <si>
-    <t xml:space="preserve">juive</t>
+    <t xml:space="preserve">juive;femme</t>
   </si>
   <si>
     <t xml:space="preserve">1937</t>
@@ -310,6 +296,9 @@
     <t xml:space="preserve">philosophe serbe connu pour sa critique des conceptions réductionnistes de l'esprit.</t>
   </si>
   <si>
+    <t xml:space="preserve">juive</t>
+  </si>
+  <si>
     <t xml:space="preserve">1938</t>
   </si>
   <si>
@@ -338,31 +327,7 @@
     <t xml:space="preserve">philosophe camerounais qui analyse les phénomènes entravant le développement du pays.</t>
   </si>
   <si>
-    <t xml:space="preserve">1940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saul KRIPKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saul_Kripke"  title=" Wikipedia"&gt;Saul KRIPKE&lt;/a&gt; est un philosophe américain de la tradition analytique connu pour ses apports décisifs en logique modale, en métaphysique et en philosophie du langage. Très jeune, il révolutionne la logique en introduisant la sémantique des mondes possibles, aujourd’hui appelée &lt;a href="https://www.youtube.com/watch?v=_sIgAdvhruU"title="Qui est Saul Kripke ? par Monsieur Phi"&gt;"cadres de Kripke"&lt;/a&gt; , qui permet de formaliser la modalité (le nécessaire et le possible) de façon rigoureuse. &lt;/p&gt; &lt;p&gt; Son œuvre la plus influente est "Naming and Necessity", où il critique la conception descriptiviste des noms défendue par Frege et Russell. Selon lui, un  &lt;a href="https://www.youtube.com/watch?v=d7-8Avem7EE" title="Saul Kripke, La logique des noms propres. par Jtgrandtour"&gt; nom propre&lt;/a&gt; nom propre n’équivaut pas à une description mais fonctionne comme un « désignateur rigide » : il désigne le même individu dans tous les mondes possibles. Cette idée bouleverse la philosophie du langage et entraîne une redéfinition de la notion de référence.&lt;/p&gt; &lt;p&gt;  Il montre également qu’il existe des vérités nécessaires découvertes empiriquement : par exemple, l’identité « l’eau est H₂O » est nécessaire, mais nous ne l’avons apprise qu’a posteriori. Ce concept de nécessité a posteriori a marqué un tournant dans la métaphysique contemporaine. À l’inverse, il identifie la possibilité de certaines vérités contingentes connues a priori, ce qui remet en cause des distinctions classiques entre connaissance et modalité. &lt;/p&gt; &lt;p&gt; Il s’oppose au physicalisme en arguant que l’on peut concevoir un monde où tous les états cérébraux existent sans que la conscience subjective "le qualia" ne soit présente. Cette critique alimente encore aujourd’hui les débats sur la nature de la conscience. Son ouvrage "Wittgenstein on Rules and Private Language" propose une lecture radicale de Wittgenstein, selon laquelle toute règle est sujette à un scepticisme profond sur son application. Bien que controversée, cette interprétation a largement stimulé les discussions en philosophie du langage et en épistémologie. &lt;/p&gt; &lt;p&gt; Connu aussi pour son ouvrage " On two Paradoxes of Knowledge" et son  &lt;a href="https://www.youtube.com/watch?v=AzaUSC--2G0"  title="Le Paradoxe de l'Examen selon Saul Kripke par Silogic"&gt;"paradoxe de l'examen"&lt;/a&gt;. &lt;/p&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">_sIgAdvhruU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Qui est Saul Kripke ?" par Monsieur Phi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/kripke-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logique ; langage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytique ; Essentialisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe américain connu pour ses contributions en logique modale.</t>
+    <t xml:space="preserve">sud</t>
   </si>
   <si>
     <t xml:space="preserve">Ernest SOSA</t>
@@ -384,6 +349,9 @@
     <t xml:space="preserve">epistemologie</t>
   </si>
   <si>
+    <t xml:space="preserve">Analytique</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Philosophe et épistémologue américain  connu pour avoir fondé l’épistémologie des vertus moderne.</t>
   </si>
   <si>
@@ -415,6 +383,9 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe japonais connu pour ses analyses du capitalisme et de la structure du pouvoir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asie-est</t>
   </si>
   <si>
     <t xml:space="preserve">1942</t>
@@ -837,6 +808,9 @@
     <t xml:space="preserve">psychothérapeute et penseur russe souvent associé à des idées philosophiques alternatives.</t>
   </si>
   <si>
+    <t xml:space="preserve">russe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Graham PRIEST</t>
   </si>
   <si>
@@ -1204,17 +1178,17 @@
     <t xml:space="preserve">philosophe britannique qui conteste les modèles scientifiques réductionnistes et déterministes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Françis FUKUYAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Fukuyama"  title=" Wikipedia"&gt;Françis FUKUYAMA&lt;/a&gt; est un philosophe et politologue américain, connu surtout pour sa thèse de la  &lt;a href="https://www.youtube.com/watch?v=xFdt1ZGLLFw"  title="la fin de l’histoire par france culture"&gt;« fin de l’histoire », &lt;/a&gt; qui affirme que la démocratie libérale pourrait constituer le point final de l’évolution idéologique de l’humanité. Sa pensée s’inscrit dans une tradition de philosophie de l’histoire inspirée de Hegel, mais revisitée à travers Alexandre Kojève et une lecture moderne du capitalisme et des régimes politiques. &lt;/p&gt; &lt;p&gt; Dans son livre &lt;a href="https://www.youtube.com/watch?v=jgYgXUBcynk"  title="la fin de l’histoire par cultures et savoirs"&gt;La fin de l’histoire et le dernier homme &lt;/a&gt;  (1992), il soutient que, après la chute du communisme et la victoire des démocraties libérales, aucune idéologie majeure ne semble désormais capable de rivaliser durablement avec ce modèle. Pour lui, l’histoire n’est pas un simple enchaînement d’événements, mais un processus dirigé vers une forme politique rationnelle et libre : l’État libéral moderne, qui incarne la réalisation de l’autonomie absolue de la conscience. Cette idée est controversée, car elle suggère que toutes les sociétés devraient, tôt ou tard, tendre vers ce modèle et justifie en quelque sorte une vision universaliste et parfois néoconservatrice de la démocratie. &lt;/p&gt; &lt;p&gt; Au  &lt;a href="https://www.youtube.com/watch?v=Y_Fu9d2LGlA"  title="intervievé apr o delagarde pour editions st simon"&gt;cœur de sa philosophie, &lt;/a&gt; il pose un « double désir » humain : d’un côté, le désir de conservation de soi et de satisfaction égoïste, qui sous-tend le développement économique capitaliste ; de l’autre, le désir « thymotique » de reconnaissance, qui pousse les individus à vouloir être reconnus comme libres et dignes. Le premier favorise l’accumulation et le marché, tandis que le second, lorsqu’il est « domestiqué », conduit à des formes politiques rationnelles et non violentes, comme la démocratie libérale. Cette tension entre désir égoïste et désir de reconnaissance explique selon lui pourquoi les régimes autoritaires ou dictatoriaux sont, à terme, instables. &lt;/p&gt; &lt;p&gt;  Il évoque également la figure du « dernier homme », celui qui habite le monde posthistorique : un individu gouverné par la raison du technicien et le désir du consommateur, mais qui a perdu une partie centrale de l’âme humaine, le thumos, ce ferment de passion, de fierté et d’ambition qui avait caractérisé l’« homme historique ». Ce dernier homme, ou « homme démocratique », risque ainsi de devenir apathique, sans grands ideals, capable seulement de satisfaire ses petits désirs par calcul égoïste à long terme. Il  s’interroge alors sur les dangers internes à la démocratie libérale : (désir de reconnaissance égalitaire), pouvant conduire à des crises politiques ou à un populisme irrationnel. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus tardifs, il développe une théorie du développement politique centrée sur trois institutions fondamentales : un État moderne puissant et efficace, l’autorité de la loi, et la responsabilité politique des gouvernants. Il considère que la réussite d’une démocratie libérale dépend de l’équilibre stable entre ces trois éléments, et il utilise le Danemark comme « idéal politique symbolique » d’une société ayant parfaitement combiné ces dimensions. Selon lui, la simple mise en place d’élections ne suffit pas à créer une démocratie solide : il faut aussi des institutions fortes, une loi applicable à tous et une véritable responsabilité des gouvernants devant les citoyens. &lt;/p&gt; 
+    <t xml:space="preserve">Francis FUKUYAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Fukuyama"  title=" Wikipedia"&gt;Francis FUKUYAMA&lt;/a&gt; est un philosophe et politologue américain, connu surtout pour sa thèse de la  &lt;a href="https://www.youtube.com/watch?v=xFdt1ZGLLFw"  title="la fin de l’histoire par france culture"&gt;« fin de l’histoire », &lt;/a&gt; qui affirme que la démocratie libérale pourrait constituer le point final de l’évolution idéologique de l’humanité. Sa pensée s’inscrit dans une tradition de philosophie de l’histoire inspirée de Hegel, mais revisitée à travers Alexandre Kojève et une lecture moderne du capitalisme et des régimes politiques. &lt;/p&gt; &lt;p&gt; Dans son livre &lt;a href="https://www.youtube.com/watch?v=jgYgXUBcynk"  title="la fin de l’histoire par cultures et savoirs"&gt;La fin de l’histoire et le dernier homme &lt;/a&gt;  (1992), il soutient que, après la chute du communisme et la victoire des démocraties libérales, aucune idéologie majeure ne semble désormais capable de rivaliser durablement avec ce modèle. Pour lui, l’histoire n’est pas un simple enchaînement d’événements, mais un processus dirigé vers une forme politique rationnelle et libre : l’État libéral moderne, qui incarne la réalisation de l’autonomie absolue de la conscience. Cette idée est controversée, car elle suggère que toutes les sociétés devraient, tôt ou tard, tendre vers ce modèle et justifie en quelque sorte une vision universaliste et parfois néoconservatrice de la démocratie. &lt;/p&gt; &lt;p&gt; Au  &lt;a href="https://www.youtube.com/watch?v=Y_Fu9d2LGlA"  title="intervievé apr o delagarde pour editions st simon"&gt;cœur de sa philosophie, &lt;/a&gt; il pose un « double désir » humain : d’un côté, le désir de conservation de soi et de satisfaction égoïste, qui sous-tend le développement économique capitaliste ; de l’autre, le désir « thymotique » de reconnaissance, qui pousse les individus à vouloir être reconnus comme libres et dignes. Le premier favorise l’accumulation et le marché, tandis que le second, lorsqu’il est « domestiqué », conduit à des formes politiques rationnelles et non violentes, comme la démocratie libérale. Cette tension entre désir égoïste et désir de reconnaissance explique selon lui pourquoi les régimes autoritaires ou dictatoriaux sont, à terme, instables. &lt;/p&gt; &lt;p&gt;  Il évoque également la figure du « dernier homme », celui qui habite le monde posthistorique : un individu gouverné par la raison du technicien et le désir du consommateur, mais qui a perdu une partie centrale de l’âme humaine, le thumos, ce ferment de passion, de fierté et d’ambition qui avait caractérisé l’« homme historique ». Ce dernier homme, ou « homme démocratique », risque ainsi de devenir apathique, sans grands ideals, capable seulement de satisfaire ses petits désirs par calcul égoïste à long terme. Il  s’interroge alors sur les dangers internes à la démocratie libérale : (désir de reconnaissance égalitaire), pouvant conduire à des crises politiques ou à un populisme irrationnel. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus tardifs, il développe une théorie du développement politique centrée sur trois institutions fondamentales : un État moderne puissant et efficace, l’autorité de la loi, et la responsabilité politique des gouvernants. Il considère que la réussite d’une démocratie libérale dépend de l’équilibre stable entre ces trois éléments, et il utilise le Danemark comme « idéal politique symbolique » d’une société ayant parfaitement combiné ces dimensions. Selon lui, la simple mise en place d’élections ne suffit pas à créer une démocratie solide : il faut aussi des institutions fortes, une loi applicable à tous et une véritable responsabilité des gouvernants devant les citoyens. &lt;/p&gt; 
  &lt;audio controls title="françis fukuyama , invité exceptionnel  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18558-29.03.2025-ITEMA_24078125-2025F30378S0088-NET_MFI_CAA5AAF8-7090-406D-8A64-9AAFB37A2346-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">pc7O7qSBzM8</t>
   </si>
   <si>
-    <t xml:space="preserve">Françis kukuyama history &amp; democracy par j citarella</t>
+    <t xml:space="preserve">Francis Fukuyama history &amp; democracy par j citarella</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/ffukuyama-mini.webp</t>
@@ -1661,6 +1635,7 @@
         <sz val="9"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">森岡正博 – </t>
     </r>
@@ -1722,17 +1697,17 @@
     <t xml:space="preserve">philosophe espagnol spécialiste de l’histoire des idées morales et politiques.</t>
   </si>
   <si>
-    <t xml:space="preserve">Jean-Gedefroy BIDIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima" title=" Wikipedia"&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href="https://www.youtube.com/watch?v=DuBiS9vGgmg"  title="environnement transatlantiques par l’humain noir par YeisonArcadio"&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title="Comment dépasser le post-colonial par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+    <t xml:space="preserve">Jean-Godefroy BIDIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima" title=" Wikipedia"&gt;Jean-Godefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href="https://www.youtube.com/watch?v=DuBiS9vGgmg"  title="environnement transatlantiques par l’humain noir par YeisonArcadio"&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title="Comment dépasser le post-colonial par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
   </si>
   <si>
     <t xml:space="preserve">pUSqBXfRKCE</t>
   </si>
   <si>
-    <t xml:space="preserve">Jean-Gedefroy BIDIMA, le philosophe de la traversé par RFI</t>
+    <t xml:space="preserve">Jean-Godefroy BIDIMA, le philosophe de la traversé par RFI</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/jgbidima-mini.webp</t>
@@ -1863,6 +1838,9 @@
     <t xml:space="preserve">philosophe tunisien auteur d'essais portant principalement sur la politique et la religion.</t>
   </si>
   <si>
+    <t xml:space="preserve">islam-juif</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weyma LUBBE</t>
   </si>
   <si>
@@ -1951,10 +1929,10 @@
     <t xml:space="preserve">1963</t>
   </si>
   <si>
-    <t xml:space="preserve">Iain HAMILTON GRAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant"  title=" Wikipedia"&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif"  title="speculative realism  par Wikipedia"&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href="https://www.youtube.com/watch?v=5LGODQdFaw0"  title="Schelling’s Philosophy of Nature  par Philosophical Bachelor"&gt;"Philosophies of Nature After Schelling"&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage "On an Artificial Earth" développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; </t>
+    <t xml:space="preserve">Iain HAMILTON GRANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant"  title=" Wikipedia"&gt;Iain HAMILTON GRANT&lt;/a&gt; est un philosophe britannique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif"  title="speculative realism  par Wikipedia"&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href="https://www.youtube.com/watch?v=5LGODQdFaw0"  title="Schelling’s Philosophy of Nature  par Philosophical Bachelor"&gt;"Philosophies of Nature After Schelling"&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage "On an Artificial Earth" développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">cMoTh3HpO0E</t>
@@ -2253,7 +2231,7 @@
     <t xml:space="preserve">1972</t>
   </si>
   <si>
-    <t xml:space="preserve">Fenwire SARR</t>
+    <t xml:space="preserve">Felwine SARR</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Felwine_Sarr"  title=" Wikipedia"&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href="https://www.youtube.com/watch?v=gty0PculB7U"  title="Afrotopia par david Mboussou"&gt;"Afrotopia" &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  "Dahij, Méditations africaines"  , "Habiter le monde" et "Les lieux qu’habitent mes rêves". &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href="https://www.youtube.com/watch?v=TVXc5KT_Z6Q" title="Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD"&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Felwine Sarr, habiter poétiquement le monde par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
@@ -2405,7 +2383,10 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/dembroff-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">philosophe américaine travaillant sur les questions de genre et les questions LGBT.</t>
+    <t xml:space="preserve">philosophe américain·e non binaire travaillant sur les questions de genre et les questions LGBT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">femme;non-binaire</t>
   </si>
   <si>
     <t xml:space="preserve">1982</t>
@@ -2519,6 +2500,60 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe américain du droit et de la philosophie africaine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angela DAVIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Angela_Davis"  title=" Wikipedia"&gt;Angela DAVIS&lt;/a&gt; (née en 1944) est une philosophe, professeure et militante américaine. Née à Birmingham, en Alabama, dans un quartier surnommé « Dynamite Hill » en raison des attentats racistes qui le frappaient, elle étudia la philosophie aux États-Unis puis en Allemagne, avec Theodor Adorno, et fut l'élève d'Herbert Marcuse.&lt;/p&gt; &lt;p&gt;Membre du Parti communiste et proche des Black Panthers, elle fut accusée en 1970 de complicité dans une prise d'otages sanglante, à cause d'armes achetées à son nom. Inscrite sur la liste des personnes les plus recherchées par le FBI, elle fut arrêtée puis emprisonnée seize mois. Une immense campagne internationale, « Free Angela », se mobilisa pour elle, et elle fut acquittée en 1972.&lt;/p&gt; &lt;p&gt;Son parcours philosophique est marqué par l'École de Francfort, dont elle retient l'idée qu'une théorie critique doit viser la transformation de la société. Elle s'est aussi intéressée à la musique populaire noire, en particulier au blues de chanteuses comme Billie Holiday, qu'elle interprète comme une forme de conscience sociale et féministe. Elle est aujourd'hui une référence mondiale pour les mouvements antiracistes et féministes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Femmes, race et classe&lt;/em&gt; (1981), elle analyse comment l'esclavage, le racisme et le capitalisme ont façonné la condition des femmes noires. Elle est devenue l'une des grandes voix du mouvement pour l'abolition des prisons, qu'elle considère comme la continuation de l'esclavage et de la ségrégation. Professeure à l'université de Californie, elle incarne l'union entre la réflexion philosophique et l'engagement politique.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marxisme ; Féminisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe et militante afro-américaine, figure de la lutte contre le racisme, le sexisme et le système carcéral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">femme ; sud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seyyed Hossein NASR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Seyyed_Hossein_Nasr"  title=" Wikipedia"&gt;Seyyed Hossein NASR&lt;/a&gt; est un philosophe iranien né à Téhéran en 1933. Envoyé aux États-Unis à douze ans, il étudie la physique au MIT, puis l'histoire des sciences à Harvard, où il obtient son doctorat en 1958. Il rentre alors en Iran, enseigne à l'université de Téhéran et fonde en 1974 l'Académie impériale iranienne de philosophie. La révolution de 1979 le contraint à l'exil : il enseigne depuis 1984 à l'université George Washington.&lt;/p&gt; &lt;p&gt;Dès ses études, il est déçu par une science moderne qui ne dit rien du sens des choses, et découvre les auteurs de l'école dite « traditionaliste », René Guénon et Frithjof Schuon. Avec eux, il affirme qu'il existe une sagesse éternelle, la &lt;em&gt;philosophia perennis&lt;/em&gt;, présente au cœur de toutes les grandes religions, et que le monde moderne l'a oubliée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Connaissance et le Sacré&lt;/em&gt;, issu de conférences prononcées en 1981, il défend l'idée d'une « science sacrée » : connaître vraiment, c'est relier chaque chose à son origine divine. Il a consacré de nombreux ouvrages aux sciences et à la philosophie du monde musulman, d'Avicenne à Molla Sadra, ainsi qu'au soufisme, qu'il pratique lui-même. Il a aussi dirigé une traduction commentée du Coran en anglais, &lt;em&gt;The Study Quran&lt;/em&gt; (2015), qui rassemble les interprétations des différentes écoles.&lt;/p&gt; &lt;p&gt;Dès 1968, dans &lt;em&gt;L'Homme et la Nature&lt;/em&gt;, il soutient que la crise écologique est d'abord une crise spirituelle : en cessant de voir la nature comme sacrée, l'homme moderne s'est cru autorisé à la dominer sans limite. Il est l'un des premiers penseurs à avoir posé ce diagnostic.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pérennialisme ; Soufisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe iranien, penseur de la science sacrée et de la tradition, professeur aux États-Unis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdallah LAROUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdallah_Laroui"  title=" Wikipedia"&gt;Abdallah LAROUI&lt;/a&gt; est un historien, philosophe et romancier marocain né à Azemmour en 1933. Après des études à Rabat et à Paris, il enseigne l'histoire à l'université Mohammed V de Rabat pendant plus de trente ans. Il écrit en français et en arabe, et a traduit en arabe des textes de Rousseau et de Montesquieu. Il est aussi l'auteur d'une &lt;em&gt;Histoire du Maghreb&lt;/em&gt; (1970) et de plusieurs romans.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;L'Idéologie arabe contemporaine&lt;/em&gt; (1967), paraît l'année de la défaite arabe face à Israël et devient une référence. Il y décrit trois figures qui, depuis un siècle, répondent chacune à sa façon au défi de l'Occident : le clerc, qui cherche le salut dans le retour à la religion ; le politicien libéral, qui l'attend de la démocratie ; le technophile, qui ne croit qu'à la science et à l'industrie. Aucune, selon lui, ne pense vraiment la situation.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Crise des intellectuels arabes&lt;/em&gt; (1974), il oppose deux attitudes : le traditionalisme, qui cherche dans le passé des réponses toutes faites, et l'historicisme, qu'il défend. Être historiciste, c'est admettre que l'histoire a un sens, que la modernité née en Europe est un acquis de toute l'humanité, et qu'un peuple en retard doit en assimiler les principes : raison, liberté, État, sans croire pouvoir s'en dispenser. Le marxisme l'intéresse surtout comme le résumé de cette pensée moderne.&lt;/p&gt; &lt;p&gt;Il plaide ainsi pour une rupture nette avec l'héritage, là où son compatriote al-Jabri proposait de le relire. Il a poursuivi ce travail dans une série d'ouvrages en arabe, chacun consacré à un concept : l'idéologie, la liberté, l'État, l'histoire, la raison.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marocaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historien et philosophe marocain, auteur de L'Idéologie arabe contemporaine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdolkarim SOROUSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdolkarim_Soroush"  title=" Wikipedia"&gt;Abdolkarim SOROUSH&lt;/a&gt;, nom de plume de Hossein Haj Faraj Dabbagh, est un philosophe iranien né à Téhéran en 1945. Pharmacien de formation, il étudie à Londres la chimie, puis l'histoire et la philosophie des sciences, où il découvre Karl Popper. Rentré en Iran à la révolution de 1979, il siège au conseil chargé de réorganiser les universités, qu'il quitte en 1983. Il devient dans les années 1990 la principale voix des intellectuels réformateurs.&lt;/p&gt; &lt;p&gt;Sa thèse la plus connue est exposée dans &lt;em&gt;La Contraction et l'expansion théoriques de la charia&lt;/em&gt; (1990). Il y distingue la religion elle-même, d'origine divine, et la connaissance que les hommes en ont. Cette connaissance est humaine, faillible et historique : elle dépend de tout ce que nous savons par ailleurs, en science, en histoire ou en philosophie, et change donc avec les époques. Personne ne peut dès lors prétendre détenir l'interprétation définitive, pas même le clergé.&lt;/p&gt; &lt;p&gt;Il en tire une critique du pouvoir religieux : faire de la religion une idéologie d'État, c'est la figer et la corrompre. Un gouvernement peut être à la fois religieux et démocratique, mais seulement s'il respecte la liberté de croire et les droits de l'homme. Il rejette ainsi le principe iranien du gouvernement du juriste-théologien.&lt;/p&gt; &lt;p&gt;Il a ensuite soutenu que la révélation porte la marque de la personnalité et de l'époque du Prophète. Grand lecteur du poète mystique Rumi, il a été agressé et empêché d'enseigner, puis a quitté l'Iran vers 2000 pour les universités américaines et européennes. Il a reçu le prix Érasme en 2004. Il partagea ce prix avec la sociologue marocaine Fatima Mernissi.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epistemologie ; spiritualite ; politique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe iranien, penseur de la réforme religieuse et de la distinction entre religion et connaissance religieuse.</t>
   </si>
 </sst>
 </file>
@@ -2528,7 +2563,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2609,17 +2644,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2653,12 +2688,6 @@
       <sz val="9"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2737,100 +2766,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3086,7 +3111,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P1048576"/>
+  <dimension ref="A1:Q1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3174,14 +3199,15 @@
       <c r="N3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Groupe</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Importance</t>
+      <c r="O3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thèmes</t>
         </is>
       </c>
     </row>
@@ -3191,39 +3217,42 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
+        <v>27</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
@@ -3233,44 +3262,45 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
+        <v>38</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; continental</t>
         </is>
       </c>
     </row>
@@ -3280,1573 +3310,1658 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="213.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="213.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
-        <v>56</v>
+      <c r="C8" s="7" t="n">
+        <v>1934</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="M8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="O8" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="K9" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>1936</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>98</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="7" t="s">
-        <v>93</v>
+      <c r="C12" s="7" t="n">
+        <v>1940</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="1" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7" t="n">
-        <v>1940</v>
+      <c r="C14" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>112</v>
+        <v>120</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>115</v>
+        <v>123</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="1" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>134</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>1942</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
-        <v>128</v>
+      <c r="C16" s="7" t="n">
+        <v>1942</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>136</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>133</v>
+        <v>138</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>138</v>
+        <v>143</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>144</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="198.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7" t="n">
-        <v>1942</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>145</v>
+        <v>150</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="M18" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N18" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="371.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
-        <v>151</v>
+      <c r="C19" s="7" t="n">
+        <v>1943</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="1" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="198.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>163</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>160</v>
+        <v>166</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="1" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="371.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+      <c r="N20" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B21" s="7"/>
-      <c r="C21" s="7" t="n">
-        <v>1943</v>
+      <c r="C21" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="1" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
-        <v>174</v>
+      <c r="C22" s="7" t="n">
+        <v>1944</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>176</v>
+        <v>181</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>182</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>187</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="261" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="7" t="s">
-        <v>174</v>
+      <c r="C23" s="7" t="n">
+        <v>1944</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>194</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B24" s="7"/>
-      <c r="C24" s="7" t="n">
-        <v>1944</v>
+      <c r="C24" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>191</v>
+        <v>197</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>194</v>
+        <v>200</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="261" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>203</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B25" s="7"/>
-      <c r="C25" s="7" t="n">
-        <v>1944</v>
+      <c r="C25" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>198</v>
+        <v>205</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>206</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>201</v>
+        <v>208</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="1" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="N26" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>215</v>
+        <v>220</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>221</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="1" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N27" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B28" s="7"/>
-      <c r="C28" s="7" t="s">
-        <v>221</v>
+      <c r="C28" s="7" t="n">
+        <v>1947</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="N28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>230</v>
+        <v>235</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>236</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="N29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
-        <v>1947</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="n">
-        <v>1947</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>236</v>
+        <v>241</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>239</v>
+        <v>244</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="M30" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="N30" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O30" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B31" s="7"/>
-      <c r="C31" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="C31" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="E31" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="I31" s="10"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>250</v>
+      </c>
       <c r="J31" s="1" t="s">
-        <v>70</v>
+        <v>251</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>24</v>
+        <v>253</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
+        <v>254</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="I32" s="10"/>
+      <c r="C32" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>54</v>
+        <v>261</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>263</v>
+      </c>
+      <c r="O32" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B33" s="7"/>
-      <c r="C33" s="7" t="n">
-        <v>1948</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>259</v>
-      </c>
+      <c r="C33" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I33" s="10"/>
       <c r="J33" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>1948</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>1948</v>
-      </c>
-      <c r="D34" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="O33" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I34" s="1"/>
+      <c r="D34" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I34" s="10"/>
       <c r="J34" s="1" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>270</v>
+        <v>105</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>279</v>
+      </c>
+      <c r="N34" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O34" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel ; ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="1" t="s">
-        <v>278</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>285</v>
+      </c>
+      <c r="O35" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
-        <v>272</v>
+      <c r="C36" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>287</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>290</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="1" t="s">
-        <v>286</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>188</v>
+        <v>291</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>292</v>
+      </c>
+      <c r="O36" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>43</v>
+        <v>298</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
+        <v>300</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
     <row r="38" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="7" t="n">
-        <v>1949</v>
+      <c r="C38" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>295</v>
+        <v>302</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>298</v>
+        <v>305</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>308</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>302</v>
+        <v>309</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>310</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="1" t="s">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>306</v>
+        <v>86</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>307</v>
+        <v>148</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="N39" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O39" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>315</v>
+      </c>
+      <c r="O39" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental ; decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B40" s="7"/>
-      <c r="C40" s="7" t="s">
-        <v>309</v>
+      <c r="C40" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>311</v>
+        <v>316</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>314</v>
+        <v>319</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>320</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="N40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="O40" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>318</v>
+        <v>324</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="1" t="s">
-        <v>322</v>
+        <v>35</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>329</v>
+      </c>
+      <c r="O41" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>1950</v>
       </c>
@@ -4855,3035 +4970,3071 @@
         <v>1950</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>328</v>
+        <v>333</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>334</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M42" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B43" s="7"/>
-      <c r="C43" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>333</v>
+      <c r="C43" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>339</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>336</v>
+        <v>341</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>342</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>32</v>
+        <v>251</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B44" s="7"/>
-      <c r="C44" s="7" t="n">
-        <v>1950</v>
+      <c r="C44" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>339</v>
+        <v>346</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>347</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>342</v>
+        <v>349</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>350</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M44" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="N44" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O44" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; genre ; decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="N44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>347</v>
+      <c r="D45" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>354</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>350</v>
+        <v>356</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>357</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="O45" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>355</v>
+        <v>360</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>361</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>366</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>362</v>
+        <v>367</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>373</v>
+      </c>
+      <c r="O47" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="C48" s="7" t="s">
-        <v>353</v>
+      <c r="C48" s="7" t="n">
+        <v>1952</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>369</v>
+        <v>374</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>375</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>372</v>
+        <v>377</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>378</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="N48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+      <c r="M48" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="O48" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>376</v>
+        <v>382</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>383</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>380</v>
+        <v>57</v>
       </c>
       <c r="M49" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O49" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7" t="n">
-        <v>1952</v>
-      </c>
       <c r="D50" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>383</v>
+        <v>388</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>389</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>386</v>
+        <v>391</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>392</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="M50" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>393</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="O50" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; justice ; sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>63</v>
+        <v>400</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>401</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>1953</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>397</v>
+        <v>402</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>403</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>408</v>
+      </c>
+      <c r="O52" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
-        <v>52</v>
+        <v>415</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+      <c r="O53" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+      <c r="O54" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>419</v>
+        <v>424</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>425</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>33</v>
+        <v>430</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>424</v>
+        <v>106</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+      <c r="O55" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>427</v>
+        <v>432</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>433</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+      <c r="O56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B57" s="7"/>
-      <c r="C57" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>433</v>
+      <c r="C57" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>441</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>436</v>
+        <v>443</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>444</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>54</v>
+        <v>446</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+      <c r="O57" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>441</v>
+        <v>449</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>450</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>445</v>
+        <v>261</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+      <c r="O58" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B59" s="7"/>
-      <c r="C59" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D59" s="17" t="s">
+      <c r="C59" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>449</v>
+      <c r="D59" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>456</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>452</v>
+        <v>458</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>459</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>463</v>
+      </c>
+      <c r="O59" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>269</v>
+        <v>36</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>54</v>
+        <v>358</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>469</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="s">
-        <v>456</v>
+      <c r="C61" s="7" t="n">
+        <v>1955</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>464</v>
+        <v>470</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>471</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="1" t="s">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>469</v>
+        <v>105</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>470</v>
+        <v>172</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>475</v>
+      </c>
+      <c r="O61" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>478</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>366</v>
+        <v>172</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="N62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>482</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="B63" s="7"/>
-      <c r="C63" s="7" t="n">
-        <v>1955</v>
+      <c r="C63" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>479</v>
+        <v>484</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>485</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>181</v>
+        <v>489</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>490</v>
+      </c>
+      <c r="O63" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>486</v>
+        <v>491</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>492</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>43</v>
+        <v>496</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>181</v>
+        <v>497</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="N64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="O64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>498</v>
+      </c>
+      <c r="O64" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>493</v>
+      <c r="C65" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>500</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="P65">
-        <v>3</v>
+        <v>505</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="I66" s="10"/>
+      <c r="C66" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>509</v>
+      </c>
       <c r="J66" s="1" t="s">
-        <v>52</v>
+        <v>251</v>
       </c>
       <c r="K66" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L66" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="M66" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+      <c r="O66" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>508</v>
+      <c r="C67" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>513</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="1" t="s">
-        <v>260</v>
+        <v>114</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>518</v>
+      </c>
+      <c r="O67" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>515</v>
-      </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>517</v>
-      </c>
+      <c r="C68" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="I68" s="10"/>
       <c r="J68" s="1" t="s">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>512</v>
-      </c>
       <c r="M68" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>524</v>
+      </c>
+      <c r="O68" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>521</v>
+        <v>525</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>526</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>124</v>
+        <v>429</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>525</v>
+        <v>358</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>530</v>
+      </c>
+      <c r="O69" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B70" s="7"/>
-      <c r="C70" s="7" t="s">
-        <v>519</v>
+      <c r="C70" s="7" t="n">
+        <v>1958</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>528</v>
+        <v>531</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>532</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>531</v>
+        <v>534</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>535</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="1" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>315</v>
+        <v>47</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>536</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="O70" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B71" s="7"/>
       <c r="C71" s="7" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>534</v>
+        <v>539</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>540</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="1" t="s">
-        <v>437</v>
+        <v>278</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>366</v>
+        <v>179</v>
       </c>
       <c r="M71" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="N71" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O71" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7" t="n">
-        <v>1958</v>
-      </c>
       <c r="D72" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>540</v>
+        <v>545</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>546</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>542</v>
-      </c>
-      <c r="H72" s="12" t="s">
-        <v>543</v>
+        <v>548</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>549</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
-        <v>99</v>
+        <v>550</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="M72" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>218</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N72" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="O72" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B73" s="7"/>
-      <c r="C73" s="7" t="s">
-        <v>546</v>
+      <c r="C73" s="7" t="n">
+        <v>1960</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>548</v>
+        <v>552</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>553</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>551</v>
+        <v>555</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>556</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="1" t="s">
-        <v>286</v>
+        <v>557</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>90</v>
+        <v>558</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="I74" s="10"/>
+        <v>559</v>
+      </c>
+      <c r="M73" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="N73" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O73" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>227</v>
+        <v>47</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>567</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>568</v>
+      </c>
+      <c r="O74" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B75" s="7"/>
-      <c r="C75" s="7" t="n">
-        <v>1960</v>
+      <c r="C75" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>561</v>
+        <v>570</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>571</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>564</v>
+        <v>573</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>574</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="1" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>566</v>
+        <v>193</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="M75" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="I76" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="O75" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>581</v>
+      </c>
       <c r="J76" s="1" t="s">
-        <v>574</v>
+        <v>24</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>575</v>
+        <v>86</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>582</v>
+      </c>
+      <c r="N76" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O76" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="O77" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7" t="n">
-        <v>1961</v>
-      </c>
       <c r="D78" s="8" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="F78" s="7"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>588</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="I78" s="10"/>
       <c r="J78" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>54</v>
+        <v>595</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>596</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B79" s="7"/>
-      <c r="C79" s="7" t="s">
-        <v>590</v>
+      <c r="C79" s="7" t="n">
+        <v>1962</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>592</v>
+        <v>597</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>595</v>
+        <v>600</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>601</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="1" t="s">
-        <v>286</v>
+        <v>65</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>43</v>
+        <v>602</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>227</v>
+        <v>603</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>604</v>
+      </c>
+      <c r="O79" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>598</v>
+        <v>606</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>607</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>43</v>
+        <v>611</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>602</v>
+        <v>517</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="N80" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="O80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>612</v>
+      </c>
+      <c r="O80" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="B81" s="7"/>
-      <c r="C81" s="7" t="n">
-        <v>1962</v>
+      <c r="C81" s="7" t="s">
+        <v>613</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>605</v>
+        <v>614</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>615</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>608</v>
+        <v>617</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>609</v>
+        <v>105</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>620</v>
+      </c>
+      <c r="O81" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>614</v>
+        <v>622</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>623</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>618</v>
+        <v>47</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>525</v>
+        <v>218</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>627</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>116</v>
+        <v>611</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>634</v>
+      </c>
+      <c r="O83" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>630</v>
+        <v>636</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>637</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>227</v>
+        <v>641</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>642</v>
+      </c>
+      <c r="O84" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B85" s="7"/>
-      <c r="C85" s="7" t="s">
-        <v>628</v>
+      <c r="C85" s="7" t="n">
+        <v>1966</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>639</v>
+        <v>646</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>647</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
-        <v>70</v>
+        <v>648</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>618</v>
+        <v>76</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>650</v>
+      </c>
+      <c r="O85" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>644</v>
+        <v>652</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>653</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>315</v>
+        <v>657</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>659</v>
+      </c>
+      <c r="N86" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O86" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7" t="n">
-        <v>1966</v>
+      <c r="C87" s="7" t="s">
+        <v>651</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>654</v>
+        <v>663</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>664</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>666</v>
+      </c>
+      <c r="O87" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="E88" s="22" t="s">
-        <v>660</v>
+        <v>667</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>668</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>664</v>
+        <v>321</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="201" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>673</v>
+      </c>
+      <c r="O88" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="7" t="s">
-        <v>658</v>
+      <c r="C89" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>668</v>
+        <v>674</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>675</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>671</v>
+        <v>677</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>678</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>679</v>
+      </c>
+      <c r="O89" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7" t="s">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>675</v>
+        <v>681</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>682</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>329</v>
+        <v>496</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>679</v>
+        <v>106</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>686</v>
+      </c>
+      <c r="O90" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="n">
-        <v>1968</v>
+      <c r="C91" s="7" t="s">
+        <v>687</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>682</v>
+        <v>688</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>689</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>684</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>685</v>
+        <v>691</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>692</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>286</v>
+        <v>693</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>656</v>
+        <v>106</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>694</v>
+      </c>
+      <c r="N91" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O91" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>689</v>
+        <v>696</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>697</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>504</v>
+        <v>611</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>54</v>
+        <v>517</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>701</v>
+      </c>
+      <c r="O92" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>696</v>
+        <v>702</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>703</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>704</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>700</v>
+        <v>460</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>708</v>
+      </c>
+      <c r="M93" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="O93" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>704</v>
+        <v>711</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>712</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>22</v>
+        <v>716</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>618</v>
+        <v>496</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>525</v>
+        <v>717</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>718</v>
+      </c>
+      <c r="O94" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>709</v>
-      </c>
-      <c r="D95" s="23" t="s">
-        <v>710</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>711</v>
+        <v>719</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>721</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="M95" s="14" t="s">
-        <v>716</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="O95" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>723</v>
+        <v>65</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>504</v>
+        <v>307</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>658</v>
+      </c>
+      <c r="M96" s="14" t="s">
+        <v>732</v>
+      </c>
+      <c r="N96" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O96" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
         <v>726</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>728</v>
+        <v>733</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>734</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>116</v>
+        <v>445</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>54</v>
+        <v>738</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>739</v>
+      </c>
+      <c r="N97" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="O97" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>734</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>735</v>
+        <v>741</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>742</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>315</v>
+        <v>611</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="M98" s="14" t="s">
-        <v>739</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>633</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="O98" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>741</v>
+        <v>747</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>748</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>745</v>
+        <v>106</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>752</v>
+      </c>
+      <c r="N99" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="O99" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E100" s="12" t="s">
-        <v>749</v>
+        <v>755</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>22</v>
+        <v>716</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>618</v>
+        <v>496</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>640</v>
+        <v>106</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>760</v>
+      </c>
+      <c r="O100" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="E101" s="12" t="s">
-        <v>755</v>
+        <v>762</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>763</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>504</v>
+        <v>36</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe américain·e non binaire travaillant sur les questions de genre et les questions LGBT.</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme;non-binaire</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="N101" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O101" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>762</v>
+        <v>769</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>770</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>723</v>
+        <v>65</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>774</v>
+      </c>
+      <c r="N102" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="O102" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>54</v>
+        <v>781</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+      <c r="O103" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>776</v>
+        <v>783</v>
+      </c>
+      <c r="D104" s="22" t="s">
+        <v>784</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>785</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K104" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="N104" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="O104" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="10"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="10"/>
+      <c r="H105" s="10"/>
+      <c r="I105" s="10"/>
+    </row>
+    <row r="106" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="10"/>
+      <c r="H106" s="10"/>
+      <c r="I106" s="10"/>
+    </row>
+    <row r="107" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>791</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="N107" s="0" t="s">
+        <v>795</v>
+      </c>
+      <c r="O107" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="P107" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>796</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="N108" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="O108" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>801</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L109" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="L104" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M104" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>783</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>785</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>786</v>
-      </c>
-      <c r="I105" s="10"/>
-      <c r="J105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="M105" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="D106" s="23" t="s">
-        <v>790</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>791</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>792</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>793</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>794</v>
-      </c>
-      <c r="I106" s="10"/>
-      <c r="J106" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7">
-        <v>1944</v>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1944</t>
-        </is>
-      </c>
-      <c r="D107" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Angela DAVIS</t>
-        </is>
-      </c>
-      <c r="E107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Angela_Davis"  title=" Wikipedia"&gt;Angela DAVIS&lt;/a&gt; (née en 1944) est une philosophe, professeure et militante américaine. Née à Birmingham, en Alabama, dans un quartier surnommé « Dynamite Hill » en raison des attentats racistes qui le frappaient, elle étudia la philosophie aux États-Unis puis en Allemagne, avec Theodor Adorno, et fut l'élève d'Herbert Marcuse.&lt;/p&gt; &lt;p&gt;Membre du Parti communiste et proche des Black Panthers, elle fut accusée en 1970 de complicité dans une prise d'otages sanglante, à cause d'armes achetées à son nom. Inscrite sur la liste des personnes les plus recherchées par le FBI, elle fut arrêtée puis emprisonnée seize mois. Une immense campagne internationale, « Free Angela », se mobilisa pour elle, et elle fut acquittée en 1972.&lt;/p&gt; &lt;p&gt;Son parcours philosophique est marqué par l'École de Francfort, dont elle retient l'idée qu'une théorie critique doit viser la transformation de la société. Elle s'est aussi intéressée à la musique populaire noire, en particulier au blues de chanteuses comme Billie Holiday, qu'elle interprète comme une forme de conscience sociale et féministe. Elle est aujourd'hui une référence mondiale pour les mouvements antiracistes et féministes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Femmes, race et classe&lt;/em&gt; (1981), elle analyse comment l'esclavage, le racisme et le capitalisme ont façonné la condition des femmes noires. Elle est devenue l'une des grandes voix du mouvement pour l'abolition des prisons, qu'elle considère comme la continuation de l'esclavage et de la ségrégation. Professeure à l'université de Californie, elle incarne l'union entre la réflexion philosophique et l'engagement politique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Américaine</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; ethique</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marxisme ; Féminisme</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe et militante afro-américaine, figure de la lutte contre le racisme, le sexisme et le système carcéral.</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme ; sud</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7">
-        <v>1933</v>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1933</t>
-        </is>
-      </c>
-      <c r="D108" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seyyed Hossein NASR</t>
-        </is>
-      </c>
-      <c r="E108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Seyyed_Hossein_Nasr"  title=" Wikipedia"&gt;Seyyed Hossein NASR&lt;/a&gt; est un philosophe iranien né à Téhéran en 1933. Envoyé aux États-Unis à douze ans, il étudie la physique au MIT, puis l'histoire des sciences à Harvard, où il obtient son doctorat en 1958. Il rentre alors en Iran, enseigne à l'université de Téhéran et fonde en 1974 l'Académie impériale iranienne de philosophie. La révolution de 1979 le contraint à l'exil : il enseigne depuis 1984 à l'université George Washington.&lt;/p&gt; &lt;p&gt;Dès ses études, il est déçu par une science moderne qui ne dit rien du sens des choses, et découvre les auteurs de l'école dite « traditionaliste », René Guénon et Frithjof Schuon. Avec eux, il affirme qu'il existe une sagesse éternelle, la &lt;em&gt;philosophia perennis&lt;/em&gt;, présente au cœur de toutes les grandes religions, et que le monde moderne l'a oubliée.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Connaissance et le Sacré&lt;/em&gt;, issu de conférences prononcées en 1981, il défend l'idée d'une « science sacrée » : connaître vraiment, c'est relier chaque chose à son origine divine. Il a consacré de nombreux ouvrages aux sciences et à la philosophie du monde musulman, d'Avicenne à Molla Sadra, ainsi qu'au soufisme, qu'il pratique lui-même. Il a aussi dirigé une traduction commentée du Coran en anglais, &lt;em&gt;The Study Quran&lt;/em&gt; (2015), qui rassemble les interprétations des différentes écoles.&lt;/p&gt; &lt;p&gt;Dès 1968, dans &lt;em&gt;L'Homme et la Nature&lt;/em&gt;, il soutient que la crise écologique est d'abord une crise spirituelle : en cessant de voir la nature comme sacrée, l'homme moderne s'est cru autorisé à la dominer sans limite. Il est l'un des premiers penseurs à avoir posé ce diagnostic.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Perse</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pérennialisme ; Soufisme</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe iranien, penseur de la science sacrée et de la tradition, professeur aux États-Unis.</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7">
-        <v>1933</v>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1933</t>
-        </is>
-      </c>
-      <c r="D109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abdallah LAROUI</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdallah_Laroui"  title=" Wikipedia"&gt;Abdallah LAROUI&lt;/a&gt; est un historien, philosophe et romancier marocain né à Azemmour en 1933. Après des études à Rabat et à Paris, il enseigne l'histoire à l'université Mohammed V de Rabat pendant plus de trente ans. Il écrit en français et en arabe, et a traduit en arabe des textes de Rousseau et de Montesquieu. Il est aussi l'auteur d'une &lt;em&gt;Histoire du Maghreb&lt;/em&gt; (1970) et de plusieurs romans.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;L'Idéologie arabe contemporaine&lt;/em&gt; (1967), paraît l'année de la défaite arabe face à Israël et devient une référence. Il y décrit trois figures qui, depuis un siècle, répondent chacune à sa façon au défi de l'Occident : le clerc, qui cherche le salut dans le retour à la religion ; le politicien libéral, qui l'attend de la démocratie ; le technophile, qui ne croit qu'à la science et à l'industrie. Aucune, selon lui, ne pense vraiment la situation.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Crise des intellectuels arabes&lt;/em&gt; (1974), il oppose deux attitudes : le traditionalisme, qui cherche dans le passé des réponses toutes faites, et l'historicisme, qu'il défend. Être historiciste, c'est admettre que l'histoire a un sens, que la modernité née en Europe est un acquis de toute l'humanité, et qu'un peuple en retard doit en assimiler les principes : raison, liberté, État, sans croire pouvoir s'en dispenser. Le marxisme l'intéresse surtout comme le résumé de cette pensée moderne.&lt;/p&gt; &lt;p&gt;Il plaide ainsi pour une rupture nette avec l'héritage, là où son compatriote al-Jabri proposait de le relire. Il a poursuivi ce travail dans une série d'ouvrages en arabe, chacun consacré à un concept : l'idéologie, la liberté, l'État, l'histoire, la raison.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marocaine</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marxisme</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">historien et philosophe marocain, auteur de L'Idéologie arabe contemporaine.</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
+      <c r="M109" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="O109" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; decolonial</t>
         </is>
       </c>
     </row>
     <row r="110" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7">
+      <c r="A110" s="7" t="n">
         <v>1945</v>
       </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1945</t>
-        </is>
-      </c>
-      <c r="D110" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abdolkarim SOROUSH</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdolkarim_Soroush"  title=" Wikipedia"&gt;Abdolkarim SOROUSH&lt;/a&gt;, nom de plume de Hossein Haj Faraj Dabbagh, est un philosophe iranien né à Téhéran en 1945. Pharmacien de formation, il étudie à Londres la chimie, puis l'histoire et la philosophie des sciences, où il découvre Karl Popper. Rentré en Iran à la révolution de 1979, il siège au conseil chargé de réorganiser les universités, qu'il quitte en 1983. Il devient dans les années 1990 la principale voix des intellectuels réformateurs.&lt;/p&gt; &lt;p&gt;Sa thèse la plus connue est exposée dans &lt;em&gt;La Contraction et l'expansion théoriques de la charia&lt;/em&gt; (1990). Il y distingue la religion elle-même, d'origine divine, et la connaissance que les hommes en ont. Cette connaissance est humaine, faillible et historique : elle dépend de tout ce que nous savons par ailleurs, en science, en histoire ou en philosophie, et change donc avec les époques. Personne ne peut dès lors prétendre détenir l'interprétation définitive, pas même le clergé.&lt;/p&gt; &lt;p&gt;Il en tire une critique du pouvoir religieux : faire de la religion une idéologie d'État, c'est la figer et la corrompre. Un gouvernement peut être à la fois religieux et démocratique, mais seulement s'il respecte la liberté de croire et les droits de l'homme. Il rejette ainsi le principe iranien du gouvernement du juriste-théologien.&lt;/p&gt; &lt;p&gt;Il a ensuite soutenu que la révélation porte la marque de la personnalité et de l'époque du Prophète. Grand lecteur du poète mystique Rumi, il a été agressé et empêché d'enseigner, puis a quitté l'Iran vers 2000 pour les universités américaines et européennes. Il a reçu le prix Érasme en 2004. Il partagea ce prix avec la sociologue marocaine Fatima Mernissi.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Perse</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">epistemologie ; spiritualite ; politique</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Herméneutique</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe iranien, penseur de la réforme religieuse et de la distinction entre religion et connaissance religieuse.</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C110" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>805</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="O110" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -7892,70 +8043,69 @@
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Hermann_L%C3%BCbbe&quot; title=&quot; Wikipedia&quot;&gt;Hermann LUBBE&lt;/a&gt; est un philosophe allemand dont l'œuvre se concentre sur une théorie de la civilisation moderne et de la démocratie libérale. Figure marquante du paysage intellectuel d'après-guerre, il s'est fait connaître en analysant les bouleversements de la société dynamique et en s'opposant fermement aux mouvements de protestation de 1968, ce qui lui a valu d'être perçu comme l'un des principaux représentants du &lt;a href=&quot;https://www.persee.fr/doc/reval_0035-0974_1988_num_20_1_3302&quot; title=&quot;Le néoconservatisme par persée&quot;&gt; néoconservatisme allemand. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Sa pensée se définit comme une « philosophie après les Lumières », cherchant à sécuriser les acquis du libéralisme tout en rejetant les grandes théories historiques totalisantes. Plutôt que de proposer des projets idéologiques, il privilégie une approche pragmatique qui examine la réalité sous l'angle de l'action pratique et de la résolution de problèmes. Cette méthode valorise le sens commun, la pratique quotidienne et une attention particulière à l'individu dans sa dimension contingente. &lt;/p&gt; &lt;p&gt; Il a développé une réflexion approfondie sur la dialectique entre le progrès technique et la stabilité sociale. Face à l'accélération constante du changement social, il insiste sur l'importance irremplaçable des traditions, des conventions et des institutions stables pour offrir une orientation aux citoyens. Pour lui, ces éléments ne sont pas des freins au progrès, mais des conditions nécessaires pour permettre aux individus de faire face à la complexité et à l'imprévisibilité du monde moderne. &lt;/p&gt; &lt;p&gt; La question de la religion occupe une place centrale dans sa réflexion sur la modernité, qu'il considère comme une ressource essentielle pour donner du sens à l'existence face à la contingence. Il soutient que, malgré le recul des dogmes institutionnels, la religion demeure une composante indispensable de la conscience humaine. À travers &lt;a href=&quot;https://www.persee.fr/doc/rscir_0035-2217_1988_num_62_1_3090_t1_0082_0000_3&quot; title=&quot;Fortdchrittsreaktionen par persée&quot;&gt;ses écrits, &lt;/a&gt; comme dans Sphären der Menschlichkeit, il explore la fragilité de la condition humaine face aux défis technologiques, plaidant pour une approche qui maintient la dignité et l'identité des sujets dans un monde en mutation permanente. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E6" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Taylor_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;Charles TAYLOR&lt;/a&gt; est un philosophe canadien connu pour ses travaux sur l’identité, la modernité, la morale et la reconnaissance. Il s’intéresse moins à des vérités abstraites qu’à la manière dont les êtres humains donnent du sens à leur vie dans des contextes historiques et culturels précis. &lt;/p&gt; &lt;p&gt; Sa philosophie critique d’abord l’idée d’un  &lt;a href=&quot;https://laviedesidees.fr/Charles-Taylor-philosophe-de-la&quot; title=&quot;Charles Taylor par la vie des idées&quot;&gt; individu totalement autonome &lt;/a&gt; et isolé. Il soutient que le moi se construit toujours dans un « horizon moral », c’est-à-dire à travers des valeurs, des langages et des relations qui le dépassent; on ne comprend donc pas une personne sans comprendre le monde partagé dans lequel elle vit. &lt;/p&gt; &lt;p&gt; Un de ses apports majeurs est la notion de reconnaissance. Il explique que chacun a besoin d’être reconnu dans sa singularité, par exemple dans son identité culturelle, linguistique ou religieuse, et il défend ainsi une politique qui respecte les différences sans tomber dans le repli communautaire. Il cherche donc  &lt;a href=&quot;https://www.youtube.com/watch?v=Drd0UT-BcGU&quot; title=&quot;Charles Taylor par Sociologie de l’intégration&quot;&gt; un équilibre entre l’universel &lt;/a&gt; et le particulier, entre les droits communs et la valeur des appartenances. &lt;/p&gt; &lt;p&gt; Il critique le réductionnisme des sciences humaines et l’idée que la raison humaine serait seulement calculatrice ou « désengagée ». Il privilégie une approche interprétative de l’être humain, inspirée de   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Herm%C3%A9neutique&quot; title=&quot;Herméneutique par Wikipedia&quot;&gt; l’herméneutique, &lt;/a&gt;  selon laquelle comprendre une action, une croyance ou une identité demande d’en saisir le sens vécu de l’intérieur. &lt;/p&gt; &#10; &lt;audio controls title= &quot;La modernité peut elle survivre aux religions par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-29.06.2012-ITEMA_20381664-2012C6608S0181-NET_9F56B454-BEBB-469E-974A-6F8782D1D7B5_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E7" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Searle&quot;  title=&quot; Wikipedia&quot;&gt;John SEARLE&lt;/a&gt; est un philosophe américain  connu pour ses travaux influents dans plusieurs domaines, notamment la philosophie du langage, la philosophie de l'esprit et la philosophie sociale. Il  a développé et systématisé la théorie des &lt;a href=&quot;https://www.youtube.com/watch?v=pIbkpLfrD6A&quot; title=&quot;&#10;La théorie des actes de langage (2) - John Searle par Heraut du Mont Parnasse&quot;&gt;actes de langage&lt;/a&gt; car, pour lui, parler une langue, ce n'est pas seulement émettre des sons ou des suites de symboles, mais accomplir des actions. &lt;/p&gt; &lt;p&gt; Défenseur du &quot;naturalisme biologique&quot; en philosophie de l'esprit. Il s'oppose au dualisme cartésien tout en refusant le matérialisme réducteur qui nierait l'existence de &lt;a href=&quot;https://www.youtube.com/watch?v=EriAhi0mj7w&quot; title=&quot; Conscience et matière grise par TEDx Talks&quot;&gt;la conscience&lt;/a&gt; ou la réduirirait à de simples phénomènes physiques. Pour lui, les états mentaux (douleur, croyances, désirs, conscience) sont des phénomènes  &lt;a href=&quot;https://www.youtube.com/watch?v=Bq2bfSzkTfU&quot;  title=&quot;John Searle - Une personne peut-elle être une âme ? par Closer To Truth&quot;&gt;biologiques réels&lt;/a&gt; , causés par des processus neuronaux du cerveau, mais ils ne sont pas réductibles à ces processus au sens où ils émergent à un niveau supérieur et possèdent des propriétés irréductibles.&lt;/p&gt; &lt;p&gt; L'une des ses contributions les plus célèbres est son argument de la &lt;a href=&quot;https://www.youtube.com/watch?v=P5DtwDr9YEc&quot; title=&quot; La Chambre chinoise par Ian et frank&quot;&gt;Chambre Chinoise&lt;/a&gt; . Cet argument vise à réfuter la thèse de l'IA forte (position selon laquelle un ordinateur programmé de manière appropriée n'est pas seulement un outil pour l'étude de l'esprit, mais qu'il est véritablement un esprit, capable de comprendre et de posséder d'autres états cognitifs) opposé à l'IA faible (position selon laquelle les ordinateurs sont des outils utiles pour étudier l'esprit, mais qu'ils ne sont pas eux-mêmes des esprits). &lt;/p&gt; &lt;p&gt; Dans son ouvrage &lt;a href=&quot;https://labo.nonmarchand.org/pmwiki/uploads/Textes/JohnSearleLaConstructionDeLaRealiteSociale/JohnSearle_LaConstructionDeLaRealiteSociale.pdf&quot;  title=&quot; La construction e la réalité sociale par nonmarchand&quot;&gt;&quot;La Construction de la Réalité Sociale&quot;&lt;/a&gt;, il étend sa théorie des actes de langage et de l'intentionnalité pour expliquer comment nous construisons des faits institutionnels et sociaux. Il distingue les &quot;Faits bruts&quot; qui existent indépendamment de toute institution humaine (par exemple, la montagne Everest) des &quot;Faits institutionnels&quot; qui n'existent qu'en vertu d'institutions humaines et de l'accord collectif (par exemple, l'argent, le mariage, la propriété). &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E9" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Swinburne&quot; title=&quot; Wikipedia&quot;&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H9" r:id="rId5" display="https://www.laphilo.fr/pho/rswinburne-mini.webp"/>
-    <hyperlink ref="H10" r:id="rId6" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
-    <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
-    <hyperlink ref="H14" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
-    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alison_Jaggar&quot;  title=&quot; Wikipedia&quot;&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href=&quot;https://journals.openedition.org/lectures/15257?lang=es&quot;  title=&quot;alison jaggar ; gender and global justice par openedition &quot;&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H18" r:id="rId11" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
-    <hyperlink ref="E19" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
-    <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
-    <hyperlink ref="E24" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H24" r:id="rId15" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
-    <hyperlink ref="H25" r:id="rId16" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
-    <hyperlink ref="E27" r:id="rId17" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H30" r:id="rId18" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
-    <hyperlink ref="E31" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
-    <hyperlink ref="E32" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H33" r:id="rId21" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
-    <hyperlink ref="I33" r:id="rId22" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
-    <hyperlink ref="H34" r:id="rId23" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
-    <hyperlink ref="E38" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H38" r:id="rId25" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
-    <hyperlink ref="E40" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
-    <hyperlink ref="E41" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H42" r:id="rId28" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H44" r:id="rId30" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
-    <hyperlink ref="H45" r:id="rId32" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
-    <hyperlink ref="E46" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E47" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H50" r:id="rId35" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
-    <hyperlink ref="E57" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E59" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
-    <hyperlink ref="H59" r:id="rId38" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
-    <hyperlink ref="E61" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E64" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E66" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="E67" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
-    <hyperlink ref="E68" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
-    <hyperlink ref="H68" r:id="rId44" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
-    <hyperlink ref="I68" r:id="rId45" display="https://www.laphilo.fr/photo/tarassov.webp"/>
-    <hyperlink ref="E69" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
-    <hyperlink ref="E72" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Gedefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H72" r:id="rId48" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
-    <hyperlink ref="H75" r:id="rId49" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
-    <hyperlink ref="H76" r:id="rId50" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
-    <hyperlink ref="H78" r:id="rId51" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
-    <hyperlink ref="I78" r:id="rId52" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
-    <hyperlink ref="E81" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H81" r:id="rId54" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
-    <hyperlink ref="E82" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRAND&lt;/a&gt; est un philosophe britanique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
-    <hyperlink ref="E84" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="H87" r:id="rId57" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E88" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Jennifer_Saul&quot; title=&quot; Wikipedia&quot;&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe américaine  spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href=&quot;https://www.youtube.com/watch?v=2_FqrHs9S-s&quot; title=&quot;Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy&quot;&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre &quot;Lying, Misleading, and What Is Said&quot; aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &quot;Feminism: Issues &amp; Arguments&quot;, elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le &quot;Women in Philosophy Task Force&quot; au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href=&quot;https://www.youtube.com/watch?v=QDcuCIqCWdQ&quot; s title=&quot; Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy&quot;&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; "/>
-    <hyperlink ref="E90" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H91" r:id="rId60" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E94" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E95" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E97" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId64" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E101" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E104" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E8" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Swinburne&quot; title=&quot; Wikipedia&quot;&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H8" r:id="rId4" display="https://www.laphilo.fr/pho/rswinburne-mini.webp"/>
+    <hyperlink ref="H9" r:id="rId5" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
+    <hyperlink ref="E10" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
+    <hyperlink ref="H12" r:id="rId8" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
+    <hyperlink ref="E16" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alison_Jaggar&quot;  title=&quot; Wikipedia&quot;&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href=&quot;https://journals.openedition.org/lectures/15257?lang=es&quot;  title=&quot;alison jaggar ; gender and global justice par openedition &quot;&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H16" r:id="rId10" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
+    <hyperlink ref="E17" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
+    <hyperlink ref="H19" r:id="rId12" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
+    <hyperlink ref="E22" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H22" r:id="rId14" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
+    <hyperlink ref="H23" r:id="rId15" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
+    <hyperlink ref="E25" r:id="rId16" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H28" r:id="rId17" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
+    <hyperlink ref="E29" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
+    <hyperlink ref="E30" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H31" r:id="rId20" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
+    <hyperlink ref="I31" r:id="rId21" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
+    <hyperlink ref="H32" r:id="rId22" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
+    <hyperlink ref="E36" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H36" r:id="rId24" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
+    <hyperlink ref="E38" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
+    <hyperlink ref="E39" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H40" r:id="rId27" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H42" r:id="rId29" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
+    <hyperlink ref="E43" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
+    <hyperlink ref="H43" r:id="rId31" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
+    <hyperlink ref="E44" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E45" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H48" r:id="rId34" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
+    <hyperlink ref="E55" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E57" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
+    <hyperlink ref="H57" r:id="rId37" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
+    <hyperlink ref="E59" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E62" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E64" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="E65" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
+    <hyperlink ref="E66" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
+    <hyperlink ref="H66" r:id="rId43" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
+    <hyperlink ref="I66" r:id="rId44" display="https://www.laphilo.fr/photo/tarassov.webp"/>
+    <hyperlink ref="E67" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
+    <hyperlink ref="E70" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Godefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H70" r:id="rId47" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
+    <hyperlink ref="H73" r:id="rId48" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
+    <hyperlink ref="H74" r:id="rId49" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
+    <hyperlink ref="H76" r:id="rId50" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
+    <hyperlink ref="I76" r:id="rId51" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
+    <hyperlink ref="E79" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H79" r:id="rId53" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
+    <hyperlink ref="E80" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRANT&lt;/a&gt; est un philosophe britannique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
+    <hyperlink ref="E82" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="H85" r:id="rId56" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
+    <hyperlink ref="E86" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Jennifer_Saul&quot; title=&quot; Wikipedia&quot;&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe américaine  spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href=&quot;https://www.youtube.com/watch?v=2_FqrHs9S-s&quot; title=&quot;Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy&quot;&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre &quot;Lying, Misleading, and What Is Said&quot; aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &quot;Feminism: Issues &amp; Arguments&quot;, elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le &quot;Women in Philosophy Task Force&quot; au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href=&quot;https://www.youtube.com/watch?v=QDcuCIqCWdQ&quot; s title=&quot; Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy&quot;&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; "/>
+    <hyperlink ref="E88" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H89" r:id="rId59" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E92" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E93" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E95" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E98" r:id="rId63" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E99" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E102" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; continental</t>
+          <t xml:space="preserve">critique ; continental</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">continental ; art</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; genre</t>
+          <t xml:space="preserve">critique ; genre</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
+          <t xml:space="preserve">reel ; art</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; continental</t>
+          <t xml:space="preserve">critique ; continental</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; continental</t>
+          <t xml:space="preserve">critique ; continental</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; genre</t>
+          <t xml:space="preserve">critique ; genre</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens ; continental</t>
+          <t xml:space="preserve">sens ; continental ; art</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; justice</t>
+          <t xml:space="preserve">genre ; critique</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="Q63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">decolonial ; justice</t>
+          <t xml:space="preserve">decolonial ; critique</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">esprit-ia ; justice</t>
+          <t xml:space="preserve">esprit-ia ; critique</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="Q107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; justice</t>
+          <t xml:space="preserve">genre ; critique</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3623,312 +3623,318 @@
       <c r="XFC8" s="0"/>
       <c r="XFD8" s="0"/>
     </row>
-    <row r="9" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdallah_Laroui" title=" Wikipedia"&gt;Abdallah LAROUI&lt;/a&gt; est un historien, philosophe et romancier marocain né à Azemmour. Après des études à Rabat et à Paris, il enseigne l'histoire à l'université Mohammed V de Rabat pendant plus de trente ans. Il écrit en français et en arabe, et a traduit en arabe des textes de Rousseau et de Montesquieu. Il est aussi l'auteur d'une&lt;a href="https://www.persee.fr/doc/ahess_0395-2649_2002_num_57_1_280038_t1_0212_0000_1" title="Abdallah Laroui Islam et histoire par persée"&gt; &lt;em&gt;Histoire du Maghreb&lt;/em&gt;&lt;/a&gt; (1970) et de plusieurs romans.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;L'Idéologie arabe contemporaine&lt;/em&gt; (1967), paraît l'année de la défaite arabe face à Israël et devient une référence. Il y décrit trois figures qui, depuis un siècle, répondent chacune à sa façon au défi de l'Occident : le clerc, qui cherche le salut dans le retour à la religion ; le politicien libéral, qui l'attend de la démocratie ; le technophile, qui ne croit qu'à la science et à l'industrie. Aucune, selon lui, ne pense vraiment la situation.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Crise des intellectuels arabes&lt;/em&gt; (1974), il oppose deux attitudes : le traditionalisme, qui cherche dans le passé des réponses toutes faites, et l'&lt;a href="https://fr.wikipedia.org/wiki/Historicisme" title=" Wikipedia"&gt;historicisme&lt;/a&gt;, qu'il défend. Être historiciste, c'est admettre que l'histoire a un sens, que la modernité née en Europe est un acquis de toute l'humanité, et qu'un peuple en retard doit en assimiler les principes : raison, liberté, État, sans croire pouvoir s'en dispenser. Le marxisme l'intéresse surtout comme le résumé de cette pensée moderne.&lt;/p&gt; &lt;p&gt;Il plaide ainsi pour une rupture nette avec l'héritage, là où son compatriote al-Jabri proposait de le relire. Il a poursuivi ce travail dans une série d'ouvrages en arabe, chacun consacré à un concept : l'idéologie, la liberté, l'État, l'histoire, la raison.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w90MiZMUuxA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"فلسفة عبد الله العروي: لماذا فشل العرب في دخول الحداثة؟" par الفلسفة للنوم</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/abdallahlaroui-mini.webp</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="n">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="n">
         <v>1934</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H10" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="1" t="s">
+      <c r="I10" s="10"/>
+      <c r="J10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="O10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="11" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>1936</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="O11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+    <row r="12" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
         <v>1937</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>1938</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="7" t="n">
-        <v>1940</v>
+      <c r="C13" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>123</v>
+        <v>112</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="1" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>126</v>
+        <v>115</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
-        <v>128</v>
+      <c r="C14" s="7" t="n">
+        <v>1940</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>130</v>
+        <v>119</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>133</v>
+        <v>122</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="1" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>126</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="1" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>1942</v>
       </c>
@@ -3937,130 +3943,130 @@
         <v>140</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>151</v>
+        <v>141</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>142</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>1942</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="7" t="n">
-        <v>1942</v>
+      <c r="C17" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>159</v>
+        <v>150</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="1" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>41</v>
+        <v>155</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
-        <v>165</v>
+      <c r="C18" s="7" t="n">
+        <v>1942</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>170</v>
+        <v>161</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>162</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="198.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>1943</v>
       </c>
@@ -4069,133 +4075,130 @@
         <v>165</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>175</v>
+        <v>166</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>167</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>124</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="371.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="198.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>1943</v>
       </c>
       <c r="B20" s="7"/>
-      <c r="C20" s="7" t="n">
-        <v>1943</v>
+      <c r="C20" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="1" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>188</v>
+        <v>155</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="371.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B21" s="7"/>
-      <c r="C21" s="7" t="s">
-        <v>189</v>
+      <c r="C21" s="7" t="n">
+        <v>1943</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>191</v>
+        <v>180</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>194</v>
+        <v>183</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="1" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>41</v>
+        <v>187</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>188</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>1944</v>
       </c>
@@ -4204,84 +4207,87 @@
         <v>189</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>200</v>
+        <v>190</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>1944</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="7" t="n">
-        <v>1944</v>
+      <c r="C23" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="261" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>1944</v>
       </c>
@@ -4290,168 +4296,165 @@
         <v>1944</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="1" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>222</v>
+        <v>171</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="261" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>1944</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>227</v>
-      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="I25" s="10"/>
       <c r="J25" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>222</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P25" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Q25" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="B26" s="7"/>
+        <v>1944</v>
+      </c>
       <c r="C26" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>233</v>
+        <v>189</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="I26" s="10"/>
+        <v>224</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="J26" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="P26" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="Q26" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>242</v>
+        <v>233</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>234</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="1" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>106</v>
@@ -4460,406 +4463,412 @@
         <v>29</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
-        <v>1947</v>
-      </c>
-      <c r="B28" s="7"/>
+        <v>1945</v>
+      </c>
       <c r="C28" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="I28" s="10"/>
+        <v>232</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdolkarim_Soroush" title=" Wikipedia"&gt;Abdolkarim SOROUSH&lt;/a&gt;, nom de plume de Hossein Haj Faraj Dabbagh, est un philosophe iranien né à Téhéran en 1945. Pharmacien de formation, il étudie à Londres la chimie, puis l'histoire et la philosophie des sciences, où il découvre Karl Popper. Rentré en Iran à la révolution de 1979, il siège au conseil chargé de réorganiser les universités, qu'il quitte en 1983. Il devient dans les années 1990 la principale voix des intellectuels réformateurs.&lt;/p&gt; &lt;p&gt;Sa thèse la plus connue est exposée dans&lt;a href="https://www.youtube.com/watch?v=clvyL4BgHEo" title="Explaining Why the Qur'an has Ambiguities par exploring Quran &amp;amp; Bible"&gt; &lt;/a&gt;&lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=clvyL4BgHEo"&gt;La Contraction &lt;/a&gt;et l'expansion théoriques de la charia&lt;/em&gt; (1990). Il y distingue la religion elle-même, d'origine divine, et la connaissance que les hommes en ont. Cette connaissance est humaine, faillible et historique : elle dépend de tout ce que nous savons par ailleurs, en science, en histoire ou en philosophie, et change donc avec les époques. Personne ne peut dès lors prétendre détenir l'interprétation définitive, pas même le clergé.&lt;/p&gt; &lt;p&gt;Il en tire une critique du pouvoir religieux : faire de la religion une idéologie d'État, c'est la figer et la corrompre. Un gouvernement peut être à la fois religieux et démocratique, mais seulement s'il respecte la liberté de croire et les droits de l'homme. Il rejette ainsi le principe iranien du gouvernement du juriste-théologien.&lt;/p&gt; &lt;p&gt;Il a ensuite soutenu que la révélation porte la marque de la personnalité et de l'époque du Prophète. Grand lecteur du poète mystique Rumi, il a été agressé et empêché d'enseigner, puis a quitté l'Iran vers 2000 pour les universités américaines et européennes. Il a reçu le prix Érasme en 2004. Il partagea ce prix avec la sociologue marocaine Fatima Mernissi.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1DHv1b73p5c</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Abdolkarim Soroush" par IDOS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/abdolkarimsoroush-mini.webp</t>
+        </is>
+      </c>
       <c r="J28" s="1" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>50</v>
+        <v>853</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>95</v>
+        <v>854</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>259</v>
+        <v>241</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>242</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="1" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>61</v>
+        <v>246</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
         <v>1947</v>
       </c>
       <c r="B30" s="7"/>
-      <c r="C30" s="7" t="n">
-        <v>1947</v>
+      <c r="C30" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>266</v>
+        <v>250</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>269</v>
+        <v>253</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>272</v>
+        <v>255</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="227.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>275</v>
+        <v>258</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>279</v>
+        <v>263</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
-        <v>273</v>
+      <c r="C32" s="7" t="n">
+        <v>1947</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>281</v>
+        <v>265</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>266</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>284</v>
+        <v>268</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>269</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>124</v>
+        <v>270</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>41</v>
+        <v>271</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>272</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
         <v>1948</v>
       </c>
       <c r="B33" s="7"/>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D35" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E35" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="14" t="s">
+      <c r="F35" s="7"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I35" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+    <row r="36" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C36" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q34" s="2" t="s">
+      <c r="O36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q36" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="177.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>1949</v>
       </c>
@@ -4868,84 +4877,87 @@
         <v>304</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="1" t="s">
-        <v>25</v>
+        <v>310</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="7" t="n">
-        <v>1949</v>
+      <c r="C38" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>328</v>
+        <v>313</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>331</v>
+        <v>316</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="1" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>332</v>
+        <v>204</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>333</v>
+        <v>319</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>1949</v>
       </c>
@@ -4954,176 +4966,176 @@
         <v>304</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>335</v>
+        <v>321</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="1" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>339</v>
+        <v>50</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>340</v>
+        <v>255</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>106</v>
+        <v>326</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>342</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B40" s="7"/>
-      <c r="C40" s="7" t="s">
-        <v>343</v>
+      <c r="C40" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>345</v>
+        <v>327</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>348</v>
+        <v>330</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>331</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="1" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>125</v>
+        <v>332</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>95</v>
+        <v>333</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>352</v>
+        <v>334</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>335</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="1" t="s">
-        <v>356</v>
+        <v>91</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>103</v>
+        <v>339</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>171</v>
+        <v>340</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>357</v>
+        <v>341</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="7" t="n">
-        <v>1950</v>
+      <c r="C42" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>360</v>
+        <v>344</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>345</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>363</v>
+        <v>347</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>348</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>366</v>
+        <v>125</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>1950</v>
       </c>
@@ -5132,41 +5144,41 @@
         <v>343</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>368</v>
+        <v>351</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>352</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>37</v>
+        <v>356</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1950</v>
       </c>
@@ -5175,182 +5187,176 @@
         <v>1950</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>95</v>
+        <v>365</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>366</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>382</v>
+      <c r="C45" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>368</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>385</v>
+        <v>370</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>371</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
-        <v>291</v>
+        <v>37</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>386</v>
+        <v>196</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>106</v>
+        <v>372</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="7" t="s">
-        <v>388</v>
+      <c r="C46" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>390</v>
+        <v>373</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>393</v>
+        <v>376</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>38</v>
+        <v>378</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B47" s="7"/>
-      <c r="C47" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>398</v>
+      <c r="C47" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>382</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>401</v>
+        <v>384</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>385</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="1" t="s">
-        <v>91</v>
+        <v>291</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
         <v>1952</v>
       </c>
@@ -5359,44 +5365,44 @@
         <v>388</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>405</v>
+        <v>389</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>1952</v>
       </c>
@@ -5405,176 +5411,176 @@
         <v>388</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>412</v>
+        <v>397</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>398</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>417</v>
+        <v>403</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B50" s="7"/>
-      <c r="C50" s="7" t="n">
-        <v>1952</v>
+      <c r="C50" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>419</v>
+        <v>404</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>422</v>
+        <v>407</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>408</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="M50" s="15" t="s">
-        <v>424</v>
+        <v>409</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>427</v>
+        <v>411</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>412</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>61</v>
+        <v>416</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>41</v>
+        <v>417</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B52" s="7"/>
-      <c r="C52" s="7" t="s">
-        <v>425</v>
+      <c r="C52" s="7" t="n">
+        <v>1952</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>433</v>
+        <v>418</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>419</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>436</v>
+        <v>421</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>422</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>117</v>
+        <v>423</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
         <v>1953</v>
       </c>
@@ -5583,44 +5589,44 @@
         <v>425</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>445</v>
+        <v>61</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
         <v>1953</v>
       </c>
@@ -5629,130 +5635,133 @@
         <v>425</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>448</v>
+        <v>432</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>433</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>292</v>
+        <v>50</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>453</v>
+        <v>438</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>460</v>
+        <v>91</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>452</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
         <v>1954</v>
       </c>
@@ -5761,41 +5770,44 @@
         <v>454</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>472</v>
+        <v>455</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>456</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>477</v>
+        <v>38</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>125</v>
+        <v>461</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>478</v>
+        <v>462</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
         <v>1954</v>
       </c>
@@ -5804,170 +5816,170 @@
         <v>454</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>480</v>
+        <v>464</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>465</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>484</v>
+        <v>92</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B59" s="7"/>
-      <c r="C59" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>489</v>
+      <c r="C59" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>472</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>492</v>
+        <v>474</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>475</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>291</v>
+        <v>476</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>70</v>
+        <v>477</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>493</v>
+        <v>125</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7" t="s">
-        <v>495</v>
+        <v>454</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>497</v>
+        <v>479</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
         <v>80</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>301</v>
+        <v>484</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>125</v>
+        <v>485</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>503</v>
+      <c r="C61" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>489</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>506</v>
+        <v>491</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>492</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="1" t="s">
-        <v>507</v>
+        <v>291</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>508</v>
+        <v>70</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>117</v>
+        <v>295</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
         <v>1955</v>
       </c>
@@ -5976,121 +5988,118 @@
         <v>495</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>402</v>
+        <v>125</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>95</v>
+        <v>501</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B63" s="7"/>
-      <c r="C63" s="7" t="n">
-        <v>1955</v>
+      <c r="C63" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>519</v>
+        <v>502</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>503</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="1" t="s">
-        <v>91</v>
+        <v>507</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>124</v>
+        <v>508</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>196</v>
+        <v>509</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>526</v>
+        <v>512</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>513</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>196</v>
+        <v>402</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>95</v>
@@ -6099,269 +6108,272 @@
         <v>29</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="7" t="s">
-        <v>531</v>
+      <c r="C65" s="7" t="n">
+        <v>1955</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>533</v>
+        <v>518</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>537</v>
+        <v>196</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="7" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>541</v>
+        <v>525</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>526</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>545</v>
+        <v>50</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>546</v>
+        <v>196</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>547</v>
+        <v>530</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="E67" s="20" t="s">
-        <v>549</v>
+      <c r="C67" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>533</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="1" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>220</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>295</v>
+        <v>117</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>139</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>558</v>
-      </c>
+      <c r="C68" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="I68" s="10"/>
       <c r="J68" s="1" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>220</v>
+        <v>545</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>562</v>
+      <c r="C69" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>548</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>549</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>134</v>
+        <v>291</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>138</v>
+        <v>295</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B70" s="7"/>
-      <c r="C70" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="I70" s="10"/>
+      <c r="C70" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>558</v>
+      </c>
       <c r="J70" s="1" t="s">
-        <v>25</v>
+        <v>291</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>238</v>
+        <v>553</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
         <v>1958</v>
       </c>
@@ -6370,830 +6382,827 @@
         <v>560</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>575</v>
+        <v>561</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>562</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="1" t="s">
-        <v>476</v>
+        <v>134</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>402</v>
+        <v>566</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="7" t="n">
-        <v>1958</v>
+      <c r="C72" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>581</v>
+        <v>568</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>569</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="H72" s="14" t="s">
-        <v>584</v>
+        <v>571</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>572</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>50</v>
+        <v>349</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="M72" s="15" t="s">
-        <v>586</v>
+        <v>238</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7" t="s">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>589</v>
+        <v>574</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>575</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="1" t="s">
-        <v>318</v>
+        <v>476</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>41</v>
+        <v>579</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="7" t="s">
-        <v>587</v>
+      <c r="C74" s="7" t="n">
+        <v>1958</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>595</v>
+        <v>580</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>581</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>598</v>
+        <v>583</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>584</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="1" t="s">
-        <v>599</v>
+        <v>114</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>50</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>29</v>
+        <v>585</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>586</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B75" s="7"/>
-      <c r="C75" s="7" t="n">
-        <v>1960</v>
+      <c r="C75" s="7" t="s">
+        <v>587</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="E75" s="21" t="s">
-        <v>602</v>
+        <v>588</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>589</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>604</v>
-      </c>
-      <c r="H75" s="14" t="s">
-        <v>605</v>
+        <v>591</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>592</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="1" t="s">
-        <v>606</v>
+        <v>318</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>607</v>
+        <v>103</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="M75" s="15" t="s">
-        <v>609</v>
+        <v>204</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>41</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="I76" s="1"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="I76" s="10"/>
       <c r="J76" s="1" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>616</v>
+      <c r="L76" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>617</v>
+        <v>600</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B77" s="7"/>
-      <c r="C77" s="7" t="s">
-        <v>619</v>
+      <c r="C77" s="7" t="n">
+        <v>1960</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>621</v>
+        <v>601</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>602</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>624</v>
+        <v>604</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>605</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="1" t="s">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>220</v>
+        <v>607</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>626</v>
+        <v>608</v>
+      </c>
+      <c r="M77" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
         <v>1961</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="F78" s="7"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="14" t="s">
-        <v>629</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>630</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q78" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1962</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="1" t="s">
-        <v>318</v>
+        <v>625</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>255</v>
+        <v>27</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="7" t="s">
-        <v>632</v>
+      <c r="C80" s="7" t="n">
+        <v>1961</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>640</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="I80" s="10"/>
+        <v>628</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>630</v>
+      </c>
       <c r="J80" s="1" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>644</v>
+        <v>125</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B81" s="7"/>
-      <c r="C81" s="7" t="n">
-        <v>1962</v>
+      <c r="C81" s="7" t="s">
+        <v>632</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>647</v>
+        <v>633</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>634</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="H81" s="14" t="s">
-        <v>650</v>
+        <v>636</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>637</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="1" t="s">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>651</v>
+        <v>50</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>652</v>
+        <v>255</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="O81" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>657</v>
+        <v>639</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>640</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>661</v>
+        <v>50</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>566</v>
+        <v>644</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>662</v>
+        <v>645</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B83" s="7"/>
-      <c r="C83" s="7" t="s">
-        <v>663</v>
+      <c r="C83" s="7" t="n">
+        <v>1962</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>665</v>
+        <v>646</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>647</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>668</v>
+        <v>649</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>650</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>124</v>
+        <v>651</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="O83" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>50</v>
+        <v>661</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>255</v>
+        <v>566</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>661</v>
+        <v>124</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>687</v>
+        <v>672</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>673</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>691</v>
+        <v>255</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7" t="n">
-        <v>1966</v>
+      <c r="C87" s="7" t="s">
+        <v>671</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="H87" s="14" t="s">
-        <v>697</v>
+        <v>681</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>682</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
-        <v>698</v>
+        <v>80</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>92</v>
+        <v>661</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>703</v>
+        <v>686</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>687</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>707</v>
+        <v>349</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>41</v>
+        <v>692</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="7" t="s">
-        <v>701</v>
+      <c r="C89" s="7" t="n">
+        <v>1966</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>715</v>
+        <v>696</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>697</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>80</v>
+        <v>698</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>292</v>
+        <v>92</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
         <v>1968</v>
       </c>
@@ -7202,606 +7211,606 @@
         <v>701</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>364</v>
+        <v>707</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>725</v>
+        <v>709</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="7" t="n">
-        <v>1968</v>
+      <c r="C91" s="7" t="s">
+        <v>701</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>727</v>
+        <v>711</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>712</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="H91" s="14" t="s">
-        <v>730</v>
+        <v>714</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>715</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>734</v>
+        <v>719</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>720</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>545</v>
+        <v>364</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>125</v>
+        <v>724</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B93" s="7"/>
-      <c r="C93" s="7" t="s">
-        <v>739</v>
+      <c r="C93" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>741</v>
+        <v>726</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>727</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>744</v>
+        <v>729</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>730</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>745</v>
+        <v>318</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>125</v>
+        <v>699</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>41</v>
+        <v>731</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7" t="s">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>749</v>
+        <v>733</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>734</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>661</v>
+        <v>545</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>566</v>
+        <v>125</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>756</v>
+        <v>739</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>741</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>507</v>
+        <v>745</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="M95" s="15" t="s">
-        <v>761</v>
+        <v>125</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>764</v>
+        <v>748</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>749</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>768</v>
+        <v>25</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>545</v>
+        <v>661</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>769</v>
+        <v>566</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>770</v>
+        <v>753</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>772</v>
+        <v>754</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>755</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>773</v>
+        <v>756</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>774</v>
+        <v>757</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>775</v>
+        <v>758</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>776</v>
+        <v>759</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>91</v>
+        <v>507</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>777</v>
+        <v>760</v>
+      </c>
+      <c r="M97" s="15" t="s">
+        <v>761</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>80</v>
+        <v>768</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>349</v>
+        <v>545</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="M98" s="15" t="s">
-        <v>784</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>41</v>
+        <v>769</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>770</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>787</v>
+        <v>772</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>773</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>791</v>
+        <v>125</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>138</v>
+        <v>777</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>796</v>
+        <v>779</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>780</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>661</v>
+        <v>349</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>800</v>
+        <v>708</v>
+      </c>
+      <c r="M100" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>802</v>
+        <v>786</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>787</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>545</v>
+        <v>70</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>125</v>
+        <v>791</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>807</v>
+        <v>138</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>810</v>
+        <v>795</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>796</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>768</v>
+        <v>25</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>545</v>
+        <v>661</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>125</v>
+        <v>683</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="O102" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>817</v>
+        <v>801</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>802</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="1" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>38</v>
+        <v>545</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>125</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>41</v>
+        <v>807</v>
       </c>
       <c r="O103" s="1" t="s">
         <v>29</v>
@@ -7810,32 +7819,32 @@
         <v>96</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>824</v>
+        <v>809</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>810</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="1" t="s">
-        <v>80</v>
+        <v>768</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>545</v>
@@ -7844,195 +7853,220 @@
         <v>125</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="N104" s="1" t="s">
-        <v>41</v>
+        <v>814</v>
       </c>
       <c r="O104" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="199.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="1" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>835</v>
+        <v>125</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>836</v>
+        <v>821</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O105" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="n">
-        <v>1990</v>
+        <v>1984</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7" t="s">
-        <v>838</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>839</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>840</v>
+        <v>822</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>824</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="I107" s="10"/>
+      <c r="J107" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q107" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="I108" s="10"/>
+      <c r="J108" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K106" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L106" s="2" t="s">
+      <c r="L108" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="M108" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="N106" s="1" t="s">
+      <c r="N108" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O106" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q106" s="2" t="s">
+      <c r="O108" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q108" s="2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="Q107" s="1"/>
-    </row>
-    <row r="108" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0"/>
-      <c r="B108" s="0"/>
-      <c r="C108" s="0"/>
-      <c r="D108" s="0"/>
-      <c r="E108" s="0"/>
-      <c r="F108" s="0"/>
-      <c r="G108" s="0"/>
-      <c r="H108" s="0"/>
-      <c r="I108" s="0"/>
-      <c r="J108" s="0"/>
-      <c r="K108" s="0"/>
-      <c r="L108" s="0"/>
-      <c r="M108" s="0"/>
-      <c r="P108" s="0"/>
-      <c r="Q108" s="0"/>
-    </row>
-    <row r="109" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="M109" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q109" s="2" t="s">
-        <v>850</v>
-      </c>
+    <row r="109" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="Q109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>851</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>852</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M110" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>855</v>
-      </c>
+      <c r="A110" s="0"/>
+      <c r="B110" s="0"/>
+      <c r="C110" s="0"/>
+      <c r="D110" s="0"/>
+      <c r="E110" s="0"/>
+      <c r="F110" s="0"/>
+      <c r="G110" s="0"/>
+      <c r="H110" s="0"/>
+      <c r="I110" s="0"/>
+      <c r="J110" s="0"/>
+      <c r="K110" s="0"/>
+      <c r="L110" s="0"/>
+      <c r="M110" s="0"/>
+      <c r="P110" s="0"/>
+      <c r="Q110" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8043,70 +8077,70 @@
     <hyperlink ref="E4" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Hermann_L%C3%BCbbe&quot; title=&quot; Wikipedia&quot;&gt;Hermann LUBBE&lt;/a&gt; est un philosophe allemand dont l'œuvre se concentre sur une théorie de la civilisation moderne et de la démocratie libérale. Figure marquante du paysage intellectuel d'après-guerre, il s'est fait connaître en analysant les bouleversements de la société dynamique et en s'opposant fermement aux mouvements de protestation de 1968, ce qui lui a valu d'être perçu comme l'un des principaux représentants du &lt;a href=&quot;https://www.persee.fr/doc/reval_0035-0974_1988_num_20_1_3302&quot; title=&quot;Le néoconservatisme par persée&quot;&gt; néoconservatisme allemand. &lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Sa pensée se définit comme une « philosophie après les Lumières », cherchant à sécuriser les acquis du libéralisme tout en rejetant les grandes théories historiques totalisantes. Plutôt que de proposer des projets idéologiques, il privilégie une approche pragmatique qui examine la réalité sous l'angle de l'action pratique et de la résolution de problèmes. Cette méthode valorise le sens commun, la pratique quotidienne et une attention particulière à l'individu dans sa dimension contingente. &lt;/p&gt; &lt;p&gt; Il a développé une réflexion approfondie sur la dialectique entre le progrès technique et la stabilité sociale. Face à l'accélération constante du changement social, il insiste sur l'importance irremplaçable des traditions, des conventions et des institutions stables pour offrir une orientation aux citoyens. Pour lui, ces éléments ne sont pas des freins au progrès, mais des conditions nécessaires pour permettre aux individus de faire face à la complexité et à l'imprévisibilité du monde moderne. &lt;/p&gt; &lt;p&gt; La question de la religion occupe une place centrale dans sa réflexion sur la modernité, qu'il considère comme une ressource essentielle pour donner du sens à l'existence face à la contingence. Il soutient que, malgré le recul des dogmes institutionnels, la religion demeure une composante indispensable de la conscience humaine. À travers &lt;a href=&quot;https://www.persee.fr/doc/rscir_0035-2217_1988_num_62_1_3090_t1_0082_0000_3&quot; title=&quot;Fortdchrittsreaktionen par persée&quot;&gt;ses écrits, &lt;/a&gt; comme dans Sphären der Menschlichkeit, il explore la fragilité de la condition humaine face aux défis technologiques, plaidant pour une approche qui maintient la dignité et l'identité des sujets dans un monde en mutation permanente. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E6" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Taylor_(philosophe)&quot;  title=&quot; Wikipedia&quot;&gt;Charles TAYLOR&lt;/a&gt; est un philosophe canadien connu pour ses travaux sur l’identité, la modernité, la morale et la reconnaissance. Il s’intéresse moins à des vérités abstraites qu’à la manière dont les êtres humains donnent du sens à leur vie dans des contextes historiques et culturels précis. &lt;/p&gt; &lt;p&gt; Sa philosophie critique d’abord l’idée d’un  &lt;a href=&quot;https://laviedesidees.fr/Charles-Taylor-philosophe-de-la&quot; title=&quot;Charles Taylor par la vie des idées&quot;&gt; individu totalement autonome &lt;/a&gt; et isolé. Il soutient que le moi se construit toujours dans un « horizon moral », c’est-à-dire à travers des valeurs, des langages et des relations qui le dépassent; on ne comprend donc pas une personne sans comprendre le monde partagé dans lequel elle vit. &lt;/p&gt; &lt;p&gt; Un de ses apports majeurs est la notion de reconnaissance. Il explique que chacun a besoin d’être reconnu dans sa singularité, par exemple dans son identité culturelle, linguistique ou religieuse, et il défend ainsi une politique qui respecte les différences sans tomber dans le repli communautaire. Il cherche donc  &lt;a href=&quot;https://www.youtube.com/watch?v=Drd0UT-BcGU&quot; title=&quot;Charles Taylor par Sociologie de l’intégration&quot;&gt; un équilibre entre l’universel &lt;/a&gt; et le particulier, entre les droits communs et la valeur des appartenances. &lt;/p&gt; &lt;p&gt; Il critique le réductionnisme des sciences humaines et l’idée que la raison humaine serait seulement calculatrice ou « désengagée ». Il privilégie une approche interprétative de l’être humain, inspirée de   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Herm%C3%A9neutique&quot; title=&quot;Herméneutique par Wikipedia&quot;&gt; l’herméneutique, &lt;/a&gt;  selon laquelle comprendre une action, une croyance ou une identité demande d’en saisir le sens vécu de l’intérieur. &lt;/p&gt; &#10; &lt;audio controls title= &quot;La modernité peut elle survivre aux religions par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10075-29.06.2012-ITEMA_20381664-2012C6608S0181-NET_9F56B454-BEBB-469E-974A-6F8782D1D7B5_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="H8" r:id="rId3" display="https://www.laphilo.fr/pho/shnasr-mini.webp"/>
-    <hyperlink ref="E9" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Swinburne&quot; title=&quot; Wikipedia&quot;&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H9" r:id="rId5" display="https://www.laphilo.fr/pho/rswinburne-mini.webp"/>
-    <hyperlink ref="H10" r:id="rId6" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
-    <hyperlink ref="E11" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E12" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
-    <hyperlink ref="H13" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
-    <hyperlink ref="E17" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alison_Jaggar&quot;  title=&quot; Wikipedia&quot;&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href=&quot;https://journals.openedition.org/lectures/15257?lang=es&quot;  title=&quot;alison jaggar ; gender and global justice par openedition &quot;&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H17" r:id="rId11" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
-    <hyperlink ref="E18" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
-    <hyperlink ref="H20" r:id="rId13" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
-    <hyperlink ref="E23" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H23" r:id="rId15" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
-    <hyperlink ref="H24" r:id="rId16" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
-    <hyperlink ref="H25" r:id="rId17" display="https://www.laphilo.fr/pho/adavis-mini.webp"/>
-    <hyperlink ref="E27" r:id="rId18" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H30" r:id="rId19" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
-    <hyperlink ref="E31" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
-    <hyperlink ref="E32" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H33" r:id="rId22" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
-    <hyperlink ref="I33" r:id="rId23" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
-    <hyperlink ref="H34" r:id="rId24" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
-    <hyperlink ref="E38" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H38" r:id="rId26" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
-    <hyperlink ref="E40" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
-    <hyperlink ref="E41" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H42" r:id="rId29" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
-    <hyperlink ref="E44" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H44" r:id="rId31" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
-    <hyperlink ref="H45" r:id="rId33" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
-    <hyperlink ref="E46" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E47" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H50" r:id="rId36" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
-    <hyperlink ref="E57" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E59" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
-    <hyperlink ref="H59" r:id="rId39" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
-    <hyperlink ref="E61" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E64" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E66" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="E67" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
-    <hyperlink ref="E68" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
-    <hyperlink ref="H68" r:id="rId45" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
-    <hyperlink ref="I68" r:id="rId46" display="https://www.laphilo.fr/photo/tarassov.webp"/>
-    <hyperlink ref="E69" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
-    <hyperlink ref="E72" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Godefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H72" r:id="rId49" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
-    <hyperlink ref="H75" r:id="rId50" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
-    <hyperlink ref="H76" r:id="rId51" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
-    <hyperlink ref="H78" r:id="rId52" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
-    <hyperlink ref="I78" r:id="rId53" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
-    <hyperlink ref="E81" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H81" r:id="rId55" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
-    <hyperlink ref="E82" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRANT&lt;/a&gt; est un philosophe britannique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
-    <hyperlink ref="E84" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="H87" r:id="rId58" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
-    <hyperlink ref="E88" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Jennifer_Saul&quot; title=&quot; Wikipedia&quot;&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe américaine  spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href=&quot;https://www.youtube.com/watch?v=2_FqrHs9S-s&quot; title=&quot;Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy&quot;&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre &quot;Lying, Misleading, and What Is Said&quot; aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &quot;Feminism: Issues &amp; Arguments&quot;, elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le &quot;Women in Philosophy Task Force&quot; au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href=&quot;https://www.youtube.com/watch?v=QDcuCIqCWdQ&quot; s title=&quot; Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy&quot;&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; "/>
-    <hyperlink ref="E90" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
-    <hyperlink ref="H91" r:id="rId61" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
-    <hyperlink ref="E94" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E95" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E97" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
-    <hyperlink ref="E100" r:id="rId65" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E101" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
-    <hyperlink ref="E104" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
+    <hyperlink ref="E10" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Richard_Swinburne&quot; title=&quot; Wikipedia&quot;&gt;Richard SWINBURNE&lt;/a&gt;  est un philosophe britannique, professeur émérite de philosophie à l’université d’Oxford, et l’une des figures majeures de la philosophie analytique de la religion au XXe et XXIe siècles. Il a développé une œuvre systématique en philosophie de la religion, mais aussi en épistémologie, en philosophie des sciences et en philosophie de l’esprit, en défendant une forme de théisme chrétien rationnellement justifié. &lt;/p&gt; &lt;p&gt;  Un des traits centraux de sa pensée est l’usage d’arguments inductifs et probabilistes, inspirés du théorème de Bayes, pour évaluer la probabilité de l’existence de Dieu. Plutôt que de chercher des démonstrations déductives certaines, Il propose un « cas cumulatif » : chaque argument (cosmologique, téléologique, moral, de la conscience, des expériences religieuses, etc.) augmente un peu la probabilité du théisme, et leur ensemble rend, selon lui, l’hypothèse « Dieu existe » plus probable que son contraire. Il soutient ainsi que le théisme offre l’explication la plus simple et la plus puissante de l’existence de l’univers, de l’ordre des lois naturelles, de l’évolution d’êtres conscients et moraux, et de nombreux autres faits. &lt;/p&gt; &lt;p&gt; Il défend aussi un dualisme de substance : pour lui, l’être humain n’est pas réductible à un objet matériel complexe, mais est composé d’un corps et d’une âme, deux substances distinctes. Il s’appuie notamment sur l’analyse de la conscience et sur les limites, selon lui, des explications physicalistes pour rendre compte de l’expérience subjective, de la pensée et de la liberté. Cette position le place en opposition directe avec les physicalistes comme ceux que Jackson a d’abord critiqués, mais il va plus loin en affirmant que l’âme est une réalité métaphysique à part entière, compatible avec une vision théiste du monde. &lt;/p&gt; &lt;p&gt; Sur la question du mal, il reconnaît que l’existence de souffrances graves (comme Auschwitz) constitue une objection sérieuse contre le théisme, mais il estime qu’elle ne suffit pas à le réfuter. Il développe une théodicée où le mal naturel et moral joue un rôle dans la possibilité pour les êtres humains de former librement leur caractère, d’accomplir des actes moraux significatifs et de participer à un processus de maturation spirituelle. Pour lui, un monde sans aucune possibilité de mal serait un monde où la liberté et la responsabilité morale seraient radicalement appauvries. &lt;/p&gt; &lt;p&gt;  Il se présente comme « théiste » au sens classique : Dieu est une personne, un agent surnaturel omniscient, omnipotent et parfaitement libre, créateur et sustainer de l’univers, et non un simple principe abstrait ou une cause première déiste. Son projet global est de montrer que croire en un tel Dieu n’est pas irrationnel, mais au contraire bien soutenu par l’ensemble de notre expérience et de nos connaissances scientifiques et morales, interprétées dans un cadre bayésien et analytique rigoureux. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H10" r:id="rId5" display="https://www.laphilo.fr/pho/rswinburne-mini.webp"/>
+    <hyperlink ref="H11" r:id="rId6" display="https://www.laphilo.fr/pho/cgilligan-mini.webp"/>
+    <hyperlink ref="E12" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Nagel&quot;  title=&quot; Wikipedia&quot;&gt;Thomas NAGEL&lt;/a&gt; est un philosophe d'origine serbe reconnu pour ses contributions importantes dans la philosophie de l'esprit, l'éthique et la philosophie politique. &lt;/p&gt; &lt;p&gt; - Philosophie de l'esprit et la conscience : C'est probablement son domaine  &lt;a href=&quot;https://www.youtube.com/watch?v=4yrHYakYPXA&quot; title=&quot; Thomas Nagel par the filosofy guy&quot;&gt;le plus célèbre&lt;/a&gt;, notamment grâce à son article de 1974, &quot;Qu'est-ce que ça fait d'être une chauve-souris ?&quot; où il critique le réductionnisme matérialiste qui cherche à expliquer la conscience uniquement par des phénomènes physiques ou neuronaux. Il soutient que l'expérience subjective, c'est-à-dire le &quot;ce que ça fait&quot; d'être un organisme donné (comme une chauve-souris utilisant l'écholocation), est irréductible à une description purement objective et impersonnelle. Il met en avant le &quot;caractère subjectif de l'expérience&quot; ou les qualia, qui échappent aux analyses scientifiques traditionnelles. &lt;/p&gt; &lt;p&gt; - Le point de vue objectif et subjectif : il développe cette opposition entre le point de vue subjectif et objectif dans son ouvrage, &quot;Le Point de vue de nulle part&quot;. Il explore la tension entre notre capacité à adopter un point de vue impersonnel et scientifique sur le monde, et notre inévitable perspective subjective en tant qu'individus.  &lt;/p&gt; &lt;p&gt; - Éthique et philosophie politique : En éthique, il s'intéresse à l'existence de raisons morales impartiales et à la tension entre les exigences de l'impartialité et nos préoccupations personnelles (partialité). Son ouvrage &quot;Égalité et Partialité&quot;  explore ces dilemmes, notamment en ce qui concerne la justice libérale et la légitimité politique basée sur l'acceptabilité universelle. &lt;/p&gt; &lt;p&gt; Plus récemment, dans son livre &quot;L'esprit et le cosmos&quot;, il a critiqué les limites de la  &lt;a href=&quot;https://www.nonfiction.fr/article-6755-le-brulot-anti-materialiste-de-thomas-nagel.htm&quot; title=&quot;Le brûlot anti-matérialiste de Thomas Nagel par nonfiction&quot;&gt; conception matérialiste&lt;/a&gt; néo-darwinienne de la nature, en arguant qu'elle ne peut pas expliquer de manière satisfaisante l'émergence de la conscience, de la raison et de la valeur. Il y exprime ses doutes sur la capacité de la science matérialiste à rendre compte de l'ensemble de la réalité. &lt;/p&gt; &lt;p&gt; Il  est un penseur qui pousse à la réflexion sur les limites de notre connaissance et sur les aspects de la réalité qui semblent échapper à une compréhension purement objective. Il a reçu de nombreuses distinctions pour son travail, dont le Prix Balzan pour la philosophie morale en 2008. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E13" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eb%C3%A9n%C3%A9zer_Njoh-Mouell%C3%A9&quot;  title=&quot; Wikipedia&quot;&gt;Ebénézer NJOH-MOUELLÉ&lt;/a&gt;  est un philosophe et homme politique camerounais titulaire d'un doctorat d'État en lettres et sciences humaines de la Sorbonne ainsi que d'une licence en philosophie, un DES, puis son doctorat grâce à une bourse des Nations unies. Enseignant à l'Université de Yaoundé, il a influencé la philosophie africaine contemporaine. &lt;/p&gt; &lt;p&gt; Son premier livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=QBTYhXqA14s&quot;  title=&quot;De la médiocrité à l’excellence : Le réveil urgent de l’Afrique par Apprnds +&quot;&gt;&quot;De la médiocrité à l’excellence&quot;&lt;/a&gt;  paru en  1970, analyse les obstacles au développement du Cameroun et est étudié au programme de terminale. Parmi ses autres ouvrages figurent &quot;Jalons&quot; paru en 1971,&quot; Député de la Nation&quot; en 2002 et des travaux récents sur le transhumanisme comme Elixir ou Lignes rouges &quot;éthiques&quot; de l'intelligence artificielle. &lt;/p&gt; &lt;p&gt; Sa pensée, réflexive et analytique, porte sur le développement humain, la vie quotidienne, l'esprit critique et les défis  &lt;a href=&quot;https://www.youtube.com/watch?v=IHwd6B-1RfQ&quot;  title=&quot; Quelle éthique pour le transhumanisme par Ebenezer Njoh Mouelle&quot;&gt;éthiques du transhumanisme &lt;/a&gt;. Il encourage l'effort personnel et une gouvernance globale.  &lt;/p&gt; &#10;&#10;​"/>
+    <hyperlink ref="H14" r:id="rId9" display="https://www.laphilo.fr/pho/esosa-mini.webp"/>
+    <hyperlink ref="E18" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alison_Jaggar&quot;  title=&quot; Wikipedia&quot;&gt;Alison JAGGAR&lt;/a&gt; est une philosophe féministe anglo-américaine connue pour avoir contribué à installer durablement les questions de genre dans la philosophie morale, politique et sociale contemporaine. Elle appartient principalement au féminisme socialiste, tout en développant une pensée attentive aux rapports entre genre, classe, mondialisation, race et pauvreté.  &lt;/p&gt; &lt;p&gt; Elle soutient que l’oppression des femmes ne peut pas être comprise uniquement comme une affaire de préjugés individuels, de droits juridiques insuffisants ou de rapports privés entre les sexes. Elle l’analyse également comme un phénomène structurel lié à l’organisation économique, à la division sexuelle du travail, au travail domestique et de soin non rémunéré, ainsi qu’aux rapports de pouvoir capitalistes. Son féminisme est donc dit socialiste : il combine la critique féministe du patriarcat et une attention, inspirée du marxisme, aux formes d’exploitation économique. &lt;/p&gt; &lt;p&gt; Dans ses travaux d’éthique, elle critique les théories morales classiques lorsqu’elles présentent l’agent moral comme un individu abstrait, autonome et indépendant de ses relations sociales. Elle rappelle &lt;a href=&quot;https://journals.openedition.org/lectures/15257?lang=es&quot;  title=&quot;alison jaggar ; gender and global justice par openedition &quot;&gt;que les expériences de dépendance, &lt;/a&gt;  de maternité, de travail domestique, de violence ou de discrimination sont souvent marginalisées par les théories élaborées depuis des positions socialement privilégiées. L’éthique féministe doit donc à la fois repérer les biais masculins présents dans la philosophie, prendre au sérieux l’expérience morale des femmes et contribuer concrètement à leur libération. &lt;/p&gt; &lt;p&gt; Elle est particulièrement connue pour son article « Love and Knowledge », où elle défend l’idée que les émotions ne sont pas de simples perturbations irrationnelles de la pensée. Elles peuvent signaler une injustice, rendre perceptibles des formes d’oppression banalisées et devenir des ressources pour l’enquête morale et politique. Elle appelle notamment « émotions hors-la-loi » les réactions affectives — indignation, colère, malaise — qui contestent les normes dominantes et peuvent ouvrir une critique sociale. Cette position s’oppose à une image traditionnelle de la rationalité qui dissocierait radicalement raison objective et émotion subjective. &lt;/p&gt; &lt;p&gt; Dans ses travaux plus récents, elle déplace l’attention vers la justice mondiale : pauvreté, migrations, travail transnational, vulnérabilité économique, violences de genre et effets de la mondialisation. Elle reproche à certaines théories de la justice de raisonner comme si les États, les marchés et les individus étaient neutres du point de vue du genre. Elle cherche au contraire à évaluer les institutions et politiques globales à partir de leurs effets réels sur les femmes, notamment celles qui subissent simultanément des dominations économiques, sexuées et racialisées. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H18" r:id="rId11" display="https://www.laphilo.fr/pho/ajaggar-mini.webp"/>
+    <hyperlink ref="E19" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Steffen_Dietzsch&quot;  title=&quot; Wikipedia&quot;&gt;Steffen DIETZSCH&lt;/a&gt;  est surtout un historien de la philosophie et un essayiste allemand, pas un philosophe systématique au sens classique. Son travail porte notamment sur Kant, le devenir de l’idéalisme allemand, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Premier_romantisme_allemand&quot;  title=&quot;Premier romantisme allemand par Wikipedia&quot;&gt;la Frühromantik &lt;/a&gt; et plus largement sur l’histoire des idées en Europe. &lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans une réflexion sur la culture philosophique et sur la manière dont les grands concepts du passé continuent d’agir dans la modernité. Il s’intéresse particulièrement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Transcendantal&quot;  title=&quot;transcendantal par Wikipedia&quot;&gt;principe transcendantal &lt;/a&gt; chez Kant, à ses effets dans l’histoire intellectuelle, et aux prolongements de la philosophie chrétienne et du romantisme jusqu’à Nietzsche. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il lit la philosophie comme une histoire de transformations conceptuelles. Il ne cherche pas seulement à commenter les auteurs, mais à montrer comment leurs idées s’insèrent dans des configurations culturelles plus larges et se déplacent d’une époque à l’autre. &lt;/p&gt; &lt;p&gt; Sa pensée est moins centrée sur une doctrine unique que sur une méthode historique et interprétative. Il aide à comprendre la philosophie comme un ensemble de débats, de continuités et de ruptures, surtout autour de Kant et de l’héritage de l’idéalisme allemand. &lt;/p&gt; "/>
+    <hyperlink ref="H21" r:id="rId13" display="https://www.laphilo.fr/pho/fjackson-mini.webp"/>
+    <hyperlink ref="E24" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://de.wikipedia.org/wiki/Gunter_Gebauer&quot; title=&quot; Wikipedia&quot;&gt;Gunter GEBAUER&lt;/a&gt; est un philosophe et sociologue du sport allemand, professeur émérite à l'Université libre de Berlin, dont les travaux se situent à l'intersection de la philosophie du langage, de l'anthropologie et des sciences sociales. Figure polyvalente, il est reconnu pour sa capacité à décloisonner les disciplines, intégrant des réflexions théoriques rigoureuses avec des objets d'étude concrets comme le sport et la performance. &lt;/p&gt; &lt;p&gt; L'une de ses contributions majeures réside dans le renouveau de l'anthropologie philosophique, qu'il aborde à travers le prisme de &lt;a href=&quot;https://www.youtube.com/watch?v=UnI7mWbYjCA&quot;  title=&quot;The mimetic creation of human culture par MDRN&quot;&gt;l'histoire et de la culture. &lt;/a&gt; Contrairement aux approches qui cherchent à définir l'homme par des essences immuables, il s'appuyant sur Ludwig Wittgenstein, conçoit l'être humain comme un sujet socialement « produit » par le langage, les jeux de langage et les interactions quotidiennes. Pour lui, le social précède l'individuel, et la subjectivité se forme dans la pratique, au sein de structures culturelles qu'il analyse comme des réalités performatives. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches académiques, il a fait du sport, et plus particulièrement du football, un objet d'analyse philosophique sérieux. Il considère le sport non pas comme un simple divertissement, mais comme une « mise en scène » de la société, &lt;a href=&quot;https://www.persee.fr/doc/arss_0335-5322_1994_num_103_1_3105&quot;  title=&quot;Le nouveau nationalisme sportif par Persée&quot;&gt;un laboratoire &lt;/a&gt;  où s'expriment les tensions, les rituels et les valeurs d'une culture donnée. Ses travaux sur la performance et la ritualisation dans le sport ont permis d'éclairer les mécanismes par lesquels les sociétés modernes organisent la compétition et construisent du sens collectif. &lt;/p&gt; &lt;p&gt; Tout au long de sa carrière, il a dirigé des centres de recherche interdisciplinaires majeurs, notamment le Centre interdisciplinaire d'anthropologie historique de Berlin, et a participé à des projets sur les « cultures du performatif ». Par ses échanges avec d'autres grands penseurs contemporains, comme Étienne Balibar, il a contribué à redéfinir la place de l'anthropologie dans le débat philosophique actuel. Son œuvre demeure une référence pour ceux qui cherchent à comprendre la subjectivité humaine non pas comme une donnée isolée, mais comme une réalité ancrée dans le flux constant des pratiques sociales, linguistiques et sportives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H24" r:id="rId15" display="https://www.laphilo.fr/pho/ggebauer-mini.webp"/>
+    <hyperlink ref="H25" r:id="rId16" display="https://www.laphilo.fr/pho/lrockwell-mini.webp"/>
+    <hyperlink ref="H26" r:id="rId17" display="https://www.laphilo.fr/pho/adavis-mini.webp"/>
+    <hyperlink ref="E29" r:id="rId18" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Peter_Singer&quot;  title=&quot; Wikipedia&quot;&gt; Peter SINGER&lt;/a&gt; est un philosophe contemporain Australien influent et connu pour être un défenseur de l'utilitarisme, une théorie éthique fondait par Jérémy BENTHAN et qui soutient que les actions doivent être évaluées en fonction de leur capacité à maximiser le bonheur ou le bien-être de la plus grande quantité de personnes possible.  &lt;/p&gt; &lt;p&gt; Il est aussi &lt;a href=&quot;https://www.youtube.com/watch?v=hzKa5fB6_uw&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;L'Antispécisme par Alain Bajomée&quot;&gt; antispécisme &lt;/a&gt; et souligne que tous les êtres sensibles, les humains mais aussi  les animaux, doivent être pris en compte dans nos décisions éthiques et que nous avons une obligation morale de défendre  la &lt;a href=&quot;https://www.youtube.com/watch?v=bYDAjC15OTk&amp;ab_channel=FranceCulture&quot;  title=&quot;le capitalisme à l'origine de la cause animale par France Culture&quot;&gt; &quot;cause animale&quot; &lt;/a&gt; car le capitalisme actuel est à l'origine de sa souffrance. &lt;/p&gt; &lt;p&gt; Cela signifie que nous avons une obligation morale de considérer les intérets des animaux  et de ne pas les maltraiter ou les tuer sans raison valable. Il soutient également que nous avons une obligation de prendre en compte les intérêts des générations futures et de préserver l'environnement naturel. &lt;/p&gt; &lt;p&gt; &#10;En ce qui concerne la pauvreté mondiale, il propose un &lt;a href=&quot;https://www.youtube.com/watch?v=Diuv3XZQXyc&amp;ab_channel=TED&quot;  title=&quot;le pourquoi et le comment par TED&quot;&gt; &quot;altruisme efficace&quot; &lt;/a&gt; et soutient que les personnes riches ont une obligation morale de donner une partie importante de leur revenu pour aider les plus démunis, car cela pourrait améliorer considérablement la vie de nombreuses personnes.   &lt;/p&gt; &lt;audio controls title=&quot;Peter Singer et les lois de bioéthique par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2011/08/s31/NET_67e33810-681e-49cb-b7f8-e692256e2130.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H32" r:id="rId19" display="https://www.laphilo.fr/pho/dpapineau-mini.webp"/>
+    <hyperlink ref="E33" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_N._Gray&quot;  title=&quot; Wikipedia&quot;&gt;John N Gray&lt;/a&gt;  est un philosophe popitique britanique connu pour ses critiques radicales de l’humanisme, de l’idée de progrès et des utopies modernes. Il est d’abord un théoricien du libéralisme, puis devient l’un des critiques les plus féroces du libéralisme globalisé et du &quot;projet des Lumières&quot;. Il critique l’anthropocentrisme et l’humanisme et rejette ​ &lt;a href=&quot;https://www.youtube.com/watch?v=-nGP8ad4Kgo&quot;  title=&quot;Populism, Progress, and the End of the Modern World - John Gray Explained par Sagacious&quot;&gt; l’idée de progrès &lt;/a&gt;.  À son avis, l'être humain est une espèce dévastatrice et vorace qui élimine d'autres êtres vivants pour assurer leur survie et détruit également leur propre habitat. &lt;/p&gt; &lt;p&gt;  Il défend que la morale n'est qu'une illusion et que l'être humain est une espèce qui  &lt;a href=&quot;https://www.youtube.com/watch?v=6rsGkfngA5M&quot; title=&quot;Everything You Know About The Future is Wrong | Aaron Bastani meets John Gray par Novara Media&quot;&gt; s'autodétruit&lt;/a&gt; . Un exemple des tendances destructrices de l'être humain a été les idées apocalyptiques telles que le millénarisme au Moyen-Âge ou les projets utopiques socialistes et nazis du 20ème siècle.  &lt;/p&gt; &lt;p&gt;  Son livre le plus célèbre, &quot;Straw Dogs, Thoughts on Humans and Other Animals&quot;, attaque l’humanisme, qu’il voit comme un héritage sécularisé du christianisme : l’idée que l’homme est radicalement distinct de l’animal, maître de son destin et orienté vers un progrès moral de l’histoire. Pour lui, cette croyance en un &lt;a href=&quot;https://www.youtube.com/watch?v=u66WIRAwowI&quot;  title=&quot;John Gray: AI Utopias, Online Hatred, &amp; The Dangerous Myth of Progress par Philosopheasy&quot;&gt; progrès cumulatif &lt;/a&gt; de l’humanité est une illusion dangereuse, qui nourrit des projets politiques utopiques et violents. Dans &quot;False Dawn: The Delusions of Global Capitalism&quot;, il soutient que la mondialisation néolibérale n’est pas un aboutissement naturel mais un projet idéologique instable, voué aux crises et aux replis et dans &quot;Black Mass: Apocalyptic Religion and the Death of Utopia&quot;, il analyse les grands mouvements modernes (communisme, fascisme, capitalisme démocratique globalisé) comme des &quot;religions politiques&quot; héritant de la structure eschatologique du christianisme. &lt;/p&gt; "/>
+    <hyperlink ref="E34" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Catherine_Elgin&quot;  title=&quot; Wikipedia&quot;&gt;Catherine ELGIN&lt;/a&gt;   est une philosophe américain  professeure à Harvard et spécialiste en épistémologie ainsi qu'en esthétique. Elle est  &lt;a href=&quot;https://catherineelgin.com/&quot; title=&quot; Catherine Z Elgin&quot;&gt;notamment connue &lt;/a&gt; pour sa longue collaboration avec Nelson Goodman, avec qui elle a exploré les liens entre philosophie, arts et sciences. &lt;/p&gt; &lt;p&gt; Sa philosophie remet en question la quête traditionnelle de la vérité absolue en épistémologie. Pour elle, la compréhension prime sur la connaissance factuelle, car elle permet de saisir des ensembles cohérents et systématiques, même si ceux-ci incluent des modèles idéalisés ou des approximations. &lt;/p&gt; &lt;p&gt; Dans Considered Judgment, elle défend l'équilibre réfléchi comme norme de rationalité : &lt;a href=&quot;https://www.youtube.com/watch?v=yqkooYMmVNU&quot; title=&quot; Disagreement between aquals par philosophy Univ Edinburgh&quot;&gt;les croyances &lt;/a&gt;  sont évaluées non par leur correspondance stricte à la réalité, mais par leur cohérence globale et leur capacité à éclairer le monde. &lt;/p&gt; &lt;p&gt; Elle applique cette approche à l'esthétique et aux sciences, où l'art et les fictions servent d'expériences de pensée pour approfondir la compréhension. Sa pensée valorise ainsi une épistémologie flexible, attentive aux valeurs cognitives au-delà des faits bruts. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H35" r:id="rId22" display="https://www.laphilo.fr/pho/vskoumine-mini.webp"/>
+    <hyperlink ref="I35" r:id="rId23" display="https://www.laphilo.fr/photo/vskoumine.webp"/>
+    <hyperlink ref="H36" r:id="rId24" display="https://www.laphilo.fr/pho/gpriest-mini.webp"/>
+    <hyperlink ref="E40" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans-Hermann_Hoppe&quot;  title=&quot; Wikipedia&quot;&gt;Hans-Hermann HOPPE&lt;/a&gt;  est un économiste et philosophe politique allemand, figure de proue de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Anarcho-capitalisme&quot; title=&quot;anarcho-capitalisme par Wikipedia&quot;&gt;l'anarcho-capitalisme moderne &lt;/a&gt; et de l'École autrichienne d'économie. Élève de Murray Rothbard, il est célèbre pour ses thèses radicales remettant en cause la légitimité de l'État et la pertinence de la démocratie comme modèle de gouvernance. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Démocratie, le dieu qui a échoué (2000), soutient que la démocratie a favorisé l'expansion incontrôlée de l'étatisme et la dégradation de la liberté individuelle. Pour lui, le passage de la monarchie à la démocratie a transformé les dirigeants de  &lt;a href=&quot;https://www.youtube.com/watch?v=lsQo0dhfTaw&quot; title=&quot;propiety, freedom and society par misesmedia&quot;&gt;« propriétaires » de l'État  &lt;/a&gt; — qui cherchaient à préserver la valeur de leur bien à long terme — en « gérants » temporaires, incités à maximiser leur exploitation immédiate par la dépense publique et l'endettement. Il considère l'ordre social idéal comme un anarcho-capitalisme fondé sur la propriété privée absolue et la concurrence entre agences privées de protection. &lt;/p&gt; &lt;p&gt; Il a développé le concept d'« éthique de l'argumentation » pour justifier rationnellement le droit de propriété. Il affirme que quiconque participe à une argumentation reconnaît implicitement la propriété de chacun sur son propre corps et le principe de non-agression, car l'acte même de débattre suppose une autonomie individuelle et une liberté d'action. Cette démonstration constitue, selon lui, le fondement irréfutable de sa philosophie libertarienne et le socle sur lequel repose sa condamnation de toute coercition étatique. &lt;/p&gt; &lt;p&gt; Sa pensée, classée dans le  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Pal%C3%A9o-libertarianisme&quot; title=&quot;paléo-liberalisme par Wikipedia&quot;&gt;« paléolibertarianisme », &lt;/a&gt;  se caractérise par une alliance entre libéralisme économique et défense de l'ordre social traditionnel. Hoppe est une figure clivante, non seulement pour son rejet total de l'État, mais aussi pour ses prises de position sociétales qui valorisent les structures sociales conservatrices et les communautés locales au détriment de l'universalisme étatique. Ses travaux ont exercé une influence notable au sein de certains courants de la droite radicale et des milieux libertariens, faisant de lui l'un des penseurs les plus radicaux et influents du paysage intellectuel allemand contemporain. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H40" r:id="rId26" display="https://www.laphilo.fr/pho/hhhoppe-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Rebecca_Goldstein&quot; title=&quot; Wikipedia&quot;&gt;Rebecca GOLDSTEIN&lt;/a&gt;  est une philosophe et romancière américaine reconnue pour sa capacité à entremêler la philosophie, la science et la littérature. Titulaire d'un doctorat en philosophie de l'Université de Princeton, elle a mené une carrière académique tout en écrivant des romans qui explorent des questions philosophiques profondes à travers des récits captivants. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=PeOxpifynbg&amp;list=PLOpOxUej26msclUDpflVMenYf1R3hPrfg&quot; title=&quot; Rebecca Goldstein  par Thinkable&quot;&gt; Son œuvre&lt;/a&gt; aborde un large éventail de sujets philosophiques, notamment le problème corps-esprit, la nature de la conscience, l'éthique et la philosophie des sciences. Elle est particulièrement connue pour son approche qui vise à rendre les idées philosophiques complexes accessibles à un public plus large, souvent en utilisant la fiction comme véhicule pour l'exploration conceptuelle. &lt;/p&gt; &lt;p&gt; Elle a également écrit des ouvrages non fictionnels remarqués, notamment des biographies intellectuelles de figures marquantes de l'histoire de la pensée. Ses travaux sur le philosophe Baruch Spinoza (&quot;Spinoza: The Renegade Jew Who Gave Us Modernity&quot;) et &lt;a href=&quot;https://www.youtube.com/watch?v=yfOOoP-TnIU&quot;  title=&quot;Incompleteness: Rebecca Goldstein on the Life and Work of Kurt Gödel par Simply Charly&quot;&gt; Kurt Gödel&lt;/a&gt; (&quot;Incompleteness: The Proof and Paradox of Kurt Gödel&quot;) sont particulièrement appréciés pour leur rigueur philosophique et leur perspicacité historique. Dans ces ouvrages, elle ne se contente pas de présenter leurs idées, mais explore également le contexte personnel et intellectuel qui les a façonnées. &lt;/p&gt; &lt;p&gt; Elle a reçu de nombreuses distinctions pour son travail, dont la Médaille nationale des sciences humaines et le Prix Richard Dawkins, reconnaissant ainsi ses contributions à la pensée et à la promotion de la raison et de l'humanisme. &lt;/p&gt; "/>
+    <hyperlink ref="E43" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Mauricio_Beuchot&quot; title=&quot; Wikipedia&quot;&gt;Mauricio BEUCHOT&lt;/a&gt; est un philosophe et prêtre dominicain mexicain reconnu principalement pour sa contribution à la philosophie contemporaine à travers la  &lt;a href=&quot;https://www.youtube.com/watch?v=QBNt2lASkFg&amp;t=17s&quot; title=&quot; La source herméneutique par Johann Michel&quot;&gt;&quot;herméneutique analogique&quot;&lt;/a&gt;, une approche originale qui cherche un chemin médian entre les interprétations univoques et équivoques des textes et du réel et vise à dépasser les limitations du positivisme et du relativisme interprétatif extrême, cherchant une voie d’interprétation fondée sur l’analogie, inspirée notamment par Paul Ricoeur.​&lt;/p&gt; &lt;p&gt; &#10;Pour lui, l'équivoque est la différence entre l'application et le sens des choses. C'est un critère relatif et subjectif, alors que l'univocité est l'identité des choses, qui ne dépend pas de leur signification ou de leur application. C'est un critère objectif. Il propose une conception ontologique et herméneutique de la nature humaine, défendant l'idée d'un noyau entitaire propre à l'humain mais traversé par l'histoire et la culture, sans tomber dans un relativisme absolu.​ &lt;/p&gt; &lt;p&gt; Il accorde une place importante à l’interprétation, à  &lt;a href=&quot;https://www.youtube.com/watch?v=HkX58vGWGt0&quot; title=&quot; Entrevista completa: Mauricio Beuchot par San Pablo Mexico&quot;&gt;l'expérience et au langage&lt;/a&gt;, et se préoccupe de la fondation philosophique des droits humains ainsi que du sens de la vie dans la société contemporaine et il considère que la philosophie doit intervenir pour orienter la société et participer à la quête de sens. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H44" r:id="rId29" display="https://www.laphilo.fr/pho/cmcginn-mini.webp"/>
+    <hyperlink ref="E46" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Seyla_Benhabib&quot; title=&quot; Wikipedia&quot;&gt;Seyla BENHABIB&lt;/a&gt;  est une philosophe et professeure de sciences politiques américaine d'origine turque, reconnue comme une figure majeure de la théorie critique contemporaine et de la théorie féministe. Elle a été élève de Herbert Marcuse et de Jürgen Habermas, et occupe depuis 2001 le titre d'Eugene Meyer Professor de Political Science et de Philosophie à l'Université de Yale, où elle est maintenant émérite. &lt;/p&gt; &lt;p&gt; Sa philosophie s'inscrit dans la deuxième tradition de la École de Frankfurt et se caractérise par sa tentative d'articuler l'universalisme avec le particularisme, en particulier dans les débats sur la différence, le féminisme et le multiculturalisme. Elle est une représentante de la discursethik  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89thique_de_la_discussion&quot; title=&quot;éthique de discours par wikipédia&quot;&gt;(éthique du discours) &lt;/a&gt; qu'elle développe de manière inclusive et participative, en intégrant une critique féministe à la conception habembrasienne. &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée concerne la citoyenneté et les droits humains, où elle identifie une tension fondamentale entre l'universalité des droits humains et les communautés juridico-civiles plurielles historiquement formées. Elle propose &lt;a href=&quot;https://www.youtube.com/watch?v=z_mmJyWLEtU&quot; title=&quot;éthique, féminisme et theorie politique par Darina Metreveli&quot;&gt;trois principes clés &lt;/a&gt; pour les relations entre minorités et majorité : la réciprocité égalitaire (mêmes droits civiques, politiques, économiques et culturels), l'assentiment volontaire (non-attribution automatique d'une religion ou culture à la naissance), et la liberté de sortie et d'association. &lt;/p&gt; &lt;p&gt; Elle rejette la vision des cultures comme monolithiques, affirmant plutôt qu'elles se forment dans le dialogue entre les autres cultures, avec un renouvellement constant des frontières imaginaires. En démocratie, elle considère que chaque individu devrait pouvoir décider de sa propre vie, plaçant les individus plus haut que la préservation des cultures pour les théoriciens démocratiques. &lt;/p&gt; &lt;p&gt; Ses contributions ont été honorées par le prix Ernst Bloch en 2009 pour sa contribution à la compréhension culturelle dans un monde global, ainsi que par des diplômes honorifiques des universités d'Utrecht (2004) et de Valencia (2010), et elle a présidé l'American Philosophical Association en 2007. Son travail combine la théorie critique de la deuxième École de Frankfurt avec la théorie féministe, faisant d'elle une des voix les plus autorisées dans les débats philosophiques et politiques contemporains. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H46" r:id="rId31" display="https://www.laphilo.fr/pho/sbenhabib-mini.webp"/>
+    <hyperlink ref="E47" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Mikhail_Epstein&quot; title=&quot; Wikipedia&quot;&gt;Mikhaïl EPSTEIN&lt;/a&gt; est un philosophe, essayiste et théoricien de la culture russe-américain, professeur à l'Université Emory (Atlanta) et l'une des figures les plus originales de la pensée postmoderne et post-soviétique contemporaine. Né à Moscou, il développa d'abord une carrière d'essayiste et de critique culturel dans les cercles intellectuels soviétiques avant d'émigrer aux États-Unis en 1990, où il poursuivit son œuvre dans un dialogue permanent entre les cultures russe et américaine.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans de nombreux ouvrages en russe et en anglais, est une pensée résolument post-métaphysique et post-soviétique qui cherche à penser &lt;a href=&quot;https://www.youtube.com/watch?v=F5yTgJvRuZk&quot; title=&quot; M Epstein on the Russian Anti-World  par Northwestern RPLRT&quot;&gt;l'après du modernisme &lt;/a&gt; et de l'idéologie soviétique. Son concept de « transculturalisme » — au-delà du multiculturalisme et de l'universalisme abstrait — propose une conception de la culture comme espace de passage entre les frontières, de traduction et d'hybridation créatrice. Ses réflexions sur le « minimalisme » et le « virtualisme » comme modes culturels post-soviétiques constituent des analyses originales des mutations culturelles contemporaines.&lt;/p&gt;&lt;p&gt;Sa &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=tdM6sFVeemY&quot; title=&quot; M Epstein the time ok AntiChrist par Darina Metreveli&quot;&gt;Philosophie du possible &lt;/a&gt; &lt;/em&gt; (2001) développe une métaphysique de la possibilité, cherchant à penser ce qui n'est pas encore mais pourrait être — modalité fondamentale de l'existence humaine et créatrice. Son projet de « translingualisme » — la philosophie de la traduction entre les langues comme condition de toute pensée créatrice — est l'une de ses contributions les plus originales. Inventeur prolixe de néologismes et de concepts, Epstein représente une philosophie de la créativité conceptuelle radicale, en dialogue permanent avec les traditions philosophiques russes et occidentales.&lt;/p&gt;"/>
+    <hyperlink ref="H47" r:id="rId33" display="https://www.laphilo.fr/pho/mepstein-mini.webp"/>
+    <hyperlink ref="E48" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vandana_Shiva&quot;   title=&quot; Wikipedia&quot;&gt;Vandana SHIVA&lt;/a&gt; est une philosophe indienne, physicienne de formation devenue philosophe des sciences, écoféministe et militante environnementale reconnue mondialement. Elle étudie la physique à l'université du Pendjab, obtient un master puis un doctorat en philosophie des sciences, influencée par sa sœur médecin qui l'alerte sur les risques des radiations. Son thèse porte sur les variables cachées en théorie quantique. &lt;/p&gt; &lt;p&gt; En 1982, elle fonde la &quot;Research Foundation for Science, Technology and Natural Resource Policy&quot; pour promouvoir une agriculture durable. En 1991, elle crée &lt;a href=&quot;https://www.youtube.com/watch?v=YEqTo8lDivs&quot;  title=&quot; Bande-annonce Les graines de Vandana Shiva  par The Seeds of Vandana Shiva&quot;&gt;Navdanya&lt;/a&gt;, une ONG protégeant la biodiversité agricole indienne contre les OGM et multinationales comme Monsanto. Elle lutte aussi contre les barrages, comme celui de Narmada. &lt;/p&gt; &lt;p&gt; Chef de file de &lt;a href=&quot;https://wildproject.org/auteurs/vandana-shiva&quot; title=&quot; Vandana Shiva  par wildproject&quot;&gt;l'écoféminisme&lt;/a&gt;, elle lie oppression des femmes et exploitation de la nature par le néolibéralisme agro-industriel, prônant un retour aux savoirs traditionnels et à la souveraineté alimentaire. Ses ouvrages comme &quot;Staying Alive&quot; paru en 1988 et &quot;Écoféministe&quot; en 1993, repositionnent les femmes comme gardiennes de l'écologie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Vandana Shiva, les souvenirs d'une femme de combat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16410-26.12.2023-ITEMA_23596286-2023C26376E0017-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E49" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christine_Korsgaard&quot;  title=&quot; Wikipedia&quot;&gt;Christine KORSGAARD&lt;/a&gt;   est une philosophe américaine, spécialisée en éthique et en histoire de la philosophie morale, particulièrement reconnue pour son interprétation originale et rigoureuse de la pensée d'Emmanuel Kant. Professeure à l'Université Harvard, elle est une figure majeure de la philosophie morale contemporaine, développant une perspective néo-kantienne qui cherche à ancrer la moralité dans la nature même de l'agence rationnelle. &lt;/p&gt; &lt;p&gt; Le cœur de son projet philosophique, souvent qualifié de &lt;a href=&quot;https://www.implications-philosophiques.org/theorie-de-la-justice-et-constructivisme-33/&quot;  title=&quot;Théorie de la justice et contructivisme part implications philosophiques&quot;&gt;« constructivisme intégral », &lt;/a&gt;  propose que les normes morales ne sont pas des faits objectifs existant indépendamment de nous, mais des structures que nous construisons par l'exercice de notre volonté rationnelle. Selon elle, l'impératif catégorique n'est pas une contrainte extérieure imposée à la volonté, mais une exigence qui émerge naturellement de la structure même de l'agent rationnel qui se gouverne lui-même. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Self-Constitution, elle approfondit cette idée en soutenant que l'action est un processus par lequel nous nous constituons nous-mêmes comme agents. Pour elle, agir de manière morale est inséparable de la cohérence de notre identité : en choisissant les principes qui guident nos actions, nous unifions notre « soi » et affirmons notre autonomie. Cette approche lie indissociablement l'éthique à la théorie de l'identité personnelle et à la nature de la raison pratique. &lt;/p&gt; &lt;p&gt; Elle  a également élargi sa réflexion à la question de nos obligations envers les animaux, contestant les approches purement utilitaristes. Dans &lt;a href=&quot;https://www.youtube.com/watch?v=Bn3-qffqiAc&quot;  title=&quot;Korsgaard a Kantian account of our obligation to animals par Harvard Animal Law&quot;&gt;Fellow Creatures, &lt;/a&gt; elle soutient que les animaux doivent être considérés comme des « fins en soi » en raison de leur nature d'êtres sensibles, tout en réinscrivant cette préoccupation dans un cadre déontologique kantien revu et corrigé. Sa philosophie propose ainsi une vision secularisée et exigeante de la dignité humaine et animale, fondée sur l'exercice de notre liberté et de notre responsabilité réciproque. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H52" r:id="rId36" display="https://www.laphilo.fr/pho/ffukuyama-mini.webp"/>
+    <hyperlink ref="E59" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Gerard_Vilar&quot;  title=&quot; Wikipedia&quot;&gt;Gérard VILAR&lt;/a&gt; est un philosophe espagnol , spécialiste d'esthétique et de théorie des arts. Professeur émérite à l'Université autonome de Barcelone (UAB), où il est catedrático depuis 2002, il a étudié la philosophie à l'UAB et s'est formé en Allemagne (Francfort, Constance, Humboldt de Berlin). Il a dirigé les revues Enrahonar (1995-2009) et Disturbis (depuis 2007), et préside depuis 2017 la Société espagnole d'esthétique et théorie des arts ; il a aussi été professeur invité à Potsdam, Northwestern et UNAM. &lt;/p&gt; &lt;p&gt;  Dans ses premières œuvres comme Raó i marxisme (1979) et Discurs sobre el senderi (1986), Vilar défend une &quot;raison praxeologique&quot; comme rationalité théorico-pratique, interprétant la raison instrumentale à la manière marxiste : une correction mutuelle constante  &lt;a href=&quot;https://www.youtube.com/watch?v=QJXl9H__ZJE&quot; title=&quot; Jornada Acollida pr Facultat de Filosopfia&quot;&gt; entre théorie et praxis.&lt;/a&gt;  Cette phase, influencée par l'École de Francfort et le Collectif Crítica, peine toutefois à justifier rationnellement les fins éthiques et politiques, limitant ainsi son ambition critique.  &lt;/p&gt; &lt;p&gt; Dès les années 1990 (La razón insatisfecha, 1999), il évolue vers une &quot;raison insatisfaite&quot;, proche de Habermas et Wellmer, mais axée sur le désaccord, l'erreur et le potentiel disruptif du langage plutôt que sur le consensus. Cette rationalité créative met l'accent sur la subjectivité moderne et les liens éthique-esthétique, dialoguant avec la théorie critique allemande et des analytiques comme Goodman ou Danto. &lt;/p&gt; &lt;p&gt; Depuis 2000 (El desorden estético, 2001 ; Disturbios de la razón, 2021), Vilar privilégie la &quot;raison esthétique&quot; comme force génératrice de &quot;disturbis de la raison&quot; : l'expérience artistique produit un désordre positif, non fonctionnel, qui ouvre à d'autres savoirs au-delà de l'instrumental (écho à Adorno : &quot;la fonction de l'art est de manquer de fonction&quot;). Il analyse l'&quot;artification&quot;, la précarité et les paradoxes postmodernes de l'art sans fin.https://richardmkearney.com/wp-content/uploads/2014/06/richard-kearney-interview-final-aug-25.pdf &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E61" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Andre%C3%AF_V%C3%A9likanov&quot;  title=&quot; Wikipedia (ru)&quot;&gt;Andreï VÉLIKANOV&lt;/a&gt; est un philosophe, artiste et théoricien de la culture russe contemporain, représentant de la réflexion esthétique et médiatique à l'ère numérique. Formé aux arts et à la philosophie, il développe une pensée à l'intersection de la  &lt;a href=&quot;https://www.youtube.com/watch?v=A7v8BiJgArA&amp;list=RDA7v8BiJgArA&quot; title=&quot;Dancing tree par Andrey Velikanov&quot;&gt;philosophie de l'art, &lt;/a&gt; de la théorie des médias et de l'esthétique philosophique, s'inscrivant dans la continuité de la tradition esthétique russe tout en l'ouvrant aux problématiques contemporaines.&lt;/p&gt;&lt;p&gt;Sa réflexion philosophique explore les transformations de l'expérience esthétique à l'ère des médias numériques et de la culture visuelle contemporaine. À la suite de Bakhtine et de Lossev, il s'intéresse au problème de la représentation et de la présence dans l'art contemporain — comment   &lt;a href=&quot;https://www.youtube.com/watch?v=xbp-7Scmh8I&quot; title=&quot; Andrey Velikanov&quot;&gt;l'œuvre d'art &lt;/a&gt; peut-elle encore prétendre à une présence authentique dans un monde saturé d'images reproductibles et de simulations ? Sa pensée dialogue avec les théories occidentales de l'esthétique et des médias (Benjamin, Baudrillard, Virilio) tout en maintenant un ancrage dans la tradition philosophique russe.&lt;/p&gt;&lt;p&gt;Ses activités artistiques et ses écrits théoriques témoignent d'une pensée en prise avec les pratiques concrètes de la création contemporaine. En maintenant vivant le dialogue entre l'esthétique philosophique traditionnelle et les formes contemporaines de la culture visuelle, Vélikanov représente une tentative de renouvellement de la tradition esthétique russe face aux défis de la modernité tardive. Sa figure illustre la continuité, à travers les ruptures de l'histoire, d'une préoccupation russe constante pour les questions de la forme, du sens et de la beauté.&lt;/p&gt;"/>
+    <hyperlink ref="H61" r:id="rId39" display="https://www.laphilo.fr/pho/avelikanov-mini.webp"/>
+    <hyperlink ref="E63" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Souleymane_Bachir_Diagne&quot;  title=&quot; Wikipedia&quot;&gt;Souleymane Bachir DIAGNE&lt;/a&gt; est un philosophe sénégalais de renommée internationale dont la pensée tisse des liens entre philosophie islamique, philosophie africaine, logique, histoire des sciences et humanisme.  Sa recherche couvre aussi l'histoire de la logique, les mathématiques, l’histoire des sciences et la philosophie occidentale, avec un intérêt constant pour le  &lt;a href=&quot;https://www.youtube.com/watch?v=g8LSLi9RgWo&quot; title=&quot;Souleymane Bachir Diagne : « Les cultures doivent conspirer ensemble pour fabriquer de l’universel  par Mediapart&quot;&gt; dialogue interculturel &lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;Comment philosopher en Islam&quot;, il explore comment l’islam a historiquement encouragé le rationalisme, dès les débuts via les mutazilites, jusqu’aux figures d’Averroès ou de Ghazâlî, mettant en lumière l’interprétation philosophique dans la tradition islamique,Il défend une conception de l’universel comme un processus partagé : un &quot;universel latéral&quot; (inspiré de Merleau-Ponty), qui se construit au sein de la pluralité culturelle, et non imposé de façon descendante. &lt;/p&gt; &lt;p&gt;  L’un des axes centraux de son œuvre est la traduction, qu’il considère comme un geste éthique essentielle de construction de lien entre cultures — rapprocher des « langues-mondes » pour composer des mondes. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages, on trouve &quot;Boole, l’oiseau de nuit en plein jour&quot;, oeuvre sur la symbolique de georges Boole,  &quot;Universaliser&quot;, essai où il défend un humanisme fondé sur  &lt;a href=&quot;https://www.youtube.com/watch?v=RPa4_LBLw50&amp;t=126s&quot; title=&quot;  Souleymane Bachir Diagne - UBUNTU par Apm&quot;&gt;  l’ubuntu  &lt;/a&gt; (faire humanité ensemble), invitant à décoloniser les esprits pour recréer un universel inclusif et &quot;De langue à langue&quot;, ouvrage sur sur la traduction comme acte moral et confrontation entre mondes linguistiques et culturel. &lt;/p&gt; &lt;p&gt; Il a reçu le prix Dagnan-Bouveret et le prix Édouard-Glissant en 2011, a été fait chevalier des Arts et Lettres en 2017, et élu à l’American Academy of Arts and Sciences en 2019. Sa pensée, à la croisée des mondes, invite à « faire humanité ensemble » en décolonisant les savoirs, en pratiquant la traduction comme hospitalité intellectuelle, et en construisant un universel inclusif enraciné dans la diversité humaine. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Souleymane Bachir Diagne par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-25.10.2024-ITEMA_23904458-2024F45096S0299-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E66" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Judith_Butler&quot;   title=&quot; Wikipedia&quot;&gt;Judith BUTLER&lt;/a&gt; est une philosophe américaine contemporaine, reconnue pour ses travaux sur le genre et a marqué les champs de la philosophie politique, de l'éthique, du féminisme, de la &lt;a href=&quot;https://www.cairn.info/revue-cahiers-du-genre-2008-1-page-205.htm&quot;  title=&quot;Theoricienne du genre  par Cairn Info  &quot;&gt;théorie queer &lt;/a&gt; et de la théorie littéraire. &lt;/p&gt;&#10;&lt;p&gt; Elle a révolutionné notre compréhension du genre en le &lt;a href=&quot;https://www.celles-qui-osent.com/judith-butler/&quot;  title=&quot;Edith Butler par celles qui osent  &quot;&gt;conceptualisant&lt;/a&gt;  non pas comme une essence innée, mais comme une performance répétée. Le genre est ainsi produit et reproduit par des actes, des discours et des pratiques sociales. Elle s'est intéressée aux limites du langage et aux façons dont le discours peut à la fois constituer et opprimer les sujets. Elle a notamment analysé comment les normes hétéronormatives et les catégories binaires (homme/femme) contraignent les individus et limitent leur expression. Elle a également réfléchi sur la notion de précarité et sur les violences subies par les personnes marginalisées. &lt;/p&gt;&#10; &lt;p&gt; Dans ces ouvrages, &lt;a href=&quot;https://ia801908.us.archive.org/7/items/jbutler_202006/jbutler.pdf&quot;  title=&quot;Trouble dans le genre par Eric Fassin  &quot;&gt;&quot;Trouble dans le genre&quot; &lt;/a&gt; (Gender Trouble) qui est considéré comme un classique des études de genre. Elle y développe sa théorie de la performativité du genre et critique les notions essentialistes d'identité ainsi que dans  &quot;Corps qui comptent&quot; (Bodies That Matter) où explore les limites discursives du sexe et du genre, en montrant comment les corps sont façonnés par les normes sociales et les discours.&#10;&lt;p&gt; Pour comprendre les enjeux contemporains:  &lt;a href=&quot;https://www.youtube.com/watch?v=UD9IOllUR4k&quot; title=&quot;Berkeley professor explains gender theory par Big think  &quot;&gt;Les questions de genre &lt;/a&gt;, d'identité et de discrimination, les travaux de Butler offrent des outils conceptuels précieux qui nous invite à remettre en question les normes sociales et à penser de manière critique les catégories auxquelles nous sommes habitués. &lt;/p&gt; &#10;&lt;p&gt; &lt;/p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Gender trouble: théorie queer et études de genre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-21.07.2020-ITEMA_22386626-2020C35448S0203-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E68" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Abram&quot; title=&quot; Wikipedia&quot;&gt;David ABRAM&lt;/a&gt;   est un philosophe américain,  écologiste culturel et géophilosophe,  reconnu pour ses travaux sur l'écologie de la perception et l'animisme. Ancien magicien itinérant, il a étudié auprès de chamanes au Népal et en Indonésie, expériences qui ont nourri sa pensée reliant philosophie occidentale et traditions orales indigènes. Fondateur de l'Alliance for Wild Ethics, il est auteur de The Spell of the Sensuous (1996) et Becoming Animal (2010), ouvrages pionniers en écopsychologie. &lt;/p&gt; &lt;p&gt; Sa philosophie centrale repose sur une  &lt;a href=&quot;https://www.youtube.com/watch?v=Tms_HnOICAo&quot; title=&quot;David Abram la magie est une initiation à la phénoménologie par Philosophie magazine&quot;&gt;&quot;écologie de la perception&quot;, &lt;/a&gt; où le corps humain est indissociable du monde vivant, perçu comme animé et réciproque. Inspiré par Merleau-Ponty, il argue que la langue et la perception humaine émergent du dialogue sensoriel avec la Terre, contre la vision cartésienne d'un sujet isolé face à des objets inertes. L'alphabétisation, dit-il, nous a éloignés de cette participation sensuelle, transformant le monde en texte statique et favorisant   &lt;a href=&quot;https://www.youtube.com/watch?v=lWWNlNKFAuk&quot; title=&quot;David Abram marcher dans un monde de joie par Campus AFD&quot;&gt;l'exploitation écologique. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  réhabilite l'animisme comme vision du monde viable, où animaux, plantes et éléments possèdent une agency propre, entrelacée à la nôtre dans une &quot;chair collective&quot; terrestre. Il critique le matérialisme réductionniste et prône un &quot;nouveau matérialisme&quot; spinoziste, où esprit et matière ne font qu'une substance infinie de modes. Cette pensée invite à &quot;devenir animal&quot; pour réenchanter le monde et affronter la crise climatique par une reconnexion sensorielle. &lt;/p&gt; &lt;p&gt; Influencé par Heidegger et les traditions indigènes, il appelle à raviver une culture orale ancrée dans le lieu, contre l'universalisme abstrait de la modernité. Sa vision, débattue dans des revues comme Environmental Ethics, promeut une éthique participative où l'humain n'est qu'un mode parmi d'autres dans la biosphère vivante. &lt;/p&gt; &lt;audio controls title=&quot;La nature a t’elle ceccé de nous parler ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-12.04.2024-ITEMA_23708479-2024C48904S0103-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="E69" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Boris_Kagarlitsky&quot; title=&quot; Wikipedia&quot;&gt;Boris KAGARLITSKY&lt;/a&gt; est un sociologue, philosophe politique et militant de gauche russe, l'un des représentants les plus connus du post-marxisme et de la gauche critique en Russie contemporaine. Emprisonné sous Brejnev pour ses activités dissidentes dans les années 1970, actif dans les cercles réformistes sous Gorbatchev, il développa après 1991 une pensée critique du capitalisme russe post-soviétique qui lui vaut une reconnaissance internationale croissante.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans le courant du socialisme démocratique et du post-marxisme critique. Ses analyses du capitalisme de rente russe — notamment dans &lt;em&gt;La Vengeance de l'histoire&lt;/em&gt; et &lt;em&gt;L'Empire de la périphérie&lt;/em&gt; — développent une critique du système économique post-soviétique comme forme de capitalisme de rente et de pillage, fondée sur l'extraction des ressources naturelles et le maintien d'une dépendance structurelle vis-à-vis des marchés financiers occidentaux. Cette analyse, qui articule marxisme classique et théorie des systèmes-mondes (Wallerstein), constitue l'une  &lt;a href=&quot;https://www.youtube.com/watch?v=tVpTL54sZNM&quot;  title=&quot;Boris Kargalisky Report on Russia par laborvideo&quot;&gt;des lectures les plus lucides &lt;/a&gt; de l'économie politique russe post-soviétique.&lt;/p&gt;&lt;p&gt;Son engagement politique — il fonda l'Institut de la globalisation et des mouvements sociaux à Moscou — et ses activités journalistiques illustrent une conception de la philosophie politique comme pratique engagée. Arrêté en 2023 dans le contexte de la guerre russo-ukrainienne pour ses prises de position critiques, il représente la figure de l'intellectuel de gauche engagé qui refuse de choisir entre le nationalisme russe et le libéralisme occidental, en maintenant une critique cohérente de toutes les formes de capitalisme et d'autoritarisme.&lt;/p&gt;"/>
+    <hyperlink ref="E70" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexandre_Tarassov&quot; title=&quot; Wikipedia (ru)&quot;&gt;Alexandre TARASSOV&lt;/a&gt; est un philosophe, sociologue et militant marxiste russe, l'un des représentants les plus cohérents du marxisme radical et de la pensée post-marxiste en Russie contemporaine. Chercheur et publiciste, il développe depuis les années 1990 une analyse critique du capitalisme russe post-soviétique et une réflexion théorique sur le marxisme contemporain.&lt;/p&gt;&lt;p&gt;Sa philosophie politique s'inscrit dans une tradition marxiste radicale qui refuse les compromis avec le capitalisme libéral et avec le nationalisme autoritaire russe. Ses analyses des mouvements de jeunesse radicaux — notamment son ouvrage sur les Skinheads soviétiques et ses études sur la contre-culture russe — constituent des contributions sociologiques originales à la compréhension des phénomènes politiques marginaux. Sa réflexion sur le rapport entre culture et politique, entre la contre-culture et les mouvements sociaux, s'inscrit dans la tradition de la théorie critique de la culture marxiste.&lt;/p&gt;&lt;p&gt;Ses travaux théoriques sur le marxisme contemporain — notamment ses analyses des nouvelles formes de domination capitaliste et de résistance sociale — cherchent à renouveler la pensée marxiste en l'adaptant aux conditions du capitalisme global du XXIe siècle, tout en maintenant la rigueur théorique et l'engagement révolutionnaire de la tradition marxiste classique. Tarassov représente la continuité d'une gauche intellectuelle russe radicale qui, malgré la marginalisation politique, maintient vivante une tradition de pensée critique cohérente et rigoureuse face aux dérives libérales et nationalistes de la Russie contemporaine.&lt;/p&gt;"/>
+    <hyperlink ref="H70" r:id="rId45" display="https://www.laphilo.fr/pho/atarassov-mini.webp"/>
+    <hyperlink ref="I70" r:id="rId46" display="https://www.laphilo.fr/photo/tarassov.webp"/>
+    <hyperlink ref="E71" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yujin_Nagasawa&quot; title=&quot; Wikipedia&quot;&gt;Masahiro MORIOKA&lt;/a&gt;  est un philosophe et &lt;a href=&quot;https://www.projetecolo.com/qu-est-ce-que-la-bioethique-definition-et-principes-143.html&quot; title=&quot; Qu'est-ce que la bioéthique - Définition et principes par Projet Ecolo&quot;&gt;bioéthicien&lt;/a&gt; japonnais et son travail est caractérisé par une profonde interrogation sur le sens de la vie, de la mort et de l'existence à l'époque contemporaine. &lt;/p&gt; &lt;p&gt; Une part centrale de sa pensée est constituée par ce qu'il appelle la &quot;philosophie de la vie&quot; où il explore la valeur et le sens de la vie non pas comme une abstraction, mais dans son vécu concret, corporel et relationnel. Il s'intéresse à la façon dont les individus perçoivent la valeur de leur propre existence dans un monde marqué par la souffrance, l'isolement et la perte des repères traditionnels. &lt;a href=&quot;https://www.youtube.com/watch?v=z59AAehikuU&quot; title=&quot; A Japanese approach : between life and death, from nature to artefacts par Maison des sciences humaines&quot;&gt; Cette réflexion &lt;/a&gt; l'a naturellement conduit à des contributions majeures en bioéthique, où il critique l'approche occidentale souvent centrée sur les principes abstraits comme l'autonomie et la justice, pour lui préférer une approche phénoménologique qui part de l'expérience vécue des personnes, de leurs émotions et de leurs relations interconnectées. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est sans doute celui de &quot;l'angoisse de l'existence du lien&quot; ou &quot;l'inquiétude de l'être-en-relation&quot;. Il postule que l'être humain est fondamentalement un &quot;être-de-lien&quot;, toujours défini par ses relations avec les autres, la société et le monde. La souffrance psychique moderne, et en particulier la dépression, proviendrait souvent d'une angoisse liée à ces liens eux-mêmes : la peur de les perdre, la sensation d'être un fardeau dans ces liens, ou l'impression que ces liens nous étouffent et nous aliènent. Cette théorie offre un cadre puissant pour repenser des phénomènes sociaux comme le suicide, le harcèlement scolaire ou l'isolement social, non comme des échecs individuels, mais comme des pathologies du lien social. &lt;/p&gt; &lt;p&gt; Dans le domaine du suicide, il a développé une position nuancée et controversée. Il distingue le suicide comme &quot;arrêt de la vie&quot; de celui comme &quot;arrêt du soi&quot;. Il avance que dans certains cas de souffrance psychique extrême et incurable, où le sentiment d'être un &quot;soi&quot; est détruit, le suicide peut être compris non pas comme un choix de mourir, mais comme la seule issue pour mettre fin à une agonie du soi devenue intolérable. Il défend une approche compréhensive plutôt que purement préventive, qui écoute la souffrance de celui qui envisage le suicide sans le juger moralement. Cette perspective a eu une grande influence sur les lignes d'écoute téléphonique et le soutien aux personnes en détresse au Japon. &lt;/p&gt; "/>
+    <hyperlink ref="E74" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Godefroy_Bidima&quot; title=&quot; Wikipedia&quot;&gt;Jean-Godefroy BIDIMA&lt;/a&gt; est un philosophe et universitaire influent, professeur à l'Université Tulane (Nouvelle-Orléans) et ancien directeur de programme au Collège international de philosophie à Paris. Son œuvre se distingue par un dialogue constant entre la tradition philosophique occidentale, notamment la théorie critique de l'École de Francfort, et les réalités, imaginaires et enjeux politiques du continent africain.https://www.youtube.com/watch?v=pUSqBXfRKCE &lt;/p&gt; &lt;p&gt; Au cœur de sa réflexion se trouve le concept de « palabre », qu'il théorise comme une véritable « juridiction de la parole ». Loin de n'être qu'une simple discussion, la palabre est pour lui une pratique politique et éthique visant à restaurer le lien social et à réguler les conflits au sein de la communauté. Il appelle à « quitter le cri pour forger la parole », une démarche inspirée par Édouard Glissant qui exhorte à substituer aux réactions émotionnelles ou à la simple revendication une réflexion patiente, structurée et créatrice. &lt;/p&gt; &lt;p&gt; Il  développe une « philosophie de la traversée », cherchant à décentrer le regard philosophique pour mieux intégrer les savoirs et les expériences africaines dans le débat universel. Il utilise les outils de la théorie critique pour interroger les discours anthropologiques, juridiques et historiques   &lt;a href=&quot;https://www.youtube.com/watch?v=DuBiS9vGgmg&quot;  title=&quot;environnement transatlantiques par l’humain noir par YeisonArcadio&quot;&gt;portés sur l'Afrique, &lt;/a&gt; cherchant à mettre au jour leurs présupposés normatifs souvent coloniaux. Son travail explore ainsi les intersections entre philosophie, art et imaginaire, plaidant pour une relecture des rapports entre humains et non-humains qui résonne avec les préoccupations contemporaines sur la nature. &lt;/p&gt; &lt;p&gt; En tant qu'intellectuel, il s'est attaché à repenser l'universalité non plus comme une imposition unique, mais comme une construction plurielle née de la rencontre des langues et des cultures. Ses recherches, qui couvrent également des thématiques liées à la santé, aux femmes africaines dans la globalisation et à la création artistique, témoignent d'une exigence de rigueur et d'une volonté de faire de la philosophie un outil de compréhension et de transformation du monde actuel. Par son parcours international et sa position de chercheur « en mouvement », il demeure une figure centrale du renouveau de la pensée africaine contemporaine. &lt;/p&gt;  &lt;audio controls title=&quot;Comment dépasser le post-colonial par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21447-29.09.2021-ITEMA_22790164-2021C27677E0274-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H74" r:id="rId49" display="https://www.laphilo.fr/pho/jgbidima-mini.webp"/>
+    <hyperlink ref="H77" r:id="rId50" display="https://www.laphilo.fr/pho/olombardi-mini.webp"/>
+    <hyperlink ref="H78" r:id="rId51" display="https://www.laphilo.fr/pho/egudynas-mini.webp"/>
+    <hyperlink ref="H80" r:id="rId52" display="https://www.laphilo.fr/pho/wlubbe-mini.webp"/>
+    <hyperlink ref="I80" r:id="rId53" display="https://www.laphilo.fr/photo/wlubbe.webp"/>
+    <hyperlink ref="E83" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nick_Land&quot; title=&quot; Wikipedia&quot;&gt;Nick LAND&lt;/a&gt; est un philosophe britannique, figure centrale et controversée dont l'œuvre a profondément marqué la philosophie contemporaine par son radicalisme et son rejet de l'anthropocentrisme. Ancien membre de la Cybernetic Culture Research Unit à l'Université de Warwick dans les années 1990, son parcours intellectuel a évolué d'une critique radicale inspirée par le post-structuralisme vers des positions néoréactionnaires et hyper-libérales. &lt;/p&gt; &lt;p&gt; Son concept phare est &lt;a href=&quot;https://fr.wikipedia.org/wiki/Acc%C3%A9l%C3%A9rationnisme&quot;  title=&quot;accélerationisme par Wikipedia &quot;&gt;l'accélérationnisme,&lt;/a&gt;  une théorie selon laquelle le capitalisme doit être poussé jusqu'à ses limites extrêmes pour transformer radicalement la société. Contrairement à une vision humaniste ou réformiste, il perçoit le capitalisme comme un processus autonome et autodestructeur qui, une fois libéré des entraves démocratiques et étatiques, mènera inévitablement à une singularité technologique. Pour lui, cette force « technocapitaliste » est une  &lt;a href=&quot;https://legrandcontinent.eu/fr/2025/09/07/accelerer-le-capitalisme-pour-sortir-de-lhumanite-les-propheties-de-nick-land-mage-des-lumieres-noires/&quot;  title=&quot;qui est Nick Land par le grand continent &quot;&gt;puissance impersonnelle &lt;/a&gt;  qui dépasse l'humanité, laquelle ne serait qu'un hôte temporaire voué à être dépassé par ses propres créations. &lt;/p&gt; &lt;p&gt; À partir des années 2010, il a développé une pensée « néoréactionnaire » s'opposant frontalement à l'égalitarisme et à la démocratie libérale, qu'il accuse d'entraver le progrès et l'efficacité. Il prône un modèle de gouvernance inspiré par l'autoritarisme gestionnaire, suggérant que   &lt;a href=&quot;https://www.youtube.com/watch?v=krFQdLCx3kA&quot;  title=&quot;Nick Land par France culture &quot;&gt;l'État devrait être géré &lt;/a&gt; comme une entreprise privée par une élite dirigeante. Cette vision, souvent associée à l'alt-right, rejette les idéaux des Lumières et de la justice sociale au profit d'une hiérarchie fondée sur la compétence technologique et la performance économique. &lt;/p&gt; &lt;p&gt; Son style d'écriture est aussi singulier que ses thèses, mêlant philosophie académique, science-fiction, culture rave et occultisme. Il a inventé le concept de « hyperstition » pour désigner des idées qui, par leur diffusion et leur impact culturel, finissent par créer leur propre réalité. Par cette approche, il ne cherche pas seulement à décrire le monde, mais à « programmer » des futurs possibles, faisant de son œuvre une tentative de fusionner la pensée théorique avec les dynamiques de mutation technologique et sociale les plus brutales. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
+    <hyperlink ref="H83" r:id="rId55" display="https://www.laphilo.fr/pho/nland-mini.webp"/>
+    <hyperlink ref="E84" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Iain_Hamilton_Grant&quot;  title=&quot; Wikipedia&quot;&gt;Iain HAMILTON GRANT&lt;/a&gt; est un philosophe britannique, maître de conférences et sa pensée est particulièrement influente dans le courant du &lt;a href=&quot;https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif&quot;  title=&quot;speculative realism  par Wikipedia&quot;&gt;réalisme spéculatif&lt;/a&gt;, auquel il apporte une contribution originale par une ontologie centrée sur la nature et le domaine inorganique. Il a écrit sa thèse sur Kant et Lyotard à l’Université de Warwick, où il a participé à des travaux interdisciplinaire sur la culture cybernétique. Sa philosophie puise ses sources dans Platon, Friedrich Schelling, mais aussi Gilles Deleuze, tout en s’opposant à Aristote et Kant, critiquant leur réduction de la réalité à sa seule expressibilité humaine. &lt;/p&gt; &lt;p&gt; Son livre majeur,  &lt;a href=&quot;https://www.youtube.com/watch?v=5LGODQdFaw0&quot;  title=&quot;Schelling’s Philosophy of Nature  par Philosophical Bachelor&quot;&gt;&quot;Philosophies of Nature After Schelling&quot;&lt;/a&gt; paru en 2006, renouvelle l’intérêt contemporain pour la philosophie naturelle et l’idéalisme allemand, notamment chez Schelling. Il plaide pour un retour à la question de l’inorganique et propose une critique radicale du primat de l’humanité dans la philosophie continentale, soulignant la nécessité de repenser la nature comme productrice d’activité et de devenir. Son ouvrage &quot;On an Artificial Earth&quot; développe cette dimension en invitant à « renverser Kant » plutôt que Platon, afin de mieux répondre aux défis de la philosophie moderne et des sciences naturelles. &lt;/p&gt; &lt;/p&gt; Il se distingue par une ontologie de la puissance et du devenir, accordant un rôle central à la productivité de la nature et à ses forces et il s’intéresse à la philosophie de la nature, à la métaphysique du processus, à la science et à la condition transcendantale du réel. Son travail s’inscrit à la croisée de l’idéalisme allemand, du matérialisme spéculatif et d’une conception cosmologique de la philosophie, qui traverse la pensée contemporaine.​ &lt;/p&gt; "/>
+    <hyperlink ref="E86" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hartmut_Rosa&quot;  title=&quot; Wikipedia&quot;&gt;Hartmut ROSA&lt;/a&gt; est un sociologue et philosophe allemand connu pour sa contribution à la &lt;a href=&quot;https://laviedesidees.fr/Naissance-de-la-theorie-critique#page&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Naissance de la théorie critique par Collège de France &quot;&gt;théorie critique&lt;/a&gt; et pour ses travaux sur le concept de &quot;résonance&quot; et la théorie de l'accélération sociale. Il s'intéresse particulièrement aux dynamiques qui façonnent nos vies dans la société moderne. Selon lui, l'accélération sociale, c'est-à-dire l'augmentation constante du rythme et de l'intensité de nos activités, a des conséquences profondes sur notre expérience du monde et notre relation aux autres.  &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de &lt;a href=&quot;https://www.youtube.com/watch?v=fMd-6viV6Gc&quot;  title=&quot;concepts raisonnance par Sébastien Daxi &quot;&gt;la résonance&lt;/a&gt; propose un moyen de retrouver un lien plus harmonieux avec notre environnement et les autres individus. La résonance se produit lorsque nous entrons en contact authentique avec le monde qui nous entoure, ce qui crée un sentiment d'attachement et de plénitude. Selon Rosa, la quête de résonance est essentielle pour préserver notre bien-être et notre humanité dans une société marquée par l'accélération et la superficialité. &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs ouvrages, dont &lt;a href=&quot;https://major-prepa.com/culture-generale/hartmut-rosa-la-tripartition-du-monde-la-resonance/&quot; title=&quot;La résonance par Major-prepa &quot;&gt; &quot;Resonanz - Eine Soziologie der Weltbeziehung&quot;&lt;/a&gt; (Résonance - Une sociologie de la relation au monde)  ainsi que  &quot;Resonanz: A Sociology of Our Relationship to the World&quot;  où il propose une théorie de la résonance comme qualité des relations humaines avec le monde. Dans cette théorie, il explique comment les individus recherchent des relations résonantes, c'est-à-dire des relations qui les stimulent et les enrichissent mutuellement.. &lt;/p&gt; &lt;p&gt;&#10;Il est l'un des sociologues émergents et est reconnu pour son ouverture à l'égard des autres théories et traditions. &lt;/p&gt; &lt;audio controls title=&quot;Hartmut ROSA, philosophe de la résonance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.09.2018-ITEMA_21828397-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="H89" r:id="rId58" display="https://www.laphilo.fr/pho/dbenatar-mini.webp"/>
+    <hyperlink ref="E90" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Jennifer_Saul&quot; title=&quot; Wikipedia&quot;&gt;Jennifer SAUL&lt;/a&gt;  est une philosophe américaine  spécialisée en philosophie du langage, en philosophie féministe et en philosophie de l'esprit. Elle est connue pour ses travaux sur les &lt;a href=&quot;https://www.youtube.com/watch?v=2_FqrHs9S-s&quot; title=&quot;Jennifer Saul: 'Why Implicit Bias Matters' par The Royal Institute of Philosophy&quot;&gt;biais implicites&lt;/a&gt; et de leur impact sur les comportements sociaux. Elle explore comment ils influencent les décisions, les interactions et les structures sociales, même en l'absence de préjugés explicites, le langage et le genre, ainsi que pour ses analyses des questions liées à la discrimination et à l'oppression. &lt;/p&gt; &lt;p&gt; Elle s'intéresse aussi à la manière dont le langage peut véhiculer des stéréotypes et renforcer des inégalités, même lorsque les locuteurs n'en ont pas conscience. Son livre &quot;Lying, Misleading, and What Is Said&quot; aborde notamment les questions de tromperie et de manipulation linguistique. &lt;/p&gt; &lt;p&gt; Dans son ouvrage  &quot;Feminism: Issues &amp; Arguments&quot;, elle examine des débats clés du féminisme, comme la définition du genre, l'objectification ou les controverses autour de la pornographie et de la prostitution. Elle défend une approche analytique rigoureuse des questions féministes. &lt;/p&gt; &lt;p&gt;  Elle est également active dans la promotion de la diversité en philosophie et a cofondé le &quot;Women in Philosophy Task Force&quot; au Royaume-Uni pour lutter contre le sexisme dans le milieu académique. &lt;/p&gt; &lt;p&gt;  Elle intervient régulièrement dans des  &lt;a href=&quot;https://www.youtube.com/watch?v=QDcuCIqCWdQ&quot; s title=&quot; Interview: Jenny Saul and Nadia Mehdi par The Royal Institute of Philosophy&quot;&gt;débats publics&lt;/a&gt; sur le harcèlement, les inégalités de genre et les politiques universitaires. Elle combine une méthodologie analytique avec une perspective clairement engagée, montrant comment la philosophie peut éclairer des problèmes sociaux urgents. Son travail est influent aussi bien en philosophie académique que dans les discussions sur les politiques publiques. &lt;/p&gt; "/>
+    <hyperlink ref="E92" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Graham_Harman&quot;   title=&quot; Wikipedia&quot;&gt;Graham HARMAN&lt;/a&gt; est un philosophe américain, figure clé du mouvement du &lt;a href=&quot;https://www.youtube.com/watch?v=2voNdhpfbm0&amp;t=190s&quot; style=&quot;color:#88A1E9&quot; title=&quot; Speculative Realism | Graham Harman par The Institute of Art and Ideas &quot;&gt;&quot;réalisme spéculatif&quot;&lt;/a&gt; et co-fondateur de l'ontologie orientée objet (OOO). Sa  philosophie est une réaction contre ce qu'il appelle le &quot;corrélationnisme&quot;, l'idée selon laquelle l'existence de la réalité est inséparable de la perception humaine. Il cherche à redonner une  &lt;a href=&quot;https://www.youtube.com/watch?v=KTeyDSDcXzQ&quot;  title=&quot; Des choses dans le vide. Ce qu'on peut apprendre de Graham Harman par Ars Industrialis &quot;&gt; place centrale aux objets&lt;/a&gt;, qu'ils soient réels, fictifs, naturels, artificiels, humains ou non-humains, en affirmant leur existence indépendante de notre esprit et même de leurs relations causales. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=uxDmQ-Hn2X0&quot;  title=&quot;  Object-Oriented Ontology: A New Theory of Everything w/ Graham Harman par derek g larson &quot;&gt; (OOO) &lt;/a&gt; est le cœur de sa philosophie. Il affirme que les objets sont les entités fondamentales de la réalité. Chacun d'eux, qu'il s'agisse d'une tasse de café, d'une montagne, d'un État ou d'une idée, possède une existence autonome et &quot;se retire&quot; de la pleine compréhension, que ce soit par un esprit humain ou par d'autres objets. Pour lui les objets ne peuvent jamais être pleinement appréhendés ou épuisés par nos sens, notre intellect ou même par leurs interactions avec d'autres objets. Il y a toujours une part de l'objet qui reste cachée, insaisissable, une &quot;réalité souterraine&quot; des choses. &lt;/p&gt; &lt;p&gt; Il distingue les objets réels, qui existent indépendamment de toute perception, des objets sensuels, qui sont les objets tels qu'ils nous apparaissent ou tels qu'ils interagissent avec d'autres objets. La tension entre ce que l'objet est réellement (son retrait) et ce qu'il nous présente ou ce qu'il est pour d'autres objets est une dynamique importante de sa pensée. &lt;/p&gt; &lt;p&gt; Il  privilégient l'épistémologie ou l'éthique et met l'accent sur la métaphysique (l'étude de la nature de la réalité). Il considère également que &lt;a href=&quot;https://www.youtube.com/watch?v=QJ0GR9bf00g&quot; title=&quot; Graham Harman: Objects and the Arts par ICA &quot;&gt; l'esthétique &lt;/a&gt; joue un rôle fondamental dans notre appréhension des objets, car l'art, la littérature et la métaphore peuvent nous donner un accès indirect à la réalité retirée des objets, là où la connaissance conceptuelle échoue. &lt;/p&gt; "/>
+    <hyperlink ref="H93" r:id="rId61" display="https://www.laphilo.fr/pho/tgiraud-mini.webp"/>
+    <hyperlink ref="E96" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alexander_Schnell&quot; title=&quot; Wikipedia&quot;&gt;Alexander SCHNELL&lt;/a&gt;   est un philosophe  germano-bulgare spécialiste de l'idéalisme allemand (Kant, Fichte, Schelling) et de la phénoménologie (Husserl, Heidegger, Fink, Richir, Lévinas), il publie une trentaine d'ouvrages en français et allemand, comme Husserl et les fondements de la phénoménologie constructive (2007), Was ist Phänomenologie? (2019) ou sa trilogie récente : La déhiscence du sens (2015), Le clignotement de l’être (2021) et Préphénoménalité et générativité (2025). Il traduit aussi des textes philosophiques et édite des volumes collectifs. &lt;/p&gt; &lt;p&gt; Il développe une &lt;a href=&quot;https://www.youtube.com/watch?v=PuQPvr3xhEM&quot; title=&quot;Prephenomenalité alexxander Schnell et Charles Bobant par Salon Tout Art&quot;&gt;« phénoménologie constructive » &lt;/a&gt; ou « transcendantalisme spéculatif », reprenant le projet husserlien d'une phénoménologie de la connaissance comme idéalisme transcendantal, en intégrant imagination, inconscient phénoménologique, préphénoménalité et générativité. Ses travaux lient philosophie allemande classique, phénoménologie allemande et française, avec des accents sur esthétique et anthropologie, critiquant le primat descriptif au profit de constructions spéculatives. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E97" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Felwine_Sarr&quot;  title=&quot; Wikipedia&quot;&gt;Fenwine SARR&lt;/a&gt; est un philosophe, écrivain, économiste et musicien sénégalais, figure majeure de la pensée africaine contemporaine, il occupe actuellement la chaire Anne-Marie Bryan à l’Université Duke aux États-Unis, où il est professeur de philosophie africaine contemporaine et diasporique. &lt;/p&gt; &lt;p&gt; Il  est reconnu pour son essai marquant,  &lt;a href=&quot;https://www.youtube.com/watch?v=gty0PculB7U&quot;  title=&quot;Afrotopia par david Mboussou&quot;&gt;&quot;Afrotopia&quot; &lt;/a&gt;  ou il propose à la jeunesse africaine de s’affranchir des blessures du passé pour redevenir sujet de son destin, imaginer librement l’avenir, et construire un horizon fondé sur ses atouts propres, qui invite à repenser le futur du continent africain hors des modèles imposés, en valorisant une utopie africaine propre. Il est aussi auteur de plusieurs ouvrages, dont  &quot;Dahij, Méditations africaines&quot;  , &quot;Habiter le monde&quot; et &quot;Les lieux qu’habitent mes rêves&quot;. &lt;/p&gt;&lt;p&gt; Il invite à repenser le monde et l'Afrique à partir des perspectives et des expériences africaines, au lieu de modèles hérités de l'extérieur. Son œuvre prône une décolonisation des savoirs, une valorisation des potentiels endormis du continent et une ouverture à de nouvelles utopies portées par l’Afrique elle-même. Il  propose une « éthique du voyage » : être  &lt;a href=&quot;https://www.youtube.com/watch?v=TVXc5KT_Z6Q&quot; title=&quot;Felwine Sarr : Laisser le monde plus habitable que nous l’avons trouvé par AFD&quot;&gt;disponible au monde &lt;/a&gt; , sortir des assignations identitaires, multiplier les rencontres et apprendre de l’inattendu, loin des approches extractivistes ou exotiques. Cela implique une capacité à se laisser transformer par les lieux, les autres, et à regarder le monde depuis sa propre place, pour contribuer à une pluralité des voix et des expériences. &lt;/p&gt; &lt;p&gt; Sa philosophie est une invitation à renouer avec les potentiels créateurs de l’Afrique, à valoriser la multiplicité des regards sur le monde, et à engager un projet collectif pour redéfinir le devenir africain et humain à partir de ses propres ressources. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Felwine Sarr, habiter poétiquement le monde par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/23356-13.08.2022-ITEMA_23105530-2022C48096E0003-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E99" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joshua_Knobe&quot;  title=&quot; Wikipedia&quot;&gt;Joshua KNOBE&lt;/a&gt; est un philosophe américain,  figure marquante de la  &lt;a href=&quot;https://www.youtube.com/watch?v=t-2QldptRis&quot; style=&quot;color:#88A1E9&quot; title=&quot; Théorie de l'action et Effet Knobe (Introduction à la Philosophie Expérimentale) par Empeiria&quot;&gt;philosophie expérimentale&lt;/a&gt; . Il est actuellement professeur de sciences cognitives et de philosophie à l'Université de Yale. Son domaine de réflexion principal est l'utilisation de méthodes expérimentales issues des sciences cognitives pour aborder des questions philosophiques traditionnelles. Ses travaux portent sur des sujets variés, notamment : &lt;/p&gt; &lt;p&gt; - &lt;a href=&quot;https://www.youtube.com/watch?v=LqJD_l7wHw4&quot;  title=&quot; What is Theory of Mind? par Closer To Truth&quot;&gt;La philosophie de l'esprit&lt;/a&gt; : En étudiant nos intuitions sur la conscience. &lt;/p&gt; &lt;p&gt; - La théorie de l'action : En examinant comment nous attribuons l'intentionnalité. &lt;/p&gt; &lt;p&gt; - L'éthique et la morale : En analysant nos jugements moraux et nos intuitions face à des dilemmes. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la découverte et l'analyse de &lt;a href=&quot;https://www.youtube.com/watch?v=MC2bAYaWDNU&quot; title=&quot; What is the Knobe Effect? par Philosophical Questions&quot;&gt;&quot;l'effet Knobe&quot;&lt;/a&gt;. Cet effet met en lumière une asymétrie dans nos jugements d'intentionnalité basée sur la valence morale des conséquences d'une action. En d'autres termes, nous sommes plus enclins à juger qu'une personne a intentionnellement causé un effet négatif (même si ce n'était pas son but principal) que si elle a causé un effet positif de manière similaire. &lt;/p&gt; &lt;p&gt; Par exemple, dans un scénario classique, un PDG lance un projet qui augmente les profits de son entreprise mais nuit également à l'environnement. La plupart des gens jugent que le PDG a intentionnellement nui à l'environnement. Cependant, dans un scénario où le même projet profite à l'environnement en plus d'augmenter les profits, les gens sont moins enclins à dire que le PDG a intentionnellement aidé l'environnement. &lt;/p&gt; "/>
+    <hyperlink ref="E102" r:id="rId65" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Markus_Gabriel&quot;   title=&quot; Wikipedia&quot;&gt; Markus GABRIEL&lt;/a&gt; est un jeune philosophe Allemand qui est une figure de plus en plus remarquée dans le paysage philosophique mondial. Affirmant une rupture radicale avec la pensée occidentale, il prône un  &lt;a href=&quot;https://www.lesinrocks.com/livres/markus-gabriel-existe-excepte-monde-105595-30-09-2014/&quot;   title=&quot;Markus Gabriel par les Inrockuptibles&quot;&gt;“nouveau réalisme”&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il s'est fait connaître pour sa théorie de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ontologie_(philosophie)&quot;  title=&quot;Ontologie par Wikipédia&quot;&gt;l'ontologie&lt;/a&gt; nouvelle, qui propose une conception nouvelle de la réalité, en opposition à la métaphysique traditionnelle. Selon lui, la réalité n'est pas quelque chose qui existe en soi, indépendamment de notre perception et de notre connaissance, mais plutôt quelque chose qui est créé par notre propre activité cognitive. Autrement dit, la réalité est une construction sociale, qui dépend de notre langage et de notre culture et non de la perception humaine et qui existe indépendamment de notre esprit. &lt;/p&gt; &lt;p&gt; &#10;Il a écrit de nombreux livres, dont  « Pourquoi le monde n'existe pas », « Je ne suis pas un cerveau : philosophie de l'esprit pour le 21e siècle » et  &lt;a href=&quot;https://www.youtube.com/watch?v=cRxd09vFcxg&amp;ab_channel=FRANCE24&quot;     style=&quot;color:#88A1E9&quot;  title=&quot;Le pouvoir de l'Art par France 24&quot;&gt;&quot; Le pouvoir de 'Art&quot;&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Il contribue également régulièrement à divers journaux et magazines et est apparu dans de nombreuses émissions de télévision et de radio pour discuter de ses idées. &lt;/p&gt;   &lt;audio controls title=&quot;Si google anticipe pour moi, cela ne veut pas dire qu'il choisit pour moi  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16602-10.02.2017-ITEMA_21225836-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E103" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://www.robindembroff.com/&quot;  title=&quot; Wikipedia&quot;&gt;Robin DEMBROFF&lt;/a&gt; est un(e) philosophe américaine travaillant sur les questions de genre, ancré dans la métaphysique, la philosophie du genre, et la théorie queer, iel soulève les zones floues de l’identité en interrogant les catégories qui nous définissent, les mots que l’on utilise pour dire &quot;homme&quot;, &quot;femme&quot;, &quot;non-binaire&quot;, et surtout : pourquoi ces mots ont tant de poids sur nos vies. &lt;/p&gt; &lt;p&gt;  Robin se pose une question simple mais explosive : Et si le genre n’était pas ce que l’on croit ? De là naît une série de textes qui dérangent, qui déplacent, qui éclairent. Iel refuse les définitions rigides car le genre est une construction sociale, oui, mais c’est aussi un  &lt;a href=&quot;https://www.youtube.com/watch?v=-mHFFs49S3o&quot; title=&quot;Robin Dembroff presents at the 2022 Gender and Work Symposium par Havard Business School&quot;&gt;champ de bataille&lt;/a&gt;, un territoire politique, et un espace de résistance. Iel y développe l’idée que l’identité non-binaire n’est pas seulement une absence ou un entre-deux du masculin et du féminin, mais une &lt;a href=&quot;https://www.youtube.com/watch?v=-pNmvthQLds&quot;  title=&quot;&#10;What is sexual orientation? Part I par Center for Philosophy of Religion&quot;&gt;position à part entière&lt;/a&gt;. Une manière de dire non au système de genre binaire, tout en affirmant sa propre existence. &lt;/p&gt; &lt;p&gt; Dans ses écrits – parfois techniques, toujours engagés – on sent la chaleur d’un feu ancien : celui de la justice. Iel écrit comme on lutte, avec précision, mais aussi avec une tendresse désarmante pour celles et ceux qui cherchent leur place dans un monde trop étroit. &lt;/p&gt; "/>
+    <hyperlink ref="E106" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amia_Srinivasan&quot;  title=&quot; Wikipedia&quot;&gt;Amia SRINIVASAN&lt;/a&gt; est une femme philosophe d'origine indienne qui a grandi entre Taïwan, Singapour, New York et Londres. Son parcours cosmopolite a nourri une pensée profondément ancrée dans les réalités multiples du monde contemporain. &lt;/p&gt; &lt;p&gt;  En janvier 2020, elle devient la première femme et la première personne de couleur à occuper la prestigieuse chaire Chichele de théorie sociale et politique à l'université d'Oxford. Son travail se concentre sur l'épistémologie, la philosophie politique, la métaphilosophie et la &lt;a href=&quot;https://www.lesinrocks.com/livres/amia-srinivasan-une-nouvelle-voix-feministe-503329-05-10-2022/&quot; title=&quot;THE RIGHT TO SEX | Amia Srinivasan &amp; Sarah Leonard par Books Are Magic&quot;&gt;théorie féministe&lt;/a&gt; . &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=6NjzLlQG5cU&quot;   title=&quot;Amia Srinivasan, une nouvelle voix féministe par Les Inrockuptibles&quot;&gt;Le droit au sexe&lt;/a&gt;, publié en 2021, est une collection d'essais qui explore les intersections entre le désir sexuel, le pouvoir, la race et le genre. Elle y examine comment les normes sociales et politiques influencent nos désirs et comportements sexuels, abordant des sujets tels que le racisme sexuel, les incels, le capitalisme et le mouvement #MeToo.  Elle a aussi publié des articles dans des revues prestigieuses telles que The Philosophical Review, Journal of Political Philosophy et Philosophy &amp; Phenomenological Research. Elle est également éditrice contributrice pour la London Review of Books. &lt;/p&gt; &lt;p&gt; Actuellement, elle travaille sur un second livre intitulé &quot;The Contingent World: Genealogy, Epistemology, Politics&quot;, qui portera sur la pratique de la généalogie critique. Elle s'intéresse également à la place des mouvements identitaires dans la gauche politique, à la philosophie de l'histoire et aux droits des animaux. &lt;/p&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -8044,12 +8044,64 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7">
+        <v>1933</v>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1933</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sulak SIVARAKSA</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Sulak_Sivaraksa" title=" Wikipedia (en)"&gt;Sulak SIVARAKSA&lt;/a&gt; est un intellectuel, écrivain et militant thaïlandais, l’une des grandes figures du bouddhisme engagé. Né à Bangkok dans une famille sino-thaïe aisée, il étudie au pays de Galles, à Lampeter, puis devient avocat à Londres en 1961. De retour en Thaïlande, il dirige la &lt;em&gt;Social Science Review&lt;/em&gt;, qui devient dans les années 1960 la grande revue intellectuelle du pays, et fonde en 1968 une fondation qui soutient de nombreuses associations sociales, écologiques et culturelles.&lt;/p&gt; &lt;p&gt;Bouddhiste laïc, il refuse un bouddhisme réduit aux rituels et au mérite individuel, et parle d’un bouddhisme « avec un petit b », tourné vers la justice et la non-violence plutôt que vers les institutions. Pour lui, les trois poisons de l’enseignement du Bouddha, l’avidité, la haine et l’illusion, ne sont pas seulement des fautes personnelles : ils se sont incarnés dans des structures, la société de consommation, le militarisme et les inégalités. Il critique ainsi un modèle de développement importé d’Occident qui détruit les communautés villageoises, la nature et les cultures locales, et lui oppose une économie de la mesure et du partage.&lt;/p&gt; &lt;p&gt;Il est en 1989 l’un des fondateurs du Réseau international des bouddhistes engagés, placé sous le patronage du dalaï-lama et de Thich Nhat Hanh. Ses critiques du pouvoir lui valent d’être poursuivi à plusieurs reprises pour crime de lèse-majesté, en 1984 puis en 1991, ce qui le contraint à l’exil jusqu’à son acquittement en 1995. La même année, il reçoit le &lt;a href="https://fr.wikipedia.org/wiki/Right_Livelihood_Award" title=" Wikipedia"&gt;prix Nobel alternatif&lt;/a&gt;. Parmi ses livres traduits figure &lt;em&gt;Seeds of Peace&lt;/em&gt; (1992).&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G109" s="1"/>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sivaraksa-mini.webp</t>
+        </is>
+      </c>
       <c r="I109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
-      <c r="Q109" s="1"/>
+      <c r="J109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thaïlandaise</t>
+        </is>
+      </c>
+      <c r="K109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Theravada</t>
+        </is>
+      </c>
+      <c r="M109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">intellectuel bouddhiste thaïlandais, figure du bouddhisme engagé et critique du développement consumériste.</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P109">
+        <v>2</v>
+      </c>
+      <c r="Q109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; critique</t>
+        </is>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="0"/>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -8104,21 +8104,71 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0"/>
+      <c r="A110" s="0">
+        <v>1928</v>
+      </c>
       <c r="B110" s="0"/>
-      <c r="C110" s="0"/>
-      <c r="D110" s="0"/>
-      <c r="E110" s="0"/>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sylvia WYNTER</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sylvia_Wynter" title=" Wikipedia"&gt;Sylvia WYNTER&lt;/a&gt; est une philosophe, romancière, dramaturge et essayiste jamaïcaine, l’une des grandes penseuses décoloniales. Née à Cuba de parents jamaïcains, elle grandit en &lt;a href="https://fr.wikipedia.org/wiki/Jama%C3%AFque" title=" Wikipedia"&gt;Jamaïque&lt;/a&gt;, étudie les lettres espagnoles à Londres, puis se consacre au théâtre et à la danse et publie en 1962 un roman, &lt;em&gt;The Hills of Hebron&lt;/em&gt;. Elle enseigne ensuite à l’université des Indes occidentales, puis en Californie et à l’université Stanford, de 1977 à 1997.&lt;/p&gt; &lt;p&gt;Sa pensée part d’une question : qui a été défini comme « humain » depuis la Renaissance ? Selon elle, l’Occident a imposé une figure particulière de l’Homme comme si elle était l’humanité tout entière : c’est la « surreprésentation de l’Homme ». Cette figure a changé de forme, d’abord sujet politique et rationnel, puis être économique défini par la biologie, mais elle s’est toujours construite contre d’autres, les Indiens, les Africains, les pauvres, rejetés hors de l’humanité véritable. L’année 1492 marque pour elle le début de ce nouvel ordre du monde.&lt;/p&gt; &lt;p&gt;Reprenant Fanon, pour qui l’être humain n’est pas seulement biologique mais aussi façonné par les récits qu’une société se raconte, elle invite à inventer d’autres manières d’être humain, en écoutant ceux qui ont été exclus de la définition dominante. Ses essais, notamment « Unsettling the Coloniality of Being/Power/Truth/Freedom » (2003), ont profondément influencé les études noires, féministes et décoloniales. Elle a aussi écrit pour la radio et le théâtre, notamment une pièce sur la révolte jamaïcaine de Morant Bay, en 1865.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="F110" s="0"/>
       <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/wynter-mini.webp</t>
+        </is>
+      </c>
       <c r="I110" s="0"/>
-      <c r="J110" s="0"/>
-      <c r="K110" s="0"/>
-      <c r="L110" s="0"/>
-      <c r="M110" s="0"/>
-      <c r="P110" s="0"/>
-      <c r="Q110" s="0"/>
+      <c r="J110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jamaïcaine</t>
+        </is>
+      </c>
+      <c r="K110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et écrivaine jamaïcaine, critique de la « surreprésentation de l’Homme » occidental.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P110" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3299,7 +3299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD110"/>
+  <dimension ref="A1:XFD111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -8167,6 +8167,64 @@
       <c r="Q110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0">
+        <v>1935</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENZIN GYATSO, 14e dalaï-lama</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tenzin_Gyatso" title=" Wikipedia"&gt;TENZIN GYATSO, 14e dalaï-lama&lt;/a&gt; est le quatorzième dalaï-lama, chef spirituel du bouddhisme tibétain, et l’une des grandes figures morales de notre temps. Né en 1935 dans une famille paysanne de l’Amdo, il est reconnu à deux ans comme la réincarnation du treizième dalaï-lama et reçoit une formation monastique complète, couronnée par le plus haut diplôme de philosophie bouddhiste. En 1950, la Chine envahit le Tibet ; après l’échec du soulèvement de Lhassa en 1959, il s’exile en Inde, à Dharamsala, où il établit un gouvernement tibétain en exil.&lt;/p&gt; &lt;p&gt;Il défend la cause tibétaine par la non-violence, en réclamant une véritable autonomie plutôt que l’indépendance, ce qui lui vaut le &lt;a href="https://fr.wikipedia.org/wiki/Prix_Nobel_de_la_paix" title=" Wikipedia"&gt;prix Nobel de la paix&lt;/a&gt; en 1989. Dans &lt;em&gt;Sagesse ancienne, monde moderne&lt;/em&gt; (1999), il propose une « éthique séculière », fondée non sur une religion mais sur l’expérience commune : tous les êtres veulent le bonheur et refusent la souffrance. La compassion n’est pas pour lui une vertu religieuse mais une nécessité humaine, que l’on peut cultiver par l’éducation.&lt;/p&gt; &lt;p&gt;Curieux des sciences, il dialogue depuis des décennies avec des physiciens, des neuroscientifiques et des psychologues, notamment sur les effets de la méditation, et déclare que si la science réfute une croyance bouddhiste, il faut abandonner cette croyance. En 2011, il renonce à son rôle politique au profit d’un dirigeant élu par les Tibétains en exil. Il enseigne dans le monde entier les textes de Nagarjuna, de Shantideva et de Tsongkhapa.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dalailama-mini.webp</t>
+        </is>
+      </c>
+      <c r="J111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tibétaine</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana</t>
+        </is>
+      </c>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chef spirituel du bouddhisme tibétain en exil, prix Nobel de la paix, penseur d’une éthique universelle de la compassion.</t>
+        </is>
+      </c>
+      <c r="O111" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P111" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3299,7 +3299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD111"/>
+  <dimension ref="A1:XFD112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -8225,6 +8225,64 @@
       <c r="Q111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0">
+        <v>1945</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">né vers 1945</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mogobe RAMOSE</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mogobe_Ramose" title=" Wikipedia (en)"&gt;Mogobe RAMOSE&lt;/a&gt; est un philosophe sud-africain, l’un de ceux qui ont fait connaître dans le monde entier la philosophie africaine, et en particulier l’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;. Sa date de naissance n’est pas connue avec précision. Opposant à l’apartheid, il doit quitter son pays et vit longtemps en exil comme réfugié politique en Belgique, où il soutient en 1983 un doctorat de philosophie à l’université catholique de Louvain ; il étudie aussi les relations internationales à la London School of Economics.&lt;/p&gt; &lt;p&gt;Rentré en Afrique du Sud en 1996, il enseigne à l’université du Venda, puis à l’université d’Afrique du Sud, à Pretoria. Dans &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt; (1999), il fait de l’ubuntu, « une personne est une personne par les autres personnes », une véritable philosophie et non une simple sagesse populaire. Il décompose le mot : &lt;em&gt;ubu&lt;/em&gt; désigne l’être en général, toujours en mouvement, et &lt;em&gt;ntu&lt;/em&gt; sa manifestation concrète dans les êtres et les personnes. Pour l’ubuntu, l’être est un devenir, et la personne n’existe que dans des relations, avec les vivants, les ancêtres et ceux qui ne sont pas encore nés.&lt;/p&gt; &lt;p&gt;Ramose en tire une pensée de la justice : la colonisation et le racisme ont nié l’humanité commune du colonisateur et du colonisé, et la fin de l’apartheid ne suffit pas tant que la conquête, notamment celle des terres, n’a pas été réparée. Héritier du panafricanisme de &lt;a href="https://fr.wikipedia.org/wiki/Robert_Sobukwe" title=" Wikipedia"&gt;Robert Sobukwe&lt;/a&gt;, il critique l’idée, présente chez Hegel, que l’Afrique serait hors de l’histoire et que la raison appartiendrait à l’Occident, et défend un vrai dialogue entre les philosophies du monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ramose-mini.webp</t>
+        </is>
+      </c>
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sud-Africaine</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ubuntu ; Philosophie africaine</t>
+        </is>
+      </c>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe sud-africain, grand penseur de l’ubuntu comme philosophie de la justice et de la libération.</t>
+        </is>
+      </c>
+      <c r="O112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P112" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3299,7 +3299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD112"/>
+  <dimension ref="A1:XFD114"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -8283,6 +8283,127 @@
       <c r="Q112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0">
+        <v>1934</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1934</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wole SOYINKA</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wole_Soyinka" title=" Wikipedia"&gt;Wole SOYINKA&lt;/a&gt; est un dramaturge, poète, romancier et essayiste nigérian, premier écrivain africain à recevoir le &lt;a href="https://fr.wikipedia.org/wiki/Prix_Nobel_de_litt%C3%A9rature" title=" Wikipedia"&gt;prix Nobel de littérature&lt;/a&gt;, en 1986. Né à Abeokuta, dans le pays yoruba, il étudie à Ibadan puis à Leeds, travaille au théâtre à Londres et fonde plusieurs troupes au Nigeria. Il crée aussi ses propres pièces, dont &lt;em&gt;La Mort et l’Écuyer du roi&lt;/em&gt; (1975), une tragédie sur le sens du sacrifice et la rencontre entre l’Afrique et le pouvoir colonial.&lt;/p&gt; &lt;p&gt;Il se méfie des idéologies qui figent l’Afrique dans une identité. Face à la &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude" title=" Wikipedia"&gt;négritude&lt;/a&gt; de Senghor, il lance une formule restée célèbre : « Le tigre ne proclame pas sa tigritude : il bondit sur sa proie et la dévore. » Dans &lt;em&gt;Mythe, littérature et le monde africain&lt;/em&gt; (1976), il s’appuie sur la mythologie yoruba, notamment sur le dieu Ogun, créateur et destructeur, pour penser la tragédie, la création et le lien entre les vivants, les morts et ceux qui ne sont pas encore nés.&lt;/p&gt; &lt;p&gt;Sa vie est aussi un combat pour la liberté. Emprisonné pendant près de deux ans lors de la guerre du Biafra pour avoir tenté une médiation, il raconte sa détention dans &lt;em&gt;Cet homme est mort&lt;/em&gt;. Sous la dictature de Sani Abacha, dans les années 1990, il doit s’exiler et est condamné à mort par contumace. Il ne cesse de dénoncer la corruption, la tyrannie et les fanatismes, et défend une mémoire lucide des crimes du passé, dans un esprit de justice et de réparation. Il a enseigné dans de nombreuses universités, au Nigeria, en Grande-Bretagne et aux États-Unis.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/soyinka-mini.webp</t>
+        </is>
+      </c>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nigériane</t>
+        </is>
+      </c>
+      <c r="K113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dramaturge et essayiste nigérian, prix Nobel de littérature, penseur de la tragédie et de la liberté.</t>
+        </is>
+      </c>
+      <c r="O113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P113" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0">
+        <v>1949</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1949</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silvia RIVERA CUSICANQUI</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silvia_Rivera_Cusicanqui" title=" Wikipedia"&gt;Silvia RIVERA CUSICANQUI&lt;/a&gt; est une sociologue, historienne et militante bolivienne, l’une des grandes voix de la pensée décoloniale en Amérique latine. Née à La Paz, d’ascendance &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymara&lt;/a&gt; et européenne, elle enseigne pendant plus de trente ans la sociologie à l’université de La Paz. Elle fonde en 1983 l’Atelier d’histoire orale andine, qui recueille la mémoire des communautés indiennes, et travaille aux côtés des mouvements indigènes et paysans, comme les cultivateurs de coca.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Opprimés mais pas vaincus&lt;/em&gt; (1984) raconte un siècle de luttes des paysans aymaras et quechuas de Bolivie, à partir de leur propre mémoire et non des seules archives de l’État. Elle y montre que le colonialisme n’a pas pris fin avec l’indépendance : il se prolonge dans les hiérarchies raciales, dans le mépris des langues et des savoirs indiens, et jusque dans la manière de penser des élites.&lt;/p&gt; &lt;p&gt;Elle propose la notion aymara de &lt;em&gt;ch’ixi&lt;/em&gt;, qui désigne une couleur grise faite de minuscules points noirs et blancs juxtaposés, qui ne se mélangent pas. Contre l’idée d’un métissage harmonieux qui efface les différences, le monde &lt;em&gt;ch’ixi&lt;/em&gt; est celui de la coexistence de cultures différentes, en tension, sans fusion. Elle critique aussi le « multiculturalisme officiel », qui célèbre les Indiens tout en maintenant leur domination, et défend l’autonomie des communautés, nourrie d’anarchisme. Son essai &lt;em&gt;Ch’ixinakax utxiwa&lt;/em&gt; (2010) est devenu un texte de référence de la pensée décoloniale. Elle réalise aussi des films documentaires, et réfléchit à ce que les images disent de la société.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/riveracusicanqui-mini.webp</t>
+        </is>
+      </c>
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolivienne</t>
+        </is>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme ; Anarchisme</t>
+        </is>
+      </c>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue et historienne bolivienne, penseuse aymara du « monde ch’ixi » et critique de la décolonisation de façade.</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P114" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; genre</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -3299,7 +3299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD114"/>
+  <dimension ref="A1:XFD116"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -6885,8 +6885,10 @@
       <c r="K82" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>644</v>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie ; Pan-africanisme ; Pensée décoloniale</t>
+        </is>
       </c>
       <c r="M82" s="2" t="s">
         <v>645</v>
@@ -8143,7 +8145,7 @@
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme</t>
+          <t xml:space="preserve">Anticolonialisme ; Pensée décoloniale</t>
         </is>
       </c>
       <c r="M110" s="0" t="inlineStr">
@@ -8404,6 +8406,118 @@
       <c r="Q114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">decolonial ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0">
+        <v>1938</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leonardo BOFF</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leonardo_Boff" title=" Wikipedia"&gt;Leonardo BOFF&lt;/a&gt; (né Genézio Darci Boff) est un théologien et philosophe brésilien, l’une des grandes figures de la théologie de la libération. Né en 1938 à Concórdia, dans le sud du Brésil, petit-fils d’immigrés italiens, il entre chez les franciscains en 1959, est ordonné prêtre en 1964 et soutient en 1970 à Munich une thèse sur l’Église comme sacrement dans le monde. Il enseigne ensuite la théologie pendant plus de vingt ans à Petrópolis, près de Rio de Janeiro.&lt;/p&gt; &lt;p&gt;Proche des &lt;a href="https://fr.wikipedia.org/wiki/Communaut%C3%A9_eccl%C3%A9siale_de_base" title=" Wikipedia"&gt;communautés ecclésiales de base&lt;/a&gt;, il défend une Église des pauvres, où les laïcs prennent la parole. Son livre &lt;em&gt;Église : charisme et pouvoir&lt;/em&gt; (1981) critique la centralisation et l’autoritarisme de l’institution romaine. Convoqué à Rome en 1984 par le cardinal Joseph Ratzinger, qui avait été l’un des rapporteurs de sa thèse, il est condamné en 1985 à un an de « silence respectueux ». Menacé d’une nouvelle sanction en 1992, au moment du Sommet de la Terre de Rio, il quitte l’ordre franciscain et le ministère de prêtre, tout en restant théologien.&lt;/p&gt; &lt;p&gt;Il élargit alors la théologie de la libération à l’écologie : dans &lt;em&gt;Cri de la Terre, cri des pauvres&lt;/em&gt; (1995), il montre que l’exploitation de la nature et celle des pauvres relèvent de la même logique de domination, et que la Terre elle-même doit être libérée. Il participe à la rédaction de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_de_la_Terre" title=" Wikipedia"&gt;Charte de la Terre&lt;/a&gt; et reçoit en 2001 le prix Nobel alternatif. On a souvent souligné la proximité de ses idées avec l’encyclique &lt;a href="https://fr.wikipedia.org/wiki/Laudato_si%27" title=" Wikipedia"&gt;&lt;em&gt;Laudato si’&lt;/em&gt;&lt;/a&gt; du pape François (2015).&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lboff-mini.webp</t>
+        </is>
+      </c>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brésilienne</t>
+        </is>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération ; Ecologisme</t>
+        </is>
+      </c>
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien brésilien de la libération, sanctionné par Rome, puis penseur d’une écologie qui unit le cri de la Terre et celui des pauvres.</t>
+        </is>
+      </c>
+      <c r="O115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P115" s="0"/>
+      <c r="Q115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0">
+        <v>1941</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1941</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walter MIGNOLO</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter MIGNOLO&lt;/a&gt; est un sémiologue et penseur argentin, l’une des figures majeures de la &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;pensée décoloniale&lt;/a&gt;. Né en 1941 dans la province de Córdoba, il étudie la philosophie en Argentine, puis la sémiotique et la théorie littéraire à Paris, dans les années 1970. Installé aux États-Unis, il enseigne la littérature et les études culturelles à l’université Duke.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;The Darker Side of the Renaissance&lt;/em&gt; (1995), il montre que la Renaissance européenne a aussi une « face sombre » : la colonisation de l’Amérique, qui s’est accompagnée de la destruction ou du mépris des écritures, des mémoires et des cartes des peuples amérindiens. Avec Aníbal Quijano et Enrique Dussel, il fonde le groupe « modernité/colonialité ». Dans &lt;em&gt;Histoires locales / projets globaux&lt;/em&gt; (1999), il développe la notion de « pensée frontalière », empruntée à la poétesse chicana &lt;a href="https://fr.wikipedia.org/wiki/Gloria_Anzald%C3%BAa" title=" Wikipedia"&gt;Gloria Anzaldúa&lt;/a&gt; : penser depuis la frontière entre les cultures et depuis les marges du monde moderne, plutôt que depuis son centre. Contre l’universalisme qui impose un seul modèle de savoir, il défend la « pluriversalité », un monde où coexistent plusieurs manières de connaître et de vivre, et appelle à la « désobéissance épistémique ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;The Idea of Latin America&lt;/em&gt; (2005), il montre que l’« Amérique latine » est elle-même une invention, née d’un projet des élites créoles du XIXe siècle. Ses travaux, très lus dans les universités américaines, sont aussi critiqués, notamment par Silvia Rivera Cusicanqui, qui reproche à la pensée décoloniale d’être devenue une théorie de campus, éloignée des luttes réelles.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mignolo-mini.webp</t>
+        </is>
+      </c>
+      <c r="J116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentine</t>
+        </is>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="M116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sémiologue argentin, penseur de la « pensée frontalière », de la pluriversalité et de la désobéissance épistémique.</t>
+        </is>
+      </c>
+      <c r="O116" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P116" s="0"/>
+      <c r="Q116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-autre-actif.xlsx
+++ b/data/frise-philosophes-autre-actif.xlsx
@@ -5089,53 +5089,80 @@
         <v>342</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="178.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0">
+        <v>1949</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1949</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silvia RIVERA CUSICANQUI</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silvia_Rivera_Cusicanqui" title=" Wikipedia"&gt;Silvia RIVERA CUSICANQUI&lt;/a&gt; est une sociologue, historienne et militante bolivienne, l’une des grandes voix de la pensée décoloniale en Amérique latine. Née à La Paz, d’ascendance &lt;a href="https://fr.wikipedia.org/wiki/Aymaras" title=" Wikipedia"&gt;aymara&lt;/a&gt; et européenne, elle enseigne pendant plus de trente ans la sociologie à l’université de La Paz. Elle fonde en 1983 l’Atelier d’histoire orale andine, qui recueille la mémoire des communautés indiennes, et travaille aux côtés des mouvements indigènes et paysans, comme les cultivateurs de coca.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Opprimés mais pas vaincus&lt;/em&gt; (1984) raconte un siècle de luttes des paysans aymaras et quechuas de Bolivie, à partir de leur propre mémoire et non des seules archives de l’État. Elle y montre que le colonialisme n’a pas pris fin avec l’indépendance : il se prolonge dans les hiérarchies raciales, dans le mépris des langues et des savoirs indiens, et jusque dans la manière de penser des élites.&lt;/p&gt; &lt;p&gt;Elle propose la notion aymara de &lt;em&gt;ch’ixi&lt;/em&gt;, qui désigne une couleur grise faite de minuscules points noirs et blancs juxtaposés, qui ne se mélangent pas. Contre l’idée d’un métissage harmonieux qui efface les différences, le monde &lt;em&gt;ch’ixi&lt;/em&gt; est celui de la coexistence de cultures différentes, en tension, sans fusion. Elle critique aussi le « multiculturalisme officiel », qui célèbre les Indiens tout en maintenant leur domination, et défend l’autonomie des communautés, nourrie d’anarchisme. Son essai &lt;em&gt;&lt;a href="https://criticaltheoryworkshop.com/wp-content/uploads/2018/05/rivera-cusicanqui-chixinakax-eng.pdf" title="Silvia Rivera Cusicanqui par criticaltheory"&gt;Ch’ixinakax utxiwa&lt;/a&gt;&lt;/em&gt; (2010) est devenu un texte de référence de la &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;pensée décoloniale&lt;/a&gt;. Elle réalise aussi des films documentaires, et réfléchit à ce que les images disent de la société.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pHJkCqe2gAk</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Revista de la Universidad "Utopía ch'ixi" con Silvia Rivera Cusicanqui" par TV UNAM</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/riveracusicanqui-mini.webp</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolivienne</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme ; Anarchisme</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue et historienne bolivienne, penseuse aymara du « monde ch’ixi » et critique de la décolonisation de façade.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P42" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial ; genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>1950</v>
       </c>
@@ -5144,173 +5171,173 @@
         <v>343</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="1" t="s">
-        <v>356</v>
+        <v>91</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B44" s="7"/>
-      <c r="C44" s="7" t="n">
-        <v>1950</v>
+      <c r="C44" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>360</v>
+        <v>351</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>352</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>363</v>
+        <v>354</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="1" t="s">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>366</v>
+        <v>171</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="7" t="s">
-        <v>343</v>
+      <c r="C45" s="7" t="n">
+        <v>1950</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>368</v>
+        <v>359</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>360</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>371</v>
+        <v>362</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>363</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>146</v>
+        <v>364</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>366</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="7" t="n">
-        <v>1950</v>
+      <c r="C46" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>374</v>
+        <v>367</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>368</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>377</v>
+        <v>370</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>371</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="1" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>378</v>
+        <v>146</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>379</v>
+        <v>196</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>95</v>
+        <v>372</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>1950</v>
       </c>
@@ -5318,91 +5345,91 @@
       <c r="C47" s="7" t="n">
         <v>1950</v>
       </c>
-      <c r="D47" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>382</v>
+      <c r="D47" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>374</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="1" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>212</v>
+        <v>378</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="C48" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>390</v>
+      <c r="C48" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>382</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>393</v>
+        <v>384</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>385</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="1" t="s">
-        <v>60</v>
+        <v>291</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>63</v>
+        <v>295</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>1952</v>
       </c>
@@ -5411,44 +5438,44 @@
         <v>388</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>398</v>
+        <v>389</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="1" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
         <v>1952</v>
       </c>
@@ -5457,44 +5484,44 @@
         <v>388</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>405</v>
+        <v>397</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>398</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>212</v>
+        <v>92</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>1952</v>
       </c>
@@ -5503,130 +5530,130 @@
         <v>388</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="216.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
         <v>1952</v>
       </c>
       <c r="B52" s="7"/>
-      <c r="C52" s="7" t="n">
-        <v>1952</v>
+      <c r="C52" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>419</v>
+        <v>411</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>412</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>422</v>
+        <v>414</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>415</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="M52" s="15" t="s">
-        <v>424</v>
+        <v>416</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="325.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B53" s="7"/>
-      <c r="C53" s="7" t="s">
-        <v>425</v>
+      <c r="C53" s="7" t="n">
+        <v>1952</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>427</v>
+        <v>418</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>419</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>430</v>
+        <v>421</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>422</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>41</v>
+        <v>423</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="288" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
         <v>1953</v>
       </c>
@@ -5635,44 +5662,44 @@
         <v>425</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
         <v>1953</v>
       </c>
@@ -5681,19 +5708,19 @@
         <v>425</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
@@ -5703,22 +5730,22 @@
         <v>50</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
         <v>1953</v>
       </c>
@@ -5727,87 +5754,87 @@
         <v>425</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>448</v>
+        <v>440</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>441</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>292</v>
+        <v>50</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>456</v>
+        <v>447</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>448</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>460</v>
+        <v>91</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>117</v>
+        <v>453</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
         <v>1954</v>
       </c>
@@ -5816,41 +5843,44 @@
         <v>454</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>465</v>
+        <v>455</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>456</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>91</v>
+        <v>460</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
         <v>1954</v>
       </c>
@@ -5859,41 +5889,41 @@
         <v>454</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>472</v>
+        <v>464</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>465</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>476</v>
+        <v>91</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>477</v>
+        <v>92</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>125</v>
+        <v>452</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1954</v>
       </c>
@@ -5902,127 +5932,127 @@
         <v>454</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>480</v>
+        <v>471</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>472</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="1" t="s">
-        <v>80</v>
+        <v>476</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>485</v>
+        <v>125</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
         <v>1954</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>489</v>
+      <c r="C61" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>492</v>
+        <v>482</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>483</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="1" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>70</v>
+        <v>484</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B62" s="7"/>
-      <c r="C62" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>497</v>
+      <c r="C62" s="7" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>489</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>500</v>
+        <v>491</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>492</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="1" t="s">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>301</v>
+        <v>70</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>125</v>
+        <v>493</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="216" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
         <v>1955</v>
       </c>
@@ -6031,41 +6061,41 @@
         <v>495</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>503</v>
+        <v>496</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>497</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="1" t="s">
-        <v>507</v>
+        <v>80</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>508</v>
+        <v>301</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>509</v>
+        <v>125</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="161.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
         <v>1955</v>
       </c>
@@ -6074,179 +6104,176 @@
         <v>495</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>513</v>
+        <v>502</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>503</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="1" t="s">
-        <v>91</v>
+        <v>507</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>402</v>
+        <v>509</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>95</v>
+        <v>510</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="170.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="7" t="n">
-        <v>1955</v>
+      <c r="C65" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>519</v>
+        <v>512</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>513</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>196</v>
+        <v>402</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="7" t="s">
-        <v>524</v>
+      <c r="C66" s="7" t="n">
+        <v>1955</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>526</v>
+        <v>518</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>196</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>95</v>
+        <v>523</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="7" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>533</v>
+        <v>525</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>526</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>537</v>
+        <v>196</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>538</v>
+        <v>530</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P67" s="1" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="231.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
         <v>1957</v>
       </c>
@@ -6255,81 +6282,84 @@
         <v>531</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>541</v>
+        <v>532</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>533</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="1" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>545</v>
+        <v>220</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
+      </c>
+      <c r="P68" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>470</v>
+        <v>539</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="7" t="n">
-        <v>1958</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>549</v>
+      <c r="C69" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>541</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="1" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>220</v>
+        <v>545</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>139</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6341,19 +6371,21 @@
         <v>1958</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>558</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="I70" s="10"/>
       <c r="J70" s="1" t="s">
         <v>291</v>
       </c>
@@ -6364,7 +6396,7 @@
         <v>553</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>295</v>
@@ -6373,50 +6405,48 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B71" s="7"/>
-      <c r="C71" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>562</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="I71" s="10"/>
+      <c r="C71" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>558</v>
+      </c>
       <c r="J71" s="1" t="s">
-        <v>134</v>
+        <v>291</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>138</v>
+        <v>295</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="171.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
         <v>1958</v>
       </c>
@@ -6425,41 +6455,41 @@
         <v>560</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>569</v>
+        <v>561</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>562</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="1" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>238</v>
+        <v>566</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
         <v>1958</v>
       </c>
@@ -6468,130 +6498,127 @@
         <v>560</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>575</v>
+        <v>568</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>569</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="1" t="s">
-        <v>476</v>
+        <v>25</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>92</v>
+        <v>349</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>402</v>
+        <v>238</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
         <v>1958</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="7" t="n">
-        <v>1958</v>
+      <c r="C74" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>581</v>
+        <v>574</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>575</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>584</v>
+        <v>577</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>578</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="1" t="s">
-        <v>114</v>
+        <v>476</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="M74" s="15" t="s">
-        <v>586</v>
+        <v>402</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>579</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B75" s="7"/>
-      <c r="C75" s="7" t="s">
-        <v>587</v>
+      <c r="C75" s="7" t="n">
+        <v>1958</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>589</v>
+        <v>580</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>581</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>592</v>
+        <v>583</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>584</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="1" t="s">
-        <v>318</v>
+        <v>114</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>41</v>
+        <v>585</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>586</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
         <v>1959</v>
       </c>
@@ -6600,262 +6627,265 @@
         <v>587</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="1" t="s">
-        <v>599</v>
+        <v>318</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="N76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O76" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="Q76" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B77" s="7"/>
-      <c r="C77" s="7" t="n">
-        <v>1960</v>
+      <c r="C77" s="7" t="s">
+        <v>587</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="E77" s="21" t="s">
-        <v>602</v>
+        <v>594</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>595</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>604</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>598</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="I78" s="10"/>
+      <c r="J78" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="L77" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="M77" s="15" t="s">
+      <c r="M78" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q77" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>117</v>
       </c>
       <c r="Q78" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q79" s="2" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="I79" s="10"/>
-      <c r="J79" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q79" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="7" t="n">
-        <v>1961</v>
+      <c r="C80" s="7" t="s">
+        <v>619</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="F80" s="7"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="14" t="s">
-        <v>629</v>
-      </c>
-      <c r="I80" s="14" t="s">
-        <v>630</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I80" s="10"/>
       <c r="J80" s="1" t="s">
-        <v>25</v>
+        <v>625</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>41</v>
+        <v>626</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B81" s="7"/>
-      <c r="C81" s="7" t="s">
-        <v>632</v>
+      <c r="C81" s="7" t="n">
+        <v>1961</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="I81" s="10"/>
+        <v>628</v>
+      </c>
+      <c r="F81" s="7"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>630</v>
+      </c>
       <c r="J81" s="1" t="s">
-        <v>318</v>
+        <v>25</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>638</v>
+        <v>631</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O81" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
         <v>1962</v>
       </c>
@@ -6864,218 +6894,218 @@
         <v>632</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="1" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phénoménologie ; Pan-africanisme ; Pensée décoloniale</t>
-        </is>
+      <c r="L82" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>106</v>
+        <v>638</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="171" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="B83" s="7"/>
-      <c r="C83" s="7" t="n">
-        <v>1962</v>
+      <c r="C83" s="7" t="s">
+        <v>632</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>647</v>
+        <v>639</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>640</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>650</v>
+        <v>642</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>643</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>652</v>
+        <v>50</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie ; Pan-africanisme ; Pensée décoloniale</t>
+        </is>
       </c>
       <c r="M83" s="2" t="s">
-        <v>653</v>
+        <v>645</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B84" s="7"/>
-      <c r="C84" s="7" t="s">
-        <v>655</v>
+      <c r="C84" s="7" t="n">
+        <v>1962</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>657</v>
+        <v>646</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>647</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>660</v>
+        <v>649</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>650</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="1" t="s">
         <v>80</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>665</v>
+        <v>656</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>657</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>124</v>
+        <v>661</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>669</v>
+        <v>566</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="114.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>673</v>
+        <v>664</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>665</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>255</v>
+        <v>669</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
         <v>1965</v>
       </c>
@@ -7084,173 +7114,170 @@
         <v>671</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>678</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>679</v>
+        <v>672</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>673</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>661</v>
+        <v>50</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>683</v>
+        <v>255</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="1" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>349</v>
+        <v>661</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="363" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="7" t="n">
-        <v>1966</v>
+      <c r="C89" s="7" t="s">
+        <v>685</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="H89" s="14" t="s">
-        <v>697</v>
+        <v>689</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>690</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="1" t="s">
-        <v>698</v>
+        <v>185</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>92</v>
+        <v>349</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="224.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="7" t="s">
-        <v>701</v>
+      <c r="C90" s="7" t="n">
+        <v>1966</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>694</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="H90" s="10" t="s">
-        <v>706</v>
+        <v>696</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>697</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="1" t="s">
-        <v>91</v>
+        <v>698</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>707</v>
+        <v>92</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>41</v>
+        <v>700</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
         <v>1968</v>
       </c>
@@ -7259,41 +7286,44 @@
         <v>701</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>712</v>
+        <v>702</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>703</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>292</v>
+        <v>707</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>717</v>
+        <v>709</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
         <v>1968</v>
       </c>
@@ -7302,38 +7332,38 @@
         <v>701</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>720</v>
+        <v>711</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>712</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>127</v>
+        <v>718</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7341,352 +7371,349 @@
         <v>1968</v>
       </c>
       <c r="B93" s="7"/>
-      <c r="C93" s="7" t="n">
-        <v>1968</v>
+      <c r="C93" s="7" t="s">
+        <v>701</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="H93" s="14" t="s">
-        <v>730</v>
+        <v>722</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>723</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="1" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>92</v>
+        <v>364</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B94" s="7"/>
-      <c r="C94" s="7" t="s">
-        <v>732</v>
+      <c r="C94" s="7" t="n">
+        <v>1968</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>734</v>
+        <v>726</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>727</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>736</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>737</v>
+        <v>729</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>730</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="1" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>545</v>
+        <v>92</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>125</v>
+        <v>699</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="1" t="s">
-        <v>745</v>
+        <v>91</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>124</v>
+        <v>545</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>125</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>41</v>
+        <v>738</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>749</v>
+        <v>740</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>741</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="1" t="s">
-        <v>25</v>
+        <v>745</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>661</v>
+        <v>124</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>566</v>
+        <v>125</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>756</v>
+        <v>747</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>749</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="1" t="s">
-        <v>507</v>
+        <v>25</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>50</v>
+        <v>661</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="M97" s="15" t="s">
-        <v>761</v>
+        <v>566</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>753</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="163.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>764</v>
+        <v>754</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>756</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="1" t="s">
-        <v>768</v>
+        <v>507</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>545</v>
+        <v>50</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>770</v>
+        <v>760</v>
+      </c>
+      <c r="M98" s="15" t="s">
+        <v>761</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>773</v>
+        <v>763</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>764</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="1" t="s">
-        <v>91</v>
+        <v>768</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>124</v>
+        <v>545</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>125</v>
+        <v>769</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>780</v>
+        <v>772</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>773</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>349</v>
+        <v>124</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="M100" s="15" t="s">
-        <v>784</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
         <v>1975</v>
       </c>
@@ -7695,84 +7722,87 @@
         <v>778</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="1" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="M101" s="2" t="s">
-        <v>792</v>
+        <v>708</v>
+      </c>
+      <c r="M101" s="15" t="s">
+        <v>784</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="222.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>796</v>
+        <v>786</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>787</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="1" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>661</v>
+        <v>70</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>683</v>
+        <v>791</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="O102" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>127</v>
+        <v>793</v>
       </c>
     </row>
     